--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,57 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>Guabira</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Keflavik</t>
+  </si>
+  <si>
+    <t>Hafnarfjordur</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>Deportivo Pasto</t>
+  </si>
+  <si>
+    <t>KA Akureyri</t>
+  </si>
+  <si>
+    <t>KR Reykjavik</t>
+  </si>
+  <si>
+    <t>2026-08-03 01:08:30</t>
   </si>
 </sst>
 </file>
@@ -585,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +879,974 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2">
+        <v>1.04</v>
+      </c>
+      <c r="G2">
+        <v>1.45</v>
+      </c>
+      <c r="H2">
+        <v>1.78</v>
+      </c>
+      <c r="I2">
+        <v>870</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
+        <v>950</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.46</v>
+      </c>
+      <c r="O2">
+        <v>1.08</v>
+      </c>
+      <c r="P2">
+        <v>1.45</v>
+      </c>
+      <c r="Q2">
+        <v>1.08</v>
+      </c>
+      <c r="R2">
+        <v>1.45</v>
+      </c>
+      <c r="S2">
+        <v>1.47</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>1.75</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3">
+        <v>1.57</v>
+      </c>
+      <c r="G3">
+        <v>1.66</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>3.95</v>
+      </c>
+      <c r="K3">
+        <v>4.5</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>3.4</v>
+      </c>
+      <c r="O3">
+        <v>1.33</v>
+      </c>
+      <c r="P3">
+        <v>1.82</v>
+      </c>
+      <c r="Q3">
+        <v>1.98</v>
+      </c>
+      <c r="R3">
+        <v>1.32</v>
+      </c>
+      <c r="S3">
+        <v>3.55</v>
+      </c>
+      <c r="T3">
+        <v>2.06</v>
+      </c>
+      <c r="U3">
+        <v>1.8</v>
+      </c>
+      <c r="V3">
+        <v>1.14</v>
+      </c>
+      <c r="W3">
+        <v>2.52</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>7.4</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>12</v>
+      </c>
+      <c r="AQ3">
+        <v>17.5</v>
+      </c>
+      <c r="AR3">
+        <v>1.51</v>
+      </c>
+      <c r="AS3">
+        <v>1.51</v>
+      </c>
+      <c r="AT3">
+        <v>6.2</v>
+      </c>
+      <c r="AU3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>1.51</v>
+      </c>
+      <c r="AW3">
+        <v>1.51</v>
+      </c>
+      <c r="AX3">
+        <v>7.6</v>
+      </c>
+      <c r="AY3">
+        <v>1.32</v>
+      </c>
+      <c r="AZ3">
+        <v>21</v>
+      </c>
+      <c r="BA3">
+        <v>1.51</v>
+      </c>
+      <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
+        <v>15.5</v>
+      </c>
+      <c r="BD3">
+        <v>1.51</v>
+      </c>
+      <c r="BE3">
+        <v>1.51</v>
+      </c>
+      <c r="BF3">
+        <v>7.8</v>
+      </c>
+      <c r="BG3">
+        <v>1.51</v>
+      </c>
+      <c r="BH3">
+        <v>4.5</v>
+      </c>
+      <c r="BI3">
+        <v>1.82</v>
+      </c>
+      <c r="BJ3">
+        <v>16</v>
+      </c>
+      <c r="BK3">
+        <v>2.56</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>3.05</v>
+      </c>
+      <c r="BN3">
+        <v>5.5</v>
+      </c>
+      <c r="BO3">
+        <v>2.76</v>
+      </c>
+      <c r="BP3">
+        <v>15.5</v>
+      </c>
+      <c r="BQ3">
+        <v>2.54</v>
+      </c>
+      <c r="BR3">
+        <v>44</v>
+      </c>
+      <c r="BS3">
+        <v>2.86</v>
+      </c>
+      <c r="BT3">
+        <v>15</v>
+      </c>
+      <c r="BU3">
+        <v>2.54</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>2.96</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>2.96</v>
+      </c>
+      <c r="BZ3">
+        <v>32</v>
+      </c>
+      <c r="CA3">
+        <v>2.78</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.24</v>
+      </c>
+      <c r="Q4">
+        <v>1.01</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -304,7 +304,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 01:08:30</t>
+    <t>2026-08-03 03:16:47</t>
   </si>
 </sst>
 </file>
@@ -1143,109 +1143,109 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>1.32</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
         <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
         <v>1.14</v>
       </c>
       <c r="W3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP3">
         <v>12</v>
@@ -1254,10 +1254,10 @@
         <v>17.5</v>
       </c>
       <c r="AR3">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="AS3">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="AT3">
         <v>6.2</v>
@@ -1266,22 +1266,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>1.51</v>
+        <v>4.1</v>
       </c>
       <c r="AW3">
-        <v>1.51</v>
+        <v>4.5</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>1.32</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>1.51</v>
+        <v>4.5</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1290,76 +1290,76 @@
         <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>1.51</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG3">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="BH3">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI3">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="BJ3">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>2.56</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>3.05</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BO3">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>2.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.96</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.78</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -304,7 +304,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 03:16:47</t>
+    <t>2026-08-03 05:24:55</t>
   </si>
 </sst>
 </file>
@@ -904,10 +904,10 @@
         <v>1.45</v>
       </c>
       <c r="H2">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J2">
         <v>3.4</v>
@@ -940,16 +940,16 @@
         <v>1.47</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
         <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1063,55 +1063,55 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>1.65</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1158,37 +1158,37 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
         <v>2.56</v>
@@ -1200,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="Z3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA3">
         <v>270</v>
@@ -1242,7 +1242,7 @@
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
         <v>200</v>
@@ -1254,10 +1254,10 @@
         <v>17.5</v>
       </c>
       <c r="AR3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT3">
         <v>6.2</v>
@@ -1266,10 +1266,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
@@ -1281,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1290,37 +1290,37 @@
         <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF3">
         <v>8</v>
       </c>
       <c r="BG3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO3">
         <v>3.6</v>
@@ -1329,37 +1329,37 @@
         <v>11</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -304,7 +304,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 05:24:55</t>
+    <t>2026-08-03 07:32:48</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
         <v>1.08</v>
       </c>
       <c r="P2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
         <v>1.08</v>
@@ -1143,7 +1143,7 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -1158,7 +1158,7 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
         <v>1.07</v>
@@ -1167,7 +1167,7 @@
         <v>3.55</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
         <v>1.87</v>
@@ -1191,7 +1191,7 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X3">
         <v>17</v>
@@ -1260,7 +1260,7 @@
         <v>4.8</v>
       </c>
       <c r="AT3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
         <v>8.199999999999999</v>
@@ -1272,7 +1272,7 @@
         <v>4.7</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY3">
         <v>8.6</v>
@@ -1323,7 +1323,7 @@
         <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -304,7 +304,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 07:32:48</t>
+    <t>2026-08-03 09:40:53</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1158,7 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
         <v>1.07</v>
@@ -1167,7 +1167,7 @@
         <v>3.55</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>1.87</v>
@@ -1332,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>9.199999999999999</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -304,7 +304,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 09:40:53</t>
+    <t>2026-08-03 11:49:47</t>
   </si>
 </sst>
 </file>
@@ -898,22 +898,22 @@
         <v>92</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="G2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -922,22 +922,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>2.86</v>
       </c>
       <c r="Q2">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="S2">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -946,10 +946,10 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1143,7 +1143,7 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -1164,37 +1164,37 @@
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
         <v>1.87</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
         <v>1.33</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3">
         <v>25</v>
@@ -1221,7 +1221,7 @@
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>30</v>
@@ -1248,76 +1248,76 @@
         <v>200</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
         <v>17.5</v>
       </c>
       <c r="AR3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="AW3">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
         <v>8.6</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC3">
         <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BE3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
@@ -1329,37 +1329,37 @@
         <v>11</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>01:20:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -286,6 +292,9 @@
     <t>Millonarios</t>
   </si>
   <si>
+    <t>ACS Dumbravita</t>
+  </si>
+  <si>
     <t>Keflavik</t>
   </si>
   <si>
@@ -298,13 +307,16 @@
     <t>Deportivo Pasto</t>
   </si>
   <si>
+    <t>CSM Satu Mare</t>
+  </si>
+  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 11:49:47</t>
+    <t>2026-08-03 13:58:24</t>
   </si>
 </sst>
 </file>
@@ -636,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -886,34 +898,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="G2">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>990</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -922,22 +934,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
-        <v>2.86</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="R2">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="S2">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -949,7 +961,7 @@
         <v>1.11</v>
       </c>
       <c r="W2">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1120,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1128,94 +1140,94 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
         <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R3">
         <v>1.33</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
         <v>2</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="X3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AB3">
         <v>9</v>
       </c>
       <c r="AC3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>11</v>
@@ -1224,10 +1236,10 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
         <v>18.5</v>
@@ -1236,40 +1248,40 @@
         <v>22</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN3">
         <v>12.5</v>
       </c>
       <c r="AO3">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV3">
         <v>19</v>
       </c>
       <c r="AW3">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1278,91 +1290,91 @@
         <v>8.6</v>
       </c>
       <c r="AZ3">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BA3">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC3">
         <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF3">
         <v>8.800000000000001</v>
       </c>
       <c r="BG3">
+        <v>4.7</v>
+      </c>
+      <c r="BH3">
+        <v>3.85</v>
+      </c>
+      <c r="BI3">
+        <v>2.68</v>
+      </c>
+      <c r="BJ3">
+        <v>13</v>
+      </c>
+      <c r="BK3">
+        <v>3.55</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>4.7</v>
+      </c>
+      <c r="BN3">
+        <v>4.9</v>
+      </c>
+      <c r="BO3">
+        <v>3.65</v>
+      </c>
+      <c r="BP3">
+        <v>14</v>
+      </c>
+      <c r="BQ3">
+        <v>8.4</v>
+      </c>
+      <c r="BR3">
+        <v>36</v>
+      </c>
+      <c r="BS3">
         <v>4.3</v>
       </c>
-      <c r="BH3">
-        <v>3.45</v>
-      </c>
-      <c r="BI3">
-        <v>2.74</v>
-      </c>
-      <c r="BJ3">
+      <c r="BT3">
         <v>11.5</v>
       </c>
-      <c r="BK3">
-        <v>6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>11.5</v>
-      </c>
-      <c r="BN3">
+      <c r="BU3">
+        <v>7</v>
+      </c>
+      <c r="BV3">
+        <v>70</v>
+      </c>
+      <c r="BW3">
+        <v>4.5</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>4.6</v>
+      </c>
+      <c r="BZ3">
+        <v>28</v>
+      </c>
+      <c r="CA3">
         <v>4.1</v>
       </c>
-      <c r="BO3">
-        <v>3.15</v>
-      </c>
-      <c r="BP3">
-        <v>11</v>
-      </c>
-      <c r="BQ3">
-        <v>5.9</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT3">
-        <v>10.5</v>
-      </c>
-      <c r="BU3">
-        <v>5.7</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>10.5</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>10.5</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>8</v>
-      </c>
       <c r="CB3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1370,258 +1382,258 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1846,7 +1858,249 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>96</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -316,7 +316,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 13:58:24</t>
+    <t>2026-08-03 16:06:25</t>
   </si>
 </sst>
 </file>
@@ -910,166 +910,166 @@
         <v>95</v>
       </c>
       <c r="F2">
+        <v>1.34</v>
+      </c>
+      <c r="G2">
+        <v>1.44</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
+      </c>
+      <c r="I2">
+        <v>10.5</v>
+      </c>
+      <c r="J2">
+        <v>4.8</v>
+      </c>
+      <c r="K2">
+        <v>6.8</v>
+      </c>
+      <c r="L2">
+        <v>1.2</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>3.5</v>
+      </c>
+      <c r="O2">
         <v>1.12</v>
       </c>
-      <c r="G2">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>5.9</v>
-      </c>
-      <c r="I2">
-        <v>990</v>
-      </c>
-      <c r="J2">
-        <v>1.13</v>
-      </c>
-      <c r="K2">
-        <v>950</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>1.41</v>
-      </c>
-      <c r="O2">
-        <v>1.09</v>
-      </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="S2">
-        <v>1.09</v>
+        <v>1.96</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1152,226 +1152,226 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G3">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q3">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T3">
         <v>2</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y3">
         <v>23</v>
       </c>
       <c r="Z3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AB3">
+        <v>7.8</v>
+      </c>
+      <c r="AC3">
+        <v>10</v>
+      </c>
+      <c r="AD3">
+        <v>28</v>
+      </c>
+      <c r="AE3">
+        <v>130</v>
+      </c>
+      <c r="AF3">
         <v>9</v>
       </c>
-      <c r="AC3">
-        <v>11</v>
-      </c>
-      <c r="AD3">
-        <v>30</v>
-      </c>
-      <c r="AE3">
-        <v>120</v>
-      </c>
-      <c r="AF3">
-        <v>11</v>
-      </c>
       <c r="AG3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AJ3">
+        <v>16.5</v>
+      </c>
+      <c r="AK3">
         <v>18.5</v>
       </c>
-      <c r="AK3">
-        <v>22</v>
-      </c>
       <c r="AL3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
         <v>170</v>
       </c>
       <c r="AP3">
+        <v>12.5</v>
+      </c>
+      <c r="AQ3">
+        <v>20</v>
+      </c>
+      <c r="AR3">
+        <v>48</v>
+      </c>
+      <c r="AS3">
         <v>10.5</v>
       </c>
-      <c r="AQ3">
-        <v>16</v>
-      </c>
-      <c r="AR3">
-        <v>4.5</v>
-      </c>
-      <c r="AS3">
-        <v>4.7</v>
-      </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AW3">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BA3">
+        <v>10.5</v>
+      </c>
+      <c r="BB3">
+        <v>12.5</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>34</v>
+      </c>
+      <c r="BE3">
+        <v>10.5</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
+        <v>10.5</v>
+      </c>
+      <c r="BH3">
+        <v>3.95</v>
+      </c>
+      <c r="BI3">
+        <v>2.72</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>3.8</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>5.1</v>
+      </c>
+      <c r="BN3">
         <v>4.7</v>
       </c>
-      <c r="BB3">
-        <v>14</v>
-      </c>
-      <c r="BC3">
-        <v>15.5</v>
-      </c>
-      <c r="BD3">
-        <v>32</v>
-      </c>
-      <c r="BE3">
-        <v>4.7</v>
-      </c>
-      <c r="BF3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG3">
-        <v>4.7</v>
-      </c>
-      <c r="BH3">
-        <v>3.85</v>
-      </c>
-      <c r="BI3">
-        <v>2.68</v>
-      </c>
-      <c r="BJ3">
+      <c r="BO3">
+        <v>3.15</v>
+      </c>
+      <c r="BP3">
         <v>13</v>
       </c>
-      <c r="BK3">
-        <v>3.55</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>4.7</v>
-      </c>
-      <c r="BN3">
+      <c r="BQ3">
+        <v>3.75</v>
+      </c>
+      <c r="BR3">
+        <v>40</v>
+      </c>
+      <c r="BS3">
+        <v>4.4</v>
+      </c>
+      <c r="BT3">
+        <v>12</v>
+      </c>
+      <c r="BU3">
+        <v>3.65</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
         <v>4.9</v>
       </c>
-      <c r="BO3">
-        <v>3.65</v>
-      </c>
-      <c r="BP3">
-        <v>14</v>
-      </c>
-      <c r="BQ3">
-        <v>8.4</v>
-      </c>
-      <c r="BR3">
-        <v>36</v>
-      </c>
-      <c r="BS3">
-        <v>4.3</v>
-      </c>
-      <c r="BT3">
-        <v>11.5</v>
-      </c>
-      <c r="BU3">
-        <v>7</v>
-      </c>
-      <c r="BV3">
-        <v>70</v>
-      </c>
-      <c r="BW3">
-        <v>4.5</v>
-      </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1403,13 +1403,13 @@
         <v>1.04</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1442,10 +1442,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1654,208 +1654,208 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P5">
+        <v>1.25</v>
+      </c>
+      <c r="Q5">
+        <v>1.07</v>
+      </c>
+      <c r="R5">
         <v>1.24</v>
       </c>
-      <c r="Q5">
-        <v>1.01</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -316,7 +316,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 16:06:25</t>
+    <t>2026-08-03 18:13:16</t>
   </si>
 </sst>
 </file>
@@ -910,19 +910,19 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G2">
         <v>1.44</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>10.5</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>6.8</v>
@@ -934,16 +934,16 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="R2">
         <v>1.74</v>
@@ -955,7 +955,7 @@
         <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.1</v>
@@ -1000,7 +1000,7 @@
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK2">
         <v>15</v>
@@ -1015,31 +1015,31 @@
         <v>4.3</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
         <v>6</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
         <v>4.5</v>
       </c>
       <c r="AU2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
         <v>4.4</v>
@@ -1060,7 +1060,7 @@
         <v>4.5</v>
       </c>
       <c r="BD2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE2">
         <v>6</v>
@@ -1152,25 +1152,25 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H3">
         <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.07</v>
@@ -1179,7 +1179,7 @@
         <v>3.7</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
         <v>1.91</v>
@@ -1203,7 +1203,7 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X3">
         <v>15</v>
@@ -1227,7 +1227,7 @@
         <v>28</v>
       </c>
       <c r="AE3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>9</v>
@@ -1245,7 +1245,7 @@
         <v>16.5</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
         <v>42</v>
@@ -1254,7 +1254,7 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO3">
         <v>170</v>
@@ -1263,25 +1263,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AR3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1293,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1305,25 +1305,25 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
         <v>8.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI3">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1338,10 +1338,10 @@
         <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BR3">
         <v>40</v>
@@ -1350,10 +1350,10 @@
         <v>4.4</v>
       </c>
       <c r="BT3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1368,7 +1368,7 @@
         <v>4.9</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="CA3">
         <v>4.2</v>
@@ -1394,19 +1394,19 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1424,7 +1424,7 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q4">
         <v>1.22</v>
@@ -1660,7 +1660,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
         <v>1.07</v>
@@ -1672,7 +1672,7 @@
         <v>1.07</v>
       </c>
       <c r="R5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
         <v>1.07</v>
@@ -1744,52 +1744,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1896,208 +1896,208 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -316,7 +316,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 18:13:16</t>
+    <t>2026-08-03 20:20:42</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G2">
         <v>1.44</v>
@@ -919,10 +919,10 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K2">
         <v>6.8</v>
@@ -934,22 +934,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="Q2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
         <v>1.65</v>
@@ -958,7 +958,7 @@
         <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
         <v>3.2</v>
@@ -970,7 +970,7 @@
         <v>48</v>
       </c>
       <c r="Z2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA2">
         <v>270</v>
@@ -979,7 +979,7 @@
         <v>15</v>
       </c>
       <c r="AC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD2">
         <v>34</v>
@@ -997,7 +997,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>15</v>
@@ -1009,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AM2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN2">
         <v>4.3</v>
@@ -1018,16 +1018,16 @@
         <v>100</v>
       </c>
       <c r="AP2">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2">
         <v>5.7</v>
-      </c>
-      <c r="AQ2">
-        <v>5.8</v>
       </c>
       <c r="AR2">
         <v>6</v>
       </c>
       <c r="AS2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>4.5</v>
@@ -1036,10 +1036,10 @@
         <v>4.6</v>
       </c>
       <c r="AV2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX2">
         <v>4.4</v>
@@ -1060,7 +1060,7 @@
         <v>4.5</v>
       </c>
       <c r="BD2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE2">
         <v>6</v>
@@ -1155,7 +1155,7 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -1281,7 +1281,7 @@
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1293,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1317,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="BI3">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
@@ -1353,7 +1353,7 @@
         <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1394,19 +1394,19 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1418,13 +1418,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
         <v>1.22</v>
@@ -1657,10 +1657,10 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
         <v>1.07</v>
@@ -1675,13 +1675,13 @@
         <v>1.25</v>
       </c>
       <c r="S5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
         <v>1.01</v>
@@ -1801,61 +1801,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -2043,61 +2043,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -316,7 +316,7 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 20:20:42</t>
+    <t>2026-08-03 22:27:01</t>
   </si>
 </sst>
 </file>
@@ -910,166 +910,166 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="G2">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
+        <v>2.86</v>
+      </c>
+      <c r="Q2">
+        <v>1.42</v>
+      </c>
+      <c r="R2">
+        <v>1.77</v>
+      </c>
+      <c r="S2">
+        <v>2.04</v>
+      </c>
+      <c r="T2">
+        <v>1.62</v>
+      </c>
+      <c r="U2">
+        <v>2.3</v>
+      </c>
+      <c r="V2">
+        <v>1.15</v>
+      </c>
+      <c r="W2">
+        <v>2.78</v>
+      </c>
+      <c r="X2">
+        <v>36</v>
+      </c>
+      <c r="Y2">
+        <v>38</v>
+      </c>
+      <c r="Z2">
+        <v>70</v>
+      </c>
+      <c r="AA2">
+        <v>190</v>
+      </c>
+      <c r="AB2">
+        <v>16</v>
+      </c>
+      <c r="AC2">
+        <v>14</v>
+      </c>
+      <c r="AD2">
+        <v>29</v>
+      </c>
+      <c r="AE2">
+        <v>80</v>
+      </c>
+      <c r="AF2">
+        <v>13.5</v>
+      </c>
+      <c r="AG2">
+        <v>11.5</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>15.5</v>
+      </c>
+      <c r="AK2">
+        <v>17</v>
+      </c>
+      <c r="AL2">
+        <v>29</v>
+      </c>
+      <c r="AM2">
+        <v>75</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>70</v>
+      </c>
+      <c r="AP2">
+        <v>2.76</v>
+      </c>
+      <c r="AQ2">
+        <v>2.76</v>
+      </c>
+      <c r="AR2">
+        <v>2.86</v>
+      </c>
+      <c r="AS2">
+        <v>2.94</v>
+      </c>
+      <c r="AT2">
+        <v>2.52</v>
+      </c>
+      <c r="AU2">
+        <v>2.46</v>
+      </c>
+      <c r="AV2">
+        <v>2.7</v>
+      </c>
+      <c r="AW2">
+        <v>2.88</v>
+      </c>
+      <c r="AX2">
+        <v>2.44</v>
+      </c>
+      <c r="AY2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>2.6</v>
+      </c>
+      <c r="BA2">
+        <v>2.86</v>
+      </c>
+      <c r="BB2">
+        <v>2.5</v>
+      </c>
+      <c r="BC2">
+        <v>2.54</v>
+      </c>
+      <c r="BD2">
+        <v>2.7</v>
+      </c>
+      <c r="BE2">
+        <v>2.86</v>
+      </c>
+      <c r="BF2">
         <v>2.98</v>
       </c>
-      <c r="Q2">
-        <v>1.38</v>
-      </c>
-      <c r="R2">
-        <v>1.79</v>
-      </c>
-      <c r="S2">
-        <v>1.94</v>
-      </c>
-      <c r="T2">
-        <v>1.65</v>
-      </c>
-      <c r="U2">
-        <v>2.18</v>
-      </c>
-      <c r="V2">
-        <v>1.11</v>
-      </c>
-      <c r="W2">
-        <v>3.2</v>
-      </c>
-      <c r="X2">
-        <v>44</v>
-      </c>
-      <c r="Y2">
-        <v>48</v>
-      </c>
-      <c r="Z2">
-        <v>100</v>
-      </c>
-      <c r="AA2">
-        <v>270</v>
-      </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>16</v>
-      </c>
-      <c r="AD2">
-        <v>34</v>
-      </c>
-      <c r="AE2">
-        <v>120</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
-      </c>
-      <c r="AI2">
-        <v>90</v>
-      </c>
-      <c r="AJ2">
-        <v>15</v>
-      </c>
-      <c r="AK2">
-        <v>15</v>
-      </c>
-      <c r="AL2">
-        <v>30</v>
-      </c>
-      <c r="AM2">
-        <v>100</v>
-      </c>
-      <c r="AN2">
-        <v>4.3</v>
-      </c>
-      <c r="AO2">
-        <v>100</v>
-      </c>
-      <c r="AP2">
-        <v>5.6</v>
-      </c>
-      <c r="AQ2">
-        <v>5.7</v>
-      </c>
-      <c r="AR2">
-        <v>6</v>
-      </c>
-      <c r="AS2">
-        <v>6.2</v>
-      </c>
-      <c r="AT2">
-        <v>4.5</v>
-      </c>
-      <c r="AU2">
-        <v>4.6</v>
-      </c>
-      <c r="AV2">
-        <v>5.4</v>
-      </c>
-      <c r="AW2">
-        <v>6</v>
-      </c>
-      <c r="AX2">
-        <v>4.4</v>
-      </c>
-      <c r="AY2">
-        <v>4.3</v>
-      </c>
-      <c r="AZ2">
-        <v>5.2</v>
-      </c>
-      <c r="BA2">
-        <v>6</v>
-      </c>
-      <c r="BB2">
-        <v>4.5</v>
-      </c>
-      <c r="BC2">
-        <v>4.5</v>
-      </c>
-      <c r="BD2">
-        <v>5.3</v>
-      </c>
-      <c r="BE2">
-        <v>6</v>
-      </c>
-      <c r="BF2">
-        <v>3.35</v>
-      </c>
       <c r="BG2">
-        <v>6</v>
+        <v>2.86</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1170,7 +1170,7 @@
         <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.07</v>
@@ -1185,7 +1185,7 @@
         <v>1.91</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>1.35</v>
@@ -1221,7 +1221,7 @@
         <v>7.8</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
         <v>28</v>
@@ -1245,7 +1245,7 @@
         <v>16.5</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL3">
         <v>42</v>
@@ -1257,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="AO3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP3">
         <v>12.5</v>
@@ -1269,7 +1269,7 @@
         <v>50</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1281,7 +1281,7 @@
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1293,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1311,13 +1311,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI3">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
@@ -1329,43 +1329,43 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN3">
         <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
         <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX3">
         <v>80</v>
       </c>
       <c r="BY3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ3">
         <v>30</v>
@@ -1394,19 +1394,19 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1418,16 +1418,16 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R4">
         <v>1.15</v>
@@ -1744,52 +1744,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1986,52 +1986,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -262,12 +262,21 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
     <t>Romanian Liga II</t>
   </si>
   <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
     <t>2026-08-05</t>
   </si>
   <si>
@@ -277,6 +286,9 @@
     <t>01:20:00</t>
   </si>
   <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -286,12 +298,30 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:15:00</t>
+  </si>
+  <si>
+    <t>23:25:00</t>
+  </si>
+  <si>
     <t>Guabira</t>
   </si>
   <si>
     <t>Millonarios</t>
   </si>
   <si>
+    <t>Hubei Istar</t>
+  </si>
+  <si>
+    <t>Lanzhou Longyuan Athletic</t>
+  </si>
+  <si>
     <t>ACS Dumbravita</t>
   </si>
   <si>
@@ -301,12 +331,30 @@
     <t>Hafnarfjordur</t>
   </si>
   <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Penarol</t>
+  </si>
+  <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
     <t>Deportivo Pasto</t>
   </si>
   <si>
+    <t>Jiangxi Lushan</t>
+  </si>
+  <si>
+    <t>Beijing Tech FC</t>
+  </si>
+  <si>
     <t>CSM Satu Mare</t>
   </si>
   <si>
@@ -316,7 +364,19 @@
     <t>KR Reykjavik</t>
   </si>
   <si>
-    <t>2026-08-03 22:27:01</t>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Wanderers (Uru)</t>
+  </si>
+  <si>
+    <t>Jaguares de Cordoba</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>2026-08-04 00:34:08</t>
   </si>
 </sst>
 </file>
@@ -648,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -898,97 +958,97 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2">
+        <v>1.38</v>
+      </c>
+      <c r="G2">
+        <v>1.48</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
+      </c>
+      <c r="J2">
+        <v>5.4</v>
+      </c>
+      <c r="K2">
+        <v>6.6</v>
+      </c>
+      <c r="L2">
+        <v>1.18</v>
+      </c>
+      <c r="M2">
+        <v>1.02</v>
+      </c>
+      <c r="N2">
+        <v>6.6</v>
+      </c>
+      <c r="O2">
+        <v>1.12</v>
+      </c>
+      <c r="P2">
+        <v>3.25</v>
+      </c>
+      <c r="Q2">
+        <v>1.37</v>
+      </c>
+      <c r="R2">
+        <v>1.88</v>
+      </c>
+      <c r="S2">
+        <v>1.9</v>
+      </c>
+      <c r="T2">
+        <v>1.6</v>
+      </c>
+      <c r="U2">
+        <v>2.32</v>
+      </c>
+      <c r="V2">
+        <v>1.13</v>
+      </c>
+      <c r="W2">
+        <v>3.05</v>
+      </c>
+      <c r="X2">
+        <v>48</v>
+      </c>
+      <c r="Y2">
+        <v>44</v>
+      </c>
+      <c r="Z2">
+        <v>80</v>
+      </c>
+      <c r="AA2">
+        <v>220</v>
+      </c>
+      <c r="AB2">
+        <v>16.5</v>
+      </c>
+      <c r="AC2">
+        <v>16</v>
+      </c>
+      <c r="AD2">
+        <v>34</v>
+      </c>
+      <c r="AE2">
         <v>90</v>
       </c>
-      <c r="E2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2">
-        <v>1.44</v>
-      </c>
-      <c r="G2">
-        <v>1.57</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7.6</v>
-      </c>
-      <c r="J2">
-        <v>4.8</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>1.21</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>6.2</v>
-      </c>
-      <c r="O2">
-        <v>1.14</v>
-      </c>
-      <c r="P2">
-        <v>2.86</v>
-      </c>
-      <c r="Q2">
-        <v>1.42</v>
-      </c>
-      <c r="R2">
-        <v>1.77</v>
-      </c>
-      <c r="S2">
-        <v>2.04</v>
-      </c>
-      <c r="T2">
-        <v>1.62</v>
-      </c>
-      <c r="U2">
-        <v>2.3</v>
-      </c>
-      <c r="V2">
-        <v>1.15</v>
-      </c>
-      <c r="W2">
-        <v>2.78</v>
-      </c>
-      <c r="X2">
-        <v>36</v>
-      </c>
-      <c r="Y2">
-        <v>38</v>
-      </c>
-      <c r="Z2">
-        <v>70</v>
-      </c>
-      <c r="AA2">
-        <v>190</v>
-      </c>
-      <c r="AB2">
-        <v>16</v>
-      </c>
-      <c r="AC2">
-        <v>14</v>
-      </c>
-      <c r="AD2">
-        <v>29</v>
-      </c>
-      <c r="AE2">
-        <v>80</v>
-      </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1003,73 +1063,73 @@
         <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM2">
         <v>75</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AO2">
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="AR2">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>2.94</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
-        <v>2.52</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>2.46</v>
+        <v>12</v>
       </c>
       <c r="AV2">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW2">
-        <v>2.88</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>2.44</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC2">
-        <v>2.54</v>
+        <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>2.7</v>
+        <v>20</v>
       </c>
       <c r="BE2">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BF2">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="BG2">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1132,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1140,22 +1200,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -1167,7 +1227,7 @@
         <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1185,7 +1245,7 @@
         <v>1.91</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
         <v>1.35</v>
@@ -1221,7 +1281,7 @@
         <v>7.8</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>28</v>
@@ -1242,10 +1302,10 @@
         <v>150</v>
       </c>
       <c r="AJ3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
         <v>42</v>
@@ -1269,7 +1329,7 @@
         <v>50</v>
       </c>
       <c r="AS3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1281,7 +1341,7 @@
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1293,7 +1353,7 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1305,7 +1365,7 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF3">
         <v>8.199999999999999</v>
@@ -1314,10 +1374,10 @@
         <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
@@ -1329,7 +1389,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN3">
         <v>4.7</v>
@@ -1338,43 +1398,43 @@
         <v>3.6</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT3">
         <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BX3">
         <v>80</v>
       </c>
       <c r="BY3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ3">
         <v>30</v>
       </c>
       <c r="CA3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1382,31 +1442,31 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1418,22 +1478,22 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1442,10 +1502,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1610,72 +1670,72 @@
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1852,13 +1912,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1866,34 +1926,34 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1902,22 +1962,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O6">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q6">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -1926,10 +1986,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2100,7 +2160,1459 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.02</v>
+      </c>
+      <c r="N7">
+        <v>1.25</v>
+      </c>
+      <c r="O7">
+        <v>1.07</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.07</v>
+      </c>
+      <c r="R7">
+        <v>1.25</v>
+      </c>
+      <c r="S7">
+        <v>1.06</v>
+      </c>
+      <c r="T7">
+        <v>1.11</v>
+      </c>
+      <c r="U7">
+        <v>1.11</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.04</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.04</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.04</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.04</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.04</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.04</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.04</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.26</v>
+      </c>
+      <c r="O8">
+        <v>1.03</v>
+      </c>
+      <c r="P8">
+        <v>1.25</v>
+      </c>
+      <c r="Q8">
+        <v>1.03</v>
+      </c>
+      <c r="R8">
+        <v>1.25</v>
+      </c>
+      <c r="S8">
+        <v>1.05</v>
+      </c>
+      <c r="T8">
+        <v>1.11</v>
+      </c>
+      <c r="U8">
+        <v>1.11</v>
+      </c>
+      <c r="V8">
+        <v>1.01</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8">
+        <v>1.01</v>
+      </c>
+      <c r="AR8">
+        <v>1.01</v>
+      </c>
+      <c r="AS8">
+        <v>1.01</v>
+      </c>
+      <c r="AT8">
+        <v>1.01</v>
+      </c>
+      <c r="AU8">
+        <v>1.01</v>
+      </c>
+      <c r="AV8">
+        <v>1.01</v>
+      </c>
+      <c r="AW8">
+        <v>1.01</v>
+      </c>
+      <c r="AX8">
+        <v>1.01</v>
+      </c>
+      <c r="AY8">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8">
+        <v>1.01</v>
+      </c>
+      <c r="BA8">
+        <v>1.01</v>
+      </c>
+      <c r="BB8">
+        <v>1.01</v>
+      </c>
+      <c r="BC8">
+        <v>1.01</v>
+      </c>
+      <c r="BD8">
+        <v>1.01</v>
+      </c>
+      <c r="BE8">
+        <v>1.01</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.04</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.04</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.04</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.04</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.04</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.04</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.04</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9">
+        <v>2.14</v>
+      </c>
+      <c r="G9">
+        <v>2.26</v>
+      </c>
+      <c r="H9">
+        <v>4.2</v>
+      </c>
+      <c r="I9">
+        <v>4.7</v>
+      </c>
+      <c r="J9">
+        <v>2.96</v>
+      </c>
+      <c r="K9">
+        <v>3.2</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.14</v>
+      </c>
+      <c r="N9">
+        <v>2.44</v>
+      </c>
+      <c r="O9">
+        <v>1.6</v>
+      </c>
+      <c r="P9">
+        <v>1.47</v>
+      </c>
+      <c r="Q9">
+        <v>2.78</v>
+      </c>
+      <c r="R9">
+        <v>1.17</v>
+      </c>
+      <c r="S9">
+        <v>5.9</v>
+      </c>
+      <c r="T9">
+        <v>2.28</v>
+      </c>
+      <c r="U9">
+        <v>1.66</v>
+      </c>
+      <c r="V9">
+        <v>1.27</v>
+      </c>
+      <c r="W9">
+        <v>1.79</v>
+      </c>
+      <c r="X9">
+        <v>9</v>
+      </c>
+      <c r="Y9">
+        <v>11.5</v>
+      </c>
+      <c r="Z9">
+        <v>36</v>
+      </c>
+      <c r="AA9">
+        <v>140</v>
+      </c>
+      <c r="AB9">
+        <v>7</v>
+      </c>
+      <c r="AC9">
+        <v>7.6</v>
+      </c>
+      <c r="AD9">
+        <v>23</v>
+      </c>
+      <c r="AE9">
         <v>100</v>
+      </c>
+      <c r="AF9">
+        <v>13.5</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>32</v>
+      </c>
+      <c r="AI9">
+        <v>130</v>
+      </c>
+      <c r="AJ9">
+        <v>36</v>
+      </c>
+      <c r="AK9">
+        <v>38</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9">
+        <v>280</v>
+      </c>
+      <c r="AN9">
+        <v>40</v>
+      </c>
+      <c r="AO9">
+        <v>170</v>
+      </c>
+      <c r="AP9">
+        <v>7</v>
+      </c>
+      <c r="AQ9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR9">
+        <v>5.7</v>
+      </c>
+      <c r="AS9">
+        <v>6.4</v>
+      </c>
+      <c r="AT9">
+        <v>5.7</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>16.5</v>
+      </c>
+      <c r="AW9">
+        <v>6.2</v>
+      </c>
+      <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9">
+        <v>5.6</v>
+      </c>
+      <c r="BA9">
+        <v>6.4</v>
+      </c>
+      <c r="BB9">
+        <v>5.7</v>
+      </c>
+      <c r="BC9">
+        <v>5.7</v>
+      </c>
+      <c r="BD9">
+        <v>6.2</v>
+      </c>
+      <c r="BE9">
+        <v>6.6</v>
+      </c>
+      <c r="BF9">
+        <v>5.8</v>
+      </c>
+      <c r="BG9">
+        <v>6.4</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10">
+        <v>1.04</v>
+      </c>
+      <c r="G10">
+        <v>990</v>
+      </c>
+      <c r="H10">
+        <v>1.04</v>
+      </c>
+      <c r="I10">
+        <v>990</v>
+      </c>
+      <c r="J10">
+        <v>1.09</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.26</v>
+      </c>
+      <c r="O10">
+        <v>1.02</v>
+      </c>
+      <c r="P10">
+        <v>1.25</v>
+      </c>
+      <c r="Q10">
+        <v>1.39</v>
+      </c>
+      <c r="R10">
+        <v>1.14</v>
+      </c>
+      <c r="S10">
+        <v>1.39</v>
+      </c>
+      <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11">
+        <v>1.36</v>
+      </c>
+      <c r="G11">
+        <v>1.94</v>
+      </c>
+      <c r="H11">
+        <v>4.8</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>3.15</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1.26</v>
+      </c>
+      <c r="O11">
+        <v>1.37</v>
+      </c>
+      <c r="P11">
+        <v>1.25</v>
+      </c>
+      <c r="Q11">
+        <v>1.37</v>
+      </c>
+      <c r="R11">
+        <v>1.13</v>
+      </c>
+      <c r="S11">
+        <v>1.38</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.11</v>
+      </c>
+      <c r="V11">
+        <v>1.01</v>
+      </c>
+      <c r="W11">
+        <v>2.06</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>1.01</v>
+      </c>
+      <c r="AV11">
+        <v>1.01</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12">
+        <v>3.7</v>
+      </c>
+      <c r="G12">
+        <v>5.1</v>
+      </c>
+      <c r="H12">
+        <v>1.96</v>
+      </c>
+      <c r="I12">
+        <v>2.2</v>
+      </c>
+      <c r="J12">
+        <v>3.1</v>
+      </c>
+      <c r="K12">
+        <v>3.6</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>2.5</v>
+      </c>
+      <c r="O12">
+        <v>1.44</v>
+      </c>
+      <c r="P12">
+        <v>1.59</v>
+      </c>
+      <c r="Q12">
+        <v>2.3</v>
+      </c>
+      <c r="R12">
+        <v>1.22</v>
+      </c>
+      <c r="S12">
+        <v>4.1</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>1.79</v>
+      </c>
+      <c r="V12">
+        <v>1.83</v>
+      </c>
+      <c r="W12">
+        <v>1.24</v>
+      </c>
+      <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
+        <v>7.6</v>
+      </c>
+      <c r="Z12">
+        <v>12.5</v>
+      </c>
+      <c r="AA12">
+        <v>38</v>
+      </c>
+      <c r="AB12">
+        <v>13.5</v>
+      </c>
+      <c r="AC12">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
+        <v>38</v>
+      </c>
+      <c r="AF12">
+        <v>48</v>
+      </c>
+      <c r="AG12">
+        <v>20</v>
+      </c>
+      <c r="AH12">
+        <v>24</v>
+      </c>
+      <c r="AI12">
+        <v>75</v>
+      </c>
+      <c r="AJ12">
+        <v>150</v>
+      </c>
+      <c r="AK12">
+        <v>85</v>
+      </c>
+      <c r="AL12">
+        <v>110</v>
+      </c>
+      <c r="AM12">
+        <v>200</v>
+      </c>
+      <c r="AN12">
+        <v>140</v>
+      </c>
+      <c r="AO12">
+        <v>28</v>
+      </c>
+      <c r="AP12">
+        <v>4.6</v>
+      </c>
+      <c r="AQ12">
+        <v>5.4</v>
+      </c>
+      <c r="AR12">
+        <v>4.9</v>
+      </c>
+      <c r="AS12">
+        <v>6.2</v>
+      </c>
+      <c r="AT12">
+        <v>5.1</v>
+      </c>
+      <c r="AU12">
+        <v>5.8</v>
+      </c>
+      <c r="AV12">
+        <v>4.8</v>
+      </c>
+      <c r="AW12">
+        <v>6.2</v>
+      </c>
+      <c r="AX12">
+        <v>6.6</v>
+      </c>
+      <c r="AY12">
+        <v>5.8</v>
+      </c>
+      <c r="AZ12">
+        <v>6</v>
+      </c>
+      <c r="BA12">
+        <v>7.2</v>
+      </c>
+      <c r="BB12">
+        <v>7.8</v>
+      </c>
+      <c r="BC12">
+        <v>7.4</v>
+      </c>
+      <c r="BD12">
+        <v>7.6</v>
+      </c>
+      <c r="BE12">
+        <v>7.8</v>
+      </c>
+      <c r="BF12">
+        <v>7.8</v>
+      </c>
+      <c r="BG12">
+        <v>6.2</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.73</v>
+      </c>
+      <c r="BJ12">
+        <v>16</v>
+      </c>
+      <c r="BK12">
+        <v>1.56</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.73</v>
+      </c>
+      <c r="BN12">
+        <v>11</v>
+      </c>
+      <c r="BO12">
+        <v>1.5</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.69</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.7</v>
+      </c>
+      <c r="BT12">
+        <v>6.2</v>
+      </c>
+      <c r="BU12">
+        <v>1.35</v>
+      </c>
+      <c r="BV12">
+        <v>23</v>
+      </c>
+      <c r="BW12">
+        <v>1.61</v>
+      </c>
+      <c r="BX12">
+        <v>50</v>
+      </c>
+      <c r="BY12">
+        <v>1.68</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.68</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>01:20:00</t>
   </si>
   <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
     <t>11:30:00</t>
   </si>
   <si>
@@ -316,6 +319,12 @@
     <t>Millonarios</t>
   </si>
   <si>
+    <t>Shanghai Port B</t>
+  </si>
+  <si>
+    <t>Wenzhou Professional</t>
+  </si>
+  <si>
     <t>Hubei Istar</t>
   </si>
   <si>
@@ -349,6 +358,12 @@
     <t>Deportivo Pasto</t>
   </si>
   <si>
+    <t>Xian Chongde Ronghai</t>
+  </si>
+  <si>
+    <t>Guizhou Zhucheng Athletic</t>
+  </si>
+  <si>
     <t>Jiangxi Lushan</t>
   </si>
   <si>
@@ -376,7 +391,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 00:34:08</t>
+    <t>2026-08-04 02:41:30</t>
   </si>
 </sst>
 </file>
@@ -708,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -964,172 +979,172 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>1.38</v>
       </c>
       <c r="G2">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>8.6</v>
       </c>
       <c r="J2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L2">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S2">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="T2">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U2">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
         <v>1.13</v>
       </c>
       <c r="W2">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="X2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Y2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Z2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA2">
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD2">
         <v>34</v>
       </c>
       <c r="AE2">
+        <v>95</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>24</v>
+      </c>
+      <c r="AI2">
+        <v>75</v>
+      </c>
+      <c r="AJ2">
+        <v>15</v>
+      </c>
+      <c r="AK2">
+        <v>15.5</v>
+      </c>
+      <c r="AL2">
+        <v>29</v>
+      </c>
+      <c r="AM2">
         <v>90</v>
       </c>
-      <c r="AF2">
-        <v>15.5</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>70</v>
-      </c>
-      <c r="AJ2">
-        <v>15.5</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>28</v>
-      </c>
-      <c r="AM2">
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
         <v>75</v>
       </c>
-      <c r="AN2">
-        <v>4.3</v>
-      </c>
-      <c r="AO2">
-        <v>70</v>
-      </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>2.12</v>
       </c>
       <c r="AQ2">
-        <v>6</v>
+        <v>2.76</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>1.97</v>
       </c>
       <c r="AU2">
-        <v>12</v>
+        <v>1.94</v>
       </c>
       <c r="AV2">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>2.16</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>1.94</v>
       </c>
       <c r="BC2">
-        <v>11.5</v>
+        <v>1.94</v>
       </c>
       <c r="BD2">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="BE2">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="BF2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BG2">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1192,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1206,124 +1221,124 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F3">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
         <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="X3">
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AP3">
         <v>12.5</v>
       </c>
       <c r="AQ3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AR3">
         <v>50</v>
@@ -1335,16 +1350,16 @@
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV3">
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
         <v>8.800000000000001</v>
@@ -1353,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC3">
         <v>15</v>
@@ -1374,67 +1389,67 @@
         <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX3">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BY3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BZ3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1448,10 +1463,10 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F4">
         <v>1.04</v>
@@ -1463,10 +1478,10 @@
         <v>1.04</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1496,10 +1511,10 @@
         <v>1.45</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1562,52 +1577,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1619,55 +1634,55 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1676,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1687,28 +1702,28 @@
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.04</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H5">
         <v>1.04</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1720,28 +1735,28 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
         <v>1.01</v>
@@ -1804,52 +1819,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1861,55 +1876,55 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1918,12 +1933,12 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>87</v>
@@ -1932,25 +1947,25 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1962,22 +1977,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="R6">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -1986,10 +2001,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2154,72 +2169,72 @@
         <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
         <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2396,48 +2411,48 @@
         <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2446,22 +2461,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="O8">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q8">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2473,7 +2488,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2644,186 +2659,186 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>2.78</v>
+        <v>1.07</v>
       </c>
       <c r="R9">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S9">
-        <v>5.9</v>
+        <v>1.06</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2886,42 +2901,42 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2933,19 +2948,19 @@
         <v>1.26</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P10">
         <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="R10">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3122,192 +3137,192 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F11">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
+        <v>4.5</v>
+      </c>
+      <c r="J11">
+        <v>2.98</v>
+      </c>
+      <c r="K11">
+        <v>3.2</v>
+      </c>
+      <c r="L11">
+        <v>1.55</v>
+      </c>
+      <c r="M11">
+        <v>1.14</v>
+      </c>
+      <c r="N11">
+        <v>2.44</v>
+      </c>
+      <c r="O11">
+        <v>1.6</v>
+      </c>
+      <c r="P11">
+        <v>1.47</v>
+      </c>
+      <c r="Q11">
+        <v>2.8</v>
+      </c>
+      <c r="R11">
+        <v>1.17</v>
+      </c>
+      <c r="S11">
+        <v>6</v>
+      </c>
+      <c r="T11">
+        <v>2.28</v>
+      </c>
+      <c r="U11">
+        <v>1.66</v>
+      </c>
+      <c r="V11">
+        <v>1.28</v>
+      </c>
+      <c r="W11">
+        <v>1.75</v>
+      </c>
+      <c r="X11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y11">
+        <v>11.5</v>
+      </c>
+      <c r="Z11">
+        <v>36</v>
+      </c>
+      <c r="AA11">
+        <v>140</v>
+      </c>
+      <c r="AB11">
+        <v>7</v>
+      </c>
+      <c r="AC11">
+        <v>7.6</v>
+      </c>
+      <c r="AD11">
+        <v>23</v>
+      </c>
+      <c r="AE11">
         <v>100</v>
       </c>
-      <c r="J11">
-        <v>3.15</v>
-      </c>
-      <c r="K11">
-        <v>950</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.26</v>
-      </c>
-      <c r="O11">
-        <v>1.37</v>
-      </c>
-      <c r="P11">
-        <v>1.25</v>
-      </c>
-      <c r="Q11">
-        <v>1.37</v>
-      </c>
-      <c r="R11">
-        <v>1.13</v>
-      </c>
-      <c r="S11">
-        <v>1.38</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
-      <c r="W11">
-        <v>2.06</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3370,249 +3385,733 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
       </c>
       <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>1.08</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.08</v>
+      </c>
+      <c r="I12">
+        <v>990</v>
+      </c>
+      <c r="J12">
+        <v>1.15</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.26</v>
+      </c>
+      <c r="O12">
+        <v>1.02</v>
+      </c>
+      <c r="P12">
+        <v>1.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.39</v>
+      </c>
+      <c r="R12">
+        <v>1.14</v>
+      </c>
+      <c r="S12">
+        <v>1.39</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.04</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.04</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.04</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.04</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.04</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.04</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
         <v>97</v>
       </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12">
-        <v>3.7</v>
-      </c>
-      <c r="G12">
-        <v>5.1</v>
-      </c>
-      <c r="H12">
-        <v>1.96</v>
-      </c>
-      <c r="I12">
-        <v>2.2</v>
-      </c>
-      <c r="J12">
-        <v>3.1</v>
-      </c>
-      <c r="K12">
-        <v>3.6</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>2.5</v>
-      </c>
-      <c r="O12">
-        <v>1.44</v>
-      </c>
-      <c r="P12">
-        <v>1.59</v>
-      </c>
-      <c r="Q12">
-        <v>2.3</v>
-      </c>
-      <c r="R12">
-        <v>1.22</v>
-      </c>
-      <c r="S12">
-        <v>4.1</v>
-      </c>
-      <c r="T12">
-        <v>2</v>
-      </c>
-      <c r="U12">
-        <v>1.79</v>
-      </c>
-      <c r="V12">
-        <v>1.83</v>
-      </c>
-      <c r="W12">
-        <v>1.24</v>
-      </c>
-      <c r="X12">
-        <v>10.5</v>
-      </c>
-      <c r="Y12">
-        <v>7.6</v>
-      </c>
-      <c r="Z12">
-        <v>12.5</v>
-      </c>
-      <c r="AA12">
-        <v>38</v>
-      </c>
-      <c r="AB12">
-        <v>13.5</v>
-      </c>
-      <c r="AC12">
-        <v>8</v>
-      </c>
-      <c r="AD12">
-        <v>11.5</v>
-      </c>
-      <c r="AE12">
-        <v>38</v>
-      </c>
-      <c r="AF12">
-        <v>48</v>
-      </c>
-      <c r="AG12">
-        <v>20</v>
-      </c>
-      <c r="AH12">
-        <v>24</v>
-      </c>
-      <c r="AI12">
-        <v>75</v>
-      </c>
-      <c r="AJ12">
-        <v>150</v>
-      </c>
-      <c r="AK12">
-        <v>85</v>
-      </c>
-      <c r="AL12">
+      <c r="D13" t="s">
         <v>110</v>
       </c>
-      <c r="AM12">
-        <v>200</v>
-      </c>
-      <c r="AN12">
-        <v>140</v>
-      </c>
-      <c r="AO12">
-        <v>28</v>
-      </c>
-      <c r="AP12">
-        <v>4.6</v>
-      </c>
-      <c r="AQ12">
-        <v>5.4</v>
-      </c>
-      <c r="AR12">
-        <v>4.9</v>
-      </c>
-      <c r="AS12">
-        <v>6.2</v>
-      </c>
-      <c r="AT12">
-        <v>5.1</v>
-      </c>
-      <c r="AU12">
-        <v>5.8</v>
-      </c>
-      <c r="AV12">
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>1.36</v>
+      </c>
+      <c r="G13">
+        <v>1.94</v>
+      </c>
+      <c r="H13">
         <v>4.8</v>
       </c>
-      <c r="AW12">
-        <v>6.2</v>
-      </c>
-      <c r="AX12">
-        <v>6.6</v>
-      </c>
-      <c r="AY12">
-        <v>5.8</v>
-      </c>
-      <c r="AZ12">
-        <v>6</v>
-      </c>
-      <c r="BA12">
-        <v>7.2</v>
-      </c>
-      <c r="BB12">
-        <v>7.8</v>
-      </c>
-      <c r="BC12">
-        <v>7.4</v>
-      </c>
-      <c r="BD12">
-        <v>7.6</v>
-      </c>
-      <c r="BE12">
-        <v>7.8</v>
-      </c>
-      <c r="BF12">
-        <v>7.8</v>
-      </c>
-      <c r="BG12">
-        <v>6.2</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.73</v>
-      </c>
-      <c r="BJ12">
-        <v>16</v>
-      </c>
-      <c r="BK12">
-        <v>1.56</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.73</v>
-      </c>
-      <c r="BN12">
-        <v>11</v>
-      </c>
-      <c r="BO12">
-        <v>1.5</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.69</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.7</v>
-      </c>
-      <c r="BT12">
-        <v>6.2</v>
-      </c>
-      <c r="BU12">
-        <v>1.35</v>
-      </c>
-      <c r="BV12">
-        <v>23</v>
-      </c>
-      <c r="BW12">
-        <v>1.61</v>
-      </c>
-      <c r="BX12">
-        <v>50</v>
-      </c>
-      <c r="BY12">
-        <v>1.68</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.68</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>120</v>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <v>3.15</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.26</v>
+      </c>
+      <c r="O13">
+        <v>1.37</v>
+      </c>
+      <c r="P13">
+        <v>1.25</v>
+      </c>
+      <c r="Q13">
+        <v>1.37</v>
+      </c>
+      <c r="R13">
+        <v>1.13</v>
+      </c>
+      <c r="S13">
+        <v>1.38</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.01</v>
+      </c>
+      <c r="W13">
+        <v>2.06</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.64</v>
+      </c>
+      <c r="G14">
+        <v>990</v>
+      </c>
+      <c r="H14">
+        <v>1.72</v>
+      </c>
+      <c r="I14">
+        <v>990</v>
+      </c>
+      <c r="J14">
+        <v>1.14</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>1.33</v>
+      </c>
+      <c r="O14">
+        <v>1.41</v>
+      </c>
+      <c r="P14">
+        <v>1.33</v>
+      </c>
+      <c r="Q14">
+        <v>1.94</v>
+      </c>
+      <c r="R14">
+        <v>1.14</v>
+      </c>
+      <c r="S14">
+        <v>3.35</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.04</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.04</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.04</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.04</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -391,7 +391,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 02:41:30</t>
+    <t>2026-08-04 04:48:38</t>
   </si>
 </sst>
 </file>
@@ -985,19 +985,19 @@
         <v>112</v>
       </c>
       <c r="F2">
+        <v>1.37</v>
+      </c>
+      <c r="G2">
         <v>1.38</v>
       </c>
-      <c r="G2">
-        <v>1.42</v>
-      </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K2">
         <v>6.8</v>
@@ -1015,34 +1015,34 @@
         <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="T2">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="X2">
+        <v>42</v>
+      </c>
+      <c r="Y2">
         <v>44</v>
-      </c>
-      <c r="Y2">
-        <v>46</v>
       </c>
       <c r="Z2">
         <v>85</v>
@@ -1051,10 +1051,10 @@
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD2">
         <v>34</v>
@@ -1063,10 +1063,10 @@
         <v>95</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1075,130 +1075,130 @@
         <v>75</v>
       </c>
       <c r="AJ2">
+        <v>14.5</v>
+      </c>
+      <c r="AK2">
         <v>15</v>
       </c>
-      <c r="AK2">
-        <v>15.5</v>
-      </c>
       <c r="AL2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM2">
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>4.7</v>
       </c>
       <c r="AO2">
         <v>75</v>
       </c>
       <c r="AP2">
-        <v>2.12</v>
+        <v>5.8</v>
       </c>
       <c r="AQ2">
-        <v>2.76</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>2.16</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
-        <v>1.97</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>1.94</v>
+        <v>12</v>
       </c>
       <c r="AV2">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW2">
-        <v>2.16</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>1.94</v>
+        <v>11.5</v>
       </c>
       <c r="BC2">
-        <v>1.94</v>
+        <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>2.06</v>
+        <v>20</v>
       </c>
       <c r="BE2">
-        <v>2.16</v>
+        <v>6.2</v>
       </c>
       <c r="BF2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG2">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1227,70 +1227,70 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G3">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H3">
         <v>7.8</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.41</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
         <v>1.36</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
         <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W3">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="X3">
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA3">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
@@ -1302,7 +1302,7 @@
         <v>32</v>
       </c>
       <c r="AE3">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AF3">
         <v>8.6</v>
@@ -1311,10 +1311,10 @@
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ3">
         <v>14</v>
@@ -1332,7 +1332,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AP3">
         <v>12.5</v>
@@ -1344,19 +1344,19 @@
         <v>50</v>
       </c>
       <c r="AS3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3">
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX3">
         <v>7.4</v>
@@ -1368,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC3">
         <v>15</v>
@@ -1380,13 +1380,13 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1398,16 +1398,16 @@
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BO3">
         <v>3.45</v>
@@ -1416,13 +1416,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT3">
         <v>13</v>
@@ -1431,22 +1431,22 @@
         <v>9.4</v>
       </c>
       <c r="BV3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BW3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BY3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3">
         <v>19</v>
       </c>
       <c r="CA3">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1472,16 +1472,16 @@
         <v>1.04</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H4">
         <v>1.04</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1493,10 +1493,10 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.26</v>
+        <v>2.78</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1508,13 +1508,13 @@
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1577,52 +1577,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1634,55 +1634,55 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1714,16 +1714,16 @@
         <v>1.04</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H5">
         <v>1.04</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1735,28 +1735,28 @@
         <v>1.01</v>
       </c>
       <c r="N5">
+        <v>2.24</v>
+      </c>
+      <c r="O5">
+        <v>1.02</v>
+      </c>
+      <c r="P5">
         <v>1.26</v>
       </c>
-      <c r="O5">
-        <v>1.01</v>
-      </c>
-      <c r="P5">
-        <v>1.25</v>
-      </c>
       <c r="Q5">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
         <v>1.01</v>
@@ -1819,52 +1819,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1876,55 +1876,55 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1956,7 +1956,7 @@
         <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H6">
         <v>1.04</v>
@@ -1965,7 +1965,7 @@
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1977,7 +1977,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>2.84</v>
       </c>
       <c r="O6">
         <v>1.02</v>
@@ -2207,7 +2207,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2219,13 +2219,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O7">
         <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q7">
         <v>1.34</v>
@@ -2234,7 +2234,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2443,7 +2443,7 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I8">
         <v>990</v>
@@ -2951,7 +2951,7 @@
         <v>1.03</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q10">
         <v>1.03</v>
@@ -3163,19 +3163,19 @@
         <v>121</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
         <v>4.2</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
         <v>3.2</v>
@@ -3214,7 +3214,7 @@
         <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="X11">
         <v>8.800000000000001</v>
@@ -3229,7 +3229,7 @@
         <v>140</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
@@ -3277,10 +3277,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT11">
         <v>5.7</v>
@@ -3292,7 +3292,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX11">
         <v>10</v>
@@ -3301,88 +3301,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC11">
         <v>6</v>
       </c>
       <c r="BD11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF11">
+        <v>6.2</v>
+      </c>
+      <c r="BG11">
+        <v>7</v>
+      </c>
+      <c r="BH11">
+        <v>2.66</v>
+      </c>
+      <c r="BI11">
+        <v>2.2</v>
+      </c>
+      <c r="BJ11">
+        <v>12.5</v>
+      </c>
+      <c r="BK11">
         <v>6</v>
       </c>
-      <c r="BG11">
-        <v>6.8</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="s">
         <v>125</v>
@@ -3405,19 +3405,19 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3662,7 +3662,7 @@
         <v>3.15</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3889,22 +3889,22 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.64</v>
+        <v>3.75</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>5.1</v>
       </c>
       <c r="H14">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>2.2</v>
       </c>
       <c r="J14">
-        <v>1.14</v>
+        <v>3.15</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3913,16 +3913,16 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="O14">
         <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="R14">
         <v>1.14</v>
@@ -3937,10 +3937,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="X14">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -391,7 +391,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 04:48:38</t>
+    <t>2026-08-04 06:55:09</t>
   </si>
 </sst>
 </file>
@@ -985,22 +985,22 @@
         <v>112</v>
       </c>
       <c r="F2">
+        <v>1.35</v>
+      </c>
+      <c r="G2">
         <v>1.37</v>
       </c>
-      <c r="G2">
-        <v>1.38</v>
-      </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>1.22</v>
@@ -1009,7 +1009,7 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O2">
         <v>1.13</v>
@@ -1027,10 +1027,10 @@
         <v>1.98</v>
       </c>
       <c r="T2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.12</v>
@@ -1045,34 +1045,34 @@
         <v>44</v>
       </c>
       <c r="Z2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD2">
         <v>34</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>13</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>14.5</v>
@@ -1081,55 +1081,55 @@
         <v>15</v>
       </c>
       <c r="AL2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
         <v>11.5</v>
       </c>
-      <c r="AU2">
-        <v>12</v>
-      </c>
       <c r="AV2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
@@ -1138,13 +1138,13 @@
         <v>20</v>
       </c>
       <c r="BE2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
         <v>3.55</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>6</v>
@@ -1153,16 +1153,16 @@
         <v>4.2</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
         <v>5</v>
@@ -1171,34 +1171,34 @@
         <v>3.8</v>
       </c>
       <c r="BP2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BS2">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BU2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BV2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>1.52</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>4.4</v>
@@ -1245,7 +1245,7 @@
         <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1260,7 +1260,7 @@
         <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
         <v>1.36</v>
@@ -1272,10 +1272,10 @@
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3">
         <v>2.92</v>
@@ -1290,7 +1290,7 @@
         <v>75</v>
       </c>
       <c r="AA3">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
@@ -1302,22 +1302,22 @@
         <v>32</v>
       </c>
       <c r="AE3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI3">
         <v>140</v>
       </c>
       <c r="AJ3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AK3">
         <v>17.5</v>
@@ -1344,7 +1344,7 @@
         <v>50</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1353,10 +1353,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX3">
         <v>7.4</v>
@@ -1365,10 +1365,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1380,13 +1380,13 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
         <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1398,13 +1398,13 @@
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BN3">
         <v>3.85</v>
@@ -1416,37 +1416,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BT3">
         <v>13</v>
       </c>
       <c r="BU3">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
         <v>100</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX3">
         <v>100</v>
       </c>
       <c r="BY3">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CA3">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1469,19 +1469,19 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1493,7 +1493,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
         <v>1.02</v>
@@ -1717,16 +1717,16 @@
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I5">
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1735,16 +1735,16 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.24</v>
+        <v>1.28</v>
       </c>
       <c r="O5">
         <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1953,19 +1953,19 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2195,19 +2195,19 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2219,13 +2219,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
         <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
         <v>1.34</v>
@@ -2234,7 +2234,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2243,10 +2243,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2443,7 +2443,7 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I8">
         <v>990</v>
@@ -2461,22 +2461,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Q8">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="R8">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2488,7 +2488,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2945,13 +2945,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
         <v>1.03</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
         <v>1.03</v>
@@ -3178,7 +3178,7 @@
         <v>3.05</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11">
         <v>1.55</v>
@@ -3265,7 +3265,7 @@
         <v>280</v>
       </c>
       <c r="AN11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO11">
         <v>170</v>
@@ -3280,7 +3280,7 @@
         <v>6</v>
       </c>
       <c r="AS11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT11">
         <v>5.7</v>
@@ -3304,19 +3304,19 @@
         <v>5.8</v>
       </c>
       <c r="BA11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB11">
         <v>6</v>
       </c>
       <c r="BC11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD11">
         <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF11">
         <v>6.2</v>
@@ -3405,19 +3405,19 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I12">
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3432,7 +3432,7 @@
         <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P12">
         <v>1.25</v>
@@ -3647,226 +3647,226 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="G13">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="H13">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
         <v>1.37</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q13">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="R13">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>3.75</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="s">
         <v>125</v>
@@ -3907,34 +3907,34 @@
         <v>3.55</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N14">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P14">
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="R14">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S14">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V14">
         <v>1.83</v>
@@ -3943,112 +3943,112 @@
         <v>1.24</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH14">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -391,7 +391,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 06:55:09</t>
+    <t>2026-08-04 09:01:53</t>
   </si>
 </sst>
 </file>
@@ -985,82 +985,82 @@
         <v>112</v>
       </c>
       <c r="F2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K2">
         <v>7</v>
       </c>
       <c r="L2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O2">
         <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="R2">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S2">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="X2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB2">
         <v>15</v>
       </c>
       <c r="AC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD2">
         <v>34</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2">
         <v>13</v>
@@ -1069,40 +1069,40 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL2">
         <v>27</v>
       </c>
       <c r="AM2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN2">
         <v>4.5</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AR2">
+        <v>6.4</v>
+      </c>
+      <c r="AS2">
         <v>6.8</v>
-      </c>
-      <c r="AS2">
-        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>11</v>
@@ -1111,94 +1111,94 @@
         <v>11.5</v>
       </c>
       <c r="AV2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
+        <v>19</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>3.5</v>
+      </c>
+      <c r="BG2">
+        <v>6.4</v>
+      </c>
+      <c r="BH2">
+        <v>5.9</v>
+      </c>
+      <c r="BI2">
+        <v>4.1</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>3.95</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5.6</v>
+      </c>
+      <c r="BN2">
+        <v>4.8</v>
+      </c>
+      <c r="BO2">
+        <v>3.55</v>
+      </c>
+      <c r="BP2">
+        <v>9</v>
+      </c>
+      <c r="BQ2">
+        <v>6</v>
+      </c>
+      <c r="BR2">
         <v>20</v>
       </c>
-      <c r="BE2">
-        <v>6.8</v>
-      </c>
-      <c r="BF2">
-        <v>3.55</v>
-      </c>
-      <c r="BG2">
-        <v>6.8</v>
-      </c>
-      <c r="BH2">
-        <v>6</v>
-      </c>
-      <c r="BI2">
-        <v>4.2</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
-      <c r="BK2">
-        <v>8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>6.6</v>
-      </c>
-      <c r="BN2">
-        <v>5</v>
-      </c>
-      <c r="BO2">
-        <v>3.8</v>
-      </c>
-      <c r="BP2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BQ2">
-        <v>6.4</v>
-      </c>
-      <c r="BR2">
-        <v>19</v>
-      </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BU2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV2">
         <v>65</v>
       </c>
       <c r="BW2">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>1.52</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>8.6</v>
@@ -1245,13 +1245,13 @@
         <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
         <v>1.33</v>
@@ -1260,19 +1260,19 @@
         <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
         <v>1.13</v>
@@ -1287,16 +1287,16 @@
         <v>25</v>
       </c>
       <c r="Z3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA3">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3">
         <v>32</v>
@@ -1305,7 +1305,7 @@
         <v>160</v>
       </c>
       <c r="AF3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
@@ -1314,16 +1314,16 @@
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
         <v>18</v>
       </c>
       <c r="AK3">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>190</v>
@@ -1335,16 +1335,16 @@
         <v>210</v>
       </c>
       <c r="AP3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1353,13 +1353,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
         <v>8.800000000000001</v>
@@ -1368,7 +1368,7 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1380,31 +1380,31 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
         <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI3">
         <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BN3">
         <v>3.85</v>
@@ -1413,40 +1413,40 @@
         <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BR3">
         <v>34</v>
       </c>
       <c r="BS3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BT3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1469,19 +1469,19 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1496,7 +1496,7 @@
         <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1717,16 +1717,16 @@
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>1.77</v>
       </c>
       <c r="J5">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1738,19 +1738,19 @@
         <v>1.28</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P5">
         <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1759,10 +1759,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1953,112 +1953,112 @@
         <v>116</v>
       </c>
       <c r="F6">
+        <v>2.84</v>
+      </c>
+      <c r="G6">
+        <v>3.6</v>
+      </c>
+      <c r="H6">
+        <v>2.46</v>
+      </c>
+      <c r="I6">
+        <v>2.74</v>
+      </c>
+      <c r="J6">
+        <v>2.86</v>
+      </c>
+      <c r="K6">
+        <v>3.95</v>
+      </c>
+      <c r="L6">
+        <v>1.4</v>
+      </c>
+      <c r="M6">
         <v>1.09</v>
       </c>
-      <c r="G6">
-        <v>990</v>
-      </c>
-      <c r="H6">
-        <v>1.09</v>
-      </c>
-      <c r="I6">
-        <v>990</v>
-      </c>
-      <c r="J6">
-        <v>1.17</v>
-      </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
       <c r="N6">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP6">
         <v>1.01</v>
@@ -2115,13 +2115,13 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
         <v>1.04</v>
@@ -2133,37 +2133,37 @@
         <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
         <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
         <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
         <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW6">
         <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6">
         <v>1.04</v>
@@ -2195,19 +2195,19 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2219,16 +2219,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
         <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2243,10 +2243,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2443,13 +2443,13 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2464,19 +2464,19 @@
         <v>1.57</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="R8">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2488,7 +2488,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3169,46 +3169,46 @@
         <v>2.24</v>
       </c>
       <c r="H11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
         <v>3.05</v>
       </c>
       <c r="K11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11">
         <v>1.55</v>
       </c>
       <c r="M11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O11">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P11">
         <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="R11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="U11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V11">
         <v>1.28</v>
@@ -3217,49 +3217,49 @@
         <v>1.81</v>
       </c>
       <c r="X11">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA11">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
         <v>13.5</v>
       </c>
-      <c r="AG11">
-        <v>13</v>
-      </c>
       <c r="AH11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
         <v>280</v>
@@ -3268,70 +3268,70 @@
         <v>38</v>
       </c>
       <c r="AO11">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
         <v>7</v>
       </c>
       <c r="AQ11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
+        <v>18</v>
+      </c>
+      <c r="AS11">
+        <v>38</v>
+      </c>
+      <c r="AT11">
         <v>6</v>
       </c>
-      <c r="AS11">
-        <v>7</v>
-      </c>
-      <c r="AT11">
-        <v>5.7</v>
-      </c>
       <c r="AU11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="AX11">
         <v>10</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BB11">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BC11">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BE11">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BG11">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BH11">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK11">
         <v>6</v>
@@ -3340,7 +3340,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
         <v>4.9</v>
@@ -3349,13 +3349,13 @@
         <v>3.75</v>
       </c>
       <c r="BP11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11">
         <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS11">
         <v>9.199999999999999</v>
@@ -3370,19 +3370,19 @@
         <v>50</v>
       </c>
       <c r="BW11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX11">
+        <v>80</v>
+      </c>
+      <c r="BY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ11">
+        <v>60</v>
+      </c>
+      <c r="CA11">
         <v>9.4</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>10</v>
-      </c>
-      <c r="BZ11">
-        <v>55</v>
-      </c>
-      <c r="CA11">
-        <v>9.6</v>
       </c>
       <c r="CB11" t="s">
         <v>125</v>
@@ -3405,19 +3405,19 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G12">
         <v>990</v>
       </c>
       <c r="H12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I12">
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3453,10 +3453,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3647,7 +3647,7 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G13">
         <v>1.69</v>
@@ -3656,7 +3656,7 @@
         <v>6.4</v>
       </c>
       <c r="I13">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>3.85</v>
@@ -3665,7 +3665,7 @@
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -3677,13 +3677,13 @@
         <v>1.37</v>
       </c>
       <c r="P13">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
         <v>2.08</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
         <v>3.75</v>
@@ -3701,7 +3701,7 @@
         <v>2.44</v>
       </c>
       <c r="X13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y13">
         <v>24</v>
@@ -3710,19 +3710,19 @@
         <v>70</v>
       </c>
       <c r="AA13">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB13">
         <v>7.4</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE13">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF13">
         <v>9.4</v>
@@ -3737,7 +3737,7 @@
         <v>140</v>
       </c>
       <c r="AJ13">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AK13">
         <v>24</v>
@@ -3752,19 +3752,19 @@
         <v>14.5</v>
       </c>
       <c r="AO13">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP13">
         <v>9.6</v>
       </c>
       <c r="AQ13">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS13">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT13">
         <v>6</v>
@@ -3776,7 +3776,7 @@
         <v>19.5</v>
       </c>
       <c r="AW13">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX13">
         <v>7.6</v>
@@ -3788,7 +3788,7 @@
         <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB13">
         <v>13.5</v>
@@ -3797,16 +3797,16 @@
         <v>16</v>
       </c>
       <c r="BD13">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE13">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF13">
         <v>8.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH13">
         <v>3.35</v>
@@ -3889,64 +3889,64 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H14">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="I14">
         <v>2.2</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K14">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="O14">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P14">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q14">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="R14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S14">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T14">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="V14">
         <v>1.83</v>
       </c>
       <c r="W14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X14">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z14">
         <v>14</v>
@@ -3964,151 +3964,151 @@
         <v>13.5</v>
       </c>
       <c r="AE14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG14">
         <v>24</v>
       </c>
       <c r="AH14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ14">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AK14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN14">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AO14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP14">
+        <v>3.3</v>
+      </c>
+      <c r="AQ14">
+        <v>3.1</v>
+      </c>
+      <c r="AR14">
+        <v>3.7</v>
+      </c>
+      <c r="AS14">
+        <v>4.3</v>
+      </c>
+      <c r="AT14">
+        <v>3.8</v>
+      </c>
+      <c r="AU14">
+        <v>5.8</v>
+      </c>
+      <c r="AV14">
+        <v>3.65</v>
+      </c>
+      <c r="AW14">
+        <v>4.3</v>
+      </c>
+      <c r="AX14">
+        <v>4.4</v>
+      </c>
+      <c r="AY14">
+        <v>4.1</v>
+      </c>
+      <c r="AZ14">
+        <v>4.2</v>
+      </c>
+      <c r="BA14">
+        <v>4.7</v>
+      </c>
+      <c r="BB14">
+        <v>4.9</v>
+      </c>
+      <c r="BC14">
+        <v>4.8</v>
+      </c>
+      <c r="BD14">
+        <v>4.8</v>
+      </c>
+      <c r="BE14">
+        <v>4.9</v>
+      </c>
+      <c r="BF14">
+        <v>4.9</v>
+      </c>
+      <c r="BG14">
+        <v>4.3</v>
+      </c>
+      <c r="BH14">
         <v>3.2</v>
       </c>
-      <c r="AQ14">
-        <v>3</v>
-      </c>
-      <c r="AR14">
-        <v>3.5</v>
-      </c>
-      <c r="AS14">
+      <c r="BI14">
+        <v>2.28</v>
+      </c>
+      <c r="BJ14">
+        <v>14</v>
+      </c>
+      <c r="BK14">
+        <v>3.7</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>4.9</v>
+      </c>
+      <c r="BN14">
+        <v>9.4</v>
+      </c>
+      <c r="BO14">
+        <v>3.25</v>
+      </c>
+      <c r="BP14">
+        <v>60</v>
+      </c>
+      <c r="BQ14">
+        <v>4.6</v>
+      </c>
+      <c r="BR14">
+        <v>80</v>
+      </c>
+      <c r="BS14">
+        <v>4.7</v>
+      </c>
+      <c r="BT14">
+        <v>5.3</v>
+      </c>
+      <c r="BU14">
+        <v>2.58</v>
+      </c>
+      <c r="BV14">
+        <v>20</v>
+      </c>
+      <c r="BW14">
         <v>4</v>
       </c>
-      <c r="AT14">
-        <v>3.6</v>
-      </c>
-      <c r="AU14">
-        <v>3.05</v>
-      </c>
-      <c r="AV14">
-        <v>3.45</v>
-      </c>
-      <c r="AW14">
-        <v>4</v>
-      </c>
-      <c r="AX14">
-        <v>4.2</v>
-      </c>
-      <c r="AY14">
-        <v>3.9</v>
-      </c>
-      <c r="AZ14">
-        <v>4</v>
-      </c>
-      <c r="BA14">
-        <v>4.3</v>
-      </c>
-      <c r="BB14">
+      <c r="BX14">
+        <v>48</v>
+      </c>
+      <c r="BY14">
         <v>4.5</v>
       </c>
-      <c r="BC14">
-        <v>4.4</v>
-      </c>
-      <c r="BD14">
-        <v>4.5</v>
-      </c>
-      <c r="BE14">
-        <v>4.5</v>
-      </c>
-      <c r="BF14">
-        <v>4.5</v>
-      </c>
-      <c r="BG14">
-        <v>4</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.04</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.04</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.04</v>
-      </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB14" t="s">
         <v>125</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="129">
   <si>
     <t>League</t>
   </si>
@@ -289,6 +289,9 @@
     <t>08:30:00</t>
   </si>
   <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
     <t>11:30:00</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t>Shanghai Port B</t>
   </si>
   <si>
+    <t>Changchun Xidu</t>
+  </si>
+  <si>
     <t>Wenzhou Professional</t>
   </si>
   <si>
@@ -361,6 +367,9 @@
     <t>Xian Chongde Ronghai</t>
   </si>
   <si>
+    <t>Dalian Yingbo II</t>
+  </si>
+  <si>
     <t>Guizhou Zhucheng Athletic</t>
   </si>
   <si>
@@ -391,7 +400,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 09:01:53</t>
+    <t>2026-08-04 11:09:02</t>
   </si>
 </sst>
 </file>
@@ -723,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -979,226 +988,226 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="G2">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
         <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q2">
         <v>1.43</v>
       </c>
       <c r="R2">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S2">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T2">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="X2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y2">
+        <v>40</v>
+      </c>
+      <c r="Z2">
+        <v>70</v>
+      </c>
+      <c r="AA2">
+        <v>190</v>
+      </c>
+      <c r="AB2">
+        <v>15.5</v>
+      </c>
+      <c r="AC2">
+        <v>14.5</v>
+      </c>
+      <c r="AD2">
+        <v>27</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
+        <v>14.5</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>16.5</v>
+      </c>
+      <c r="AK2">
+        <v>14.5</v>
+      </c>
+      <c r="AL2">
+        <v>24</v>
+      </c>
+      <c r="AM2">
+        <v>75</v>
+      </c>
+      <c r="AN2">
+        <v>5.3</v>
+      </c>
+      <c r="AO2">
+        <v>55</v>
+      </c>
+      <c r="AP2">
+        <v>24</v>
+      </c>
+      <c r="AQ2">
+        <v>29</v>
+      </c>
+      <c r="AR2">
         <v>48</v>
       </c>
-      <c r="Z2">
-        <v>90</v>
-      </c>
-      <c r="AA2">
-        <v>250</v>
-      </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>16</v>
-      </c>
-      <c r="AD2">
-        <v>34</v>
-      </c>
-      <c r="AE2">
-        <v>110</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>15</v>
-      </c>
-      <c r="AK2">
-        <v>15.5</v>
-      </c>
-      <c r="AL2">
-        <v>27</v>
-      </c>
-      <c r="AM2">
-        <v>90</v>
-      </c>
-      <c r="AN2">
-        <v>4.5</v>
-      </c>
-      <c r="AO2">
-        <v>85</v>
-      </c>
-      <c r="AP2">
-        <v>6</v>
-      </c>
-      <c r="AQ2">
-        <v>32</v>
-      </c>
-      <c r="AR2">
-        <v>6.4</v>
-      </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT2">
+        <v>12</v>
+      </c>
+      <c r="AU2">
         <v>11</v>
       </c>
-      <c r="AU2">
-        <v>11.5</v>
-      </c>
       <c r="AV2">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE2">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG2">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BH2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BI2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM2">
         <v>5.6</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BU2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="BW2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1207,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1221,127 +1230,127 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F3">
         <v>1.5</v>
       </c>
       <c r="G3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>8.6</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3">
         <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
         <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X3">
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA3">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
         <v>32</v>
       </c>
       <c r="AE3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK3">
         <v>21</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN3">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO3">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AP3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="AS3">
         <v>9.6</v>
@@ -1353,22 +1362,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW3">
-        <v>15.5</v>
+        <v>75</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1380,31 +1389,31 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BH3">
         <v>4</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM3">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
         <v>3.85</v>
@@ -1413,43 +1422,43 @@
         <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS3">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY3">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CA3">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1463,25 +1472,25 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1496,7 +1505,7 @@
         <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1691,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1705,28 +1714,28 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F5">
         <v>1.04</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H5">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="I5">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1735,16 +1744,16 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1753,16 +1762,16 @@
         <v>1.05</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1876,64 +1885,64 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1944,121 +1953,121 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F6">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>3.6</v>
+        <v>990</v>
       </c>
       <c r="H6">
-        <v>2.46</v>
+        <v>1.43</v>
       </c>
       <c r="I6">
-        <v>2.74</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.66</v>
+        <v>1.29</v>
       </c>
       <c r="O6">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="W6">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
         <v>1.01</v>
@@ -2115,13 +2124,13 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>1.04</v>
@@ -2133,37 +2142,37 @@
         <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
         <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
         <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
         <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
         <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>1.04</v>
@@ -2175,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2186,229 +2195,229 @@
         <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F7">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="H7">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J7">
-        <v>1.17</v>
+        <v>2.76</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>2.86</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2417,12 +2426,12 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -2431,52 +2440,52 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>1.47</v>
       </c>
       <c r="H8">
+        <v>1.13</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>3.75</v>
+      </c>
+      <c r="K8">
+        <v>5.4</v>
+      </c>
+      <c r="L8">
+        <v>1.41</v>
+      </c>
+      <c r="M8">
+        <v>1.07</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>1.36</v>
+      </c>
+      <c r="P8">
+        <v>1.74</v>
+      </c>
+      <c r="Q8">
+        <v>1.77</v>
+      </c>
+      <c r="R8">
         <v>1.22</v>
       </c>
-      <c r="I8">
-        <v>990</v>
-      </c>
-      <c r="J8">
-        <v>3.35</v>
-      </c>
-      <c r="K8">
-        <v>950</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.57</v>
-      </c>
-      <c r="O8">
-        <v>1.22</v>
-      </c>
-      <c r="P8">
-        <v>1.44</v>
-      </c>
-      <c r="Q8">
-        <v>1.22</v>
-      </c>
-      <c r="R8">
-        <v>1.38</v>
-      </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>2.74</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2485,10 +2494,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W8">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2653,18 +2662,18 @@
         <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
@@ -2673,52 +2682,52 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="O9">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="P9">
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="R9">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S9">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2730,7 +2739,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2901,7 +2910,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2915,10 +2924,10 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2942,25 +2951,25 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P10">
         <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="R10">
         <v>1.25</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3143,12 +3152,12 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
@@ -3157,240 +3166,240 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="O11">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
         <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
         <v>1000</v>
       </c>
       <c r="AM11">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -3399,240 +3408,240 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F12">
+        <v>2.18</v>
+      </c>
+      <c r="G12">
+        <v>2.22</v>
+      </c>
+      <c r="H12">
+        <v>4.3</v>
+      </c>
+      <c r="I12">
+        <v>4.6</v>
+      </c>
+      <c r="J12">
+        <v>3.05</v>
+      </c>
+      <c r="K12">
+        <v>3.15</v>
+      </c>
+      <c r="L12">
+        <v>1.55</v>
+      </c>
+      <c r="M12">
         <v>1.14</v>
       </c>
-      <c r="G12">
-        <v>990</v>
-      </c>
-      <c r="H12">
-        <v>1.14</v>
-      </c>
-      <c r="I12">
-        <v>990</v>
-      </c>
-      <c r="J12">
-        <v>1.27</v>
-      </c>
-      <c r="K12">
-        <v>950</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
       <c r="N12">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>1.39</v>
+        <v>2.84</v>
       </c>
       <c r="R12">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>6.2</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.81</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI12">
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12">
         <v>1000</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -3641,235 +3650,235 @@
         <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F13">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="G13">
-        <v>1.69</v>
+        <v>990</v>
       </c>
       <c r="H13">
-        <v>6.4</v>
+        <v>1.15</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>1.3</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L13">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P13">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
       <c r="R13">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="S13">
-        <v>3.75</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3883,235 +3892,477 @@
         <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="G14">
+        <v>1.69</v>
+      </c>
+      <c r="H14">
+        <v>6.4</v>
+      </c>
+      <c r="I14">
+        <v>7.8</v>
+      </c>
+      <c r="J14">
+        <v>3.85</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>1.37</v>
+      </c>
+      <c r="M14">
+        <v>1.08</v>
+      </c>
+      <c r="N14">
+        <v>3.25</v>
+      </c>
+      <c r="O14">
+        <v>1.37</v>
+      </c>
+      <c r="P14">
+        <v>1.78</v>
+      </c>
+      <c r="Q14">
+        <v>2.08</v>
+      </c>
+      <c r="R14">
+        <v>1.29</v>
+      </c>
+      <c r="S14">
+        <v>3.85</v>
+      </c>
+      <c r="T14">
+        <v>2.06</v>
+      </c>
+      <c r="U14">
+        <v>1.79</v>
+      </c>
+      <c r="V14">
+        <v>1.16</v>
+      </c>
+      <c r="W14">
+        <v>2.44</v>
+      </c>
+      <c r="X14">
+        <v>15.5</v>
+      </c>
+      <c r="Y14">
+        <v>24</v>
+      </c>
+      <c r="Z14">
+        <v>70</v>
+      </c>
+      <c r="AA14">
+        <v>270</v>
+      </c>
+      <c r="AB14">
+        <v>7.2</v>
+      </c>
+      <c r="AC14">
+        <v>11.5</v>
+      </c>
+      <c r="AD14">
+        <v>32</v>
+      </c>
+      <c r="AE14">
+        <v>140</v>
+      </c>
+      <c r="AF14">
+        <v>9.4</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>32</v>
+      </c>
+      <c r="AI14">
+        <v>140</v>
+      </c>
+      <c r="AJ14">
+        <v>17</v>
+      </c>
+      <c r="AK14">
+        <v>24</v>
+      </c>
+      <c r="AL14">
+        <v>55</v>
+      </c>
+      <c r="AM14">
+        <v>210</v>
+      </c>
+      <c r="AN14">
+        <v>14.5</v>
+      </c>
+      <c r="AO14">
+        <v>210</v>
+      </c>
+      <c r="AP14">
+        <v>11</v>
+      </c>
+      <c r="AQ14">
+        <v>16.5</v>
+      </c>
+      <c r="AR14">
+        <v>4.9</v>
+      </c>
+      <c r="AS14">
         <v>5.2</v>
       </c>
-      <c r="H14">
-        <v>1.95</v>
-      </c>
-      <c r="I14">
-        <v>2.2</v>
-      </c>
-      <c r="J14">
-        <v>3.05</v>
-      </c>
-      <c r="K14">
-        <v>3.45</v>
-      </c>
-      <c r="L14">
-        <v>1.45</v>
-      </c>
-      <c r="M14">
-        <v>1.11</v>
-      </c>
-      <c r="N14">
-        <v>2.72</v>
-      </c>
-      <c r="O14">
-        <v>1.48</v>
-      </c>
-      <c r="P14">
-        <v>1.55</v>
-      </c>
-      <c r="Q14">
-        <v>2.44</v>
-      </c>
-      <c r="R14">
-        <v>1.2</v>
-      </c>
-      <c r="S14">
-        <v>4.4</v>
-      </c>
-      <c r="T14">
-        <v>2.08</v>
-      </c>
-      <c r="U14">
-        <v>1.64</v>
-      </c>
-      <c r="V14">
-        <v>1.83</v>
-      </c>
-      <c r="W14">
-        <v>1.23</v>
-      </c>
-      <c r="X14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z14">
-        <v>14</v>
-      </c>
-      <c r="AA14">
-        <v>32</v>
-      </c>
-      <c r="AB14">
-        <v>15.5</v>
-      </c>
-      <c r="AC14">
-        <v>9</v>
-      </c>
-      <c r="AD14">
+      <c r="AT14">
+        <v>6</v>
+      </c>
+      <c r="AU14">
+        <v>7.8</v>
+      </c>
+      <c r="AV14">
+        <v>4.5</v>
+      </c>
+      <c r="AW14">
+        <v>5.1</v>
+      </c>
+      <c r="AX14">
+        <v>7.6</v>
+      </c>
+      <c r="AY14">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14">
+        <v>21</v>
+      </c>
+      <c r="BA14">
+        <v>5.1</v>
+      </c>
+      <c r="BB14">
         <v>13.5</v>
       </c>
-      <c r="AE14">
-        <v>40</v>
-      </c>
-      <c r="AF14">
-        <v>50</v>
-      </c>
-      <c r="AG14">
-        <v>24</v>
-      </c>
-      <c r="AH14">
-        <v>25</v>
-      </c>
-      <c r="AI14">
-        <v>70</v>
-      </c>
-      <c r="AJ14">
-        <v>160</v>
-      </c>
-      <c r="AK14">
-        <v>100</v>
-      </c>
-      <c r="AL14">
-        <v>120</v>
-      </c>
-      <c r="AM14">
-        <v>230</v>
-      </c>
-      <c r="AN14">
-        <v>160</v>
-      </c>
-      <c r="AO14">
-        <v>30</v>
-      </c>
-      <c r="AP14">
-        <v>3.3</v>
-      </c>
-      <c r="AQ14">
-        <v>3.1</v>
-      </c>
-      <c r="AR14">
-        <v>3.7</v>
-      </c>
-      <c r="AS14">
-        <v>4.3</v>
-      </c>
-      <c r="AT14">
-        <v>3.8</v>
-      </c>
-      <c r="AU14">
-        <v>5.8</v>
-      </c>
-      <c r="AV14">
-        <v>3.65</v>
-      </c>
-      <c r="AW14">
-        <v>4.3</v>
-      </c>
-      <c r="AX14">
-        <v>4.4</v>
-      </c>
-      <c r="AY14">
-        <v>4.1</v>
-      </c>
-      <c r="AZ14">
-        <v>4.2</v>
-      </c>
-      <c r="BA14">
-        <v>4.7</v>
-      </c>
-      <c r="BB14">
-        <v>4.9</v>
-      </c>
       <c r="BC14">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BD14">
         <v>4.8</v>
       </c>
       <c r="BE14">
+        <v>5.2</v>
+      </c>
+      <c r="BF14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG14">
+        <v>5.2</v>
+      </c>
+      <c r="BH14">
+        <v>3.35</v>
+      </c>
+      <c r="BI14">
+        <v>2.58</v>
+      </c>
+      <c r="BJ14">
+        <v>12</v>
+      </c>
+      <c r="BK14">
+        <v>5.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>9.6</v>
+      </c>
+      <c r="BN14">
+        <v>4.2</v>
+      </c>
+      <c r="BO14">
+        <v>3.15</v>
+      </c>
+      <c r="BP14">
+        <v>12</v>
+      </c>
+      <c r="BQ14">
+        <v>5.4</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>7.6</v>
+      </c>
+      <c r="BT14">
+        <v>10.5</v>
+      </c>
+      <c r="BU14">
+        <v>5.1</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ14">
+        <v>26</v>
+      </c>
+      <c r="CA14">
+        <v>7.2</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15">
+        <v>3.85</v>
+      </c>
+      <c r="G15">
+        <v>5.2</v>
+      </c>
+      <c r="H15">
+        <v>1.95</v>
+      </c>
+      <c r="I15">
+        <v>2.28</v>
+      </c>
+      <c r="J15">
+        <v>3.05</v>
+      </c>
+      <c r="K15">
+        <v>3.55</v>
+      </c>
+      <c r="L15">
+        <v>1.45</v>
+      </c>
+      <c r="M15">
+        <v>1.11</v>
+      </c>
+      <c r="N15">
+        <v>2.62</v>
+      </c>
+      <c r="O15">
+        <v>1.48</v>
+      </c>
+      <c r="P15">
+        <v>1.55</v>
+      </c>
+      <c r="Q15">
+        <v>2.42</v>
+      </c>
+      <c r="R15">
+        <v>1.2</v>
+      </c>
+      <c r="S15">
+        <v>3.75</v>
+      </c>
+      <c r="T15">
+        <v>2.12</v>
+      </c>
+      <c r="U15">
+        <v>1.64</v>
+      </c>
+      <c r="V15">
+        <v>1.78</v>
+      </c>
+      <c r="W15">
+        <v>1.23</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>7.2</v>
+      </c>
+      <c r="Z15">
+        <v>12</v>
+      </c>
+      <c r="AA15">
+        <v>28</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>12</v>
+      </c>
+      <c r="AE15">
+        <v>40</v>
+      </c>
+      <c r="AF15">
+        <v>50</v>
+      </c>
+      <c r="AG15">
+        <v>21</v>
+      </c>
+      <c r="AH15">
+        <v>25</v>
+      </c>
+      <c r="AI15">
+        <v>70</v>
+      </c>
+      <c r="AJ15">
+        <v>160</v>
+      </c>
+      <c r="AK15">
+        <v>100</v>
+      </c>
+      <c r="AL15">
+        <v>120</v>
+      </c>
+      <c r="AM15">
+        <v>230</v>
+      </c>
+      <c r="AN15">
+        <v>160</v>
+      </c>
+      <c r="AO15">
+        <v>26</v>
+      </c>
+      <c r="AP15">
+        <v>4.5</v>
+      </c>
+      <c r="AQ15">
+        <v>3.65</v>
+      </c>
+      <c r="AR15">
+        <v>4.5</v>
+      </c>
+      <c r="AS15">
+        <v>5.8</v>
+      </c>
+      <c r="AT15">
+        <v>4.7</v>
+      </c>
+      <c r="AU15">
+        <v>3.8</v>
+      </c>
+      <c r="AV15">
+        <v>4.5</v>
+      </c>
+      <c r="AW15">
+        <v>5.9</v>
+      </c>
+      <c r="AX15">
+        <v>6</v>
+      </c>
+      <c r="AY15">
+        <v>5.4</v>
+      </c>
+      <c r="AZ15">
+        <v>5.7</v>
+      </c>
+      <c r="BA15">
+        <v>6.6</v>
+      </c>
+      <c r="BB15">
+        <v>7</v>
+      </c>
+      <c r="BC15">
+        <v>6.8</v>
+      </c>
+      <c r="BD15">
+        <v>6.8</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>7</v>
+      </c>
+      <c r="BG15">
+        <v>5.7</v>
+      </c>
+      <c r="BH15">
+        <v>3.2</v>
+      </c>
+      <c r="BI15">
+        <v>2.28</v>
+      </c>
+      <c r="BJ15">
+        <v>12</v>
+      </c>
+      <c r="BK15">
+        <v>3.75</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>5.3</v>
+      </c>
+      <c r="BN15">
+        <v>9.4</v>
+      </c>
+      <c r="BO15">
+        <v>3.45</v>
+      </c>
+      <c r="BP15">
+        <v>60</v>
+      </c>
+      <c r="BQ15">
+        <v>5</v>
+      </c>
+      <c r="BR15">
+        <v>80</v>
+      </c>
+      <c r="BS15">
+        <v>5.1</v>
+      </c>
+      <c r="BT15">
+        <v>5.3</v>
+      </c>
+      <c r="BU15">
+        <v>2.68</v>
+      </c>
+      <c r="BV15">
+        <v>20</v>
+      </c>
+      <c r="BW15">
+        <v>4.3</v>
+      </c>
+      <c r="BX15">
+        <v>48</v>
+      </c>
+      <c r="BY15">
         <v>4.9</v>
       </c>
-      <c r="BF14">
-        <v>4.9</v>
-      </c>
-      <c r="BG14">
-        <v>4.3</v>
-      </c>
-      <c r="BH14">
-        <v>3.2</v>
-      </c>
-      <c r="BI14">
-        <v>2.28</v>
-      </c>
-      <c r="BJ14">
-        <v>14</v>
-      </c>
-      <c r="BK14">
-        <v>3.7</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>4.9</v>
-      </c>
-      <c r="BN14">
-        <v>9.4</v>
-      </c>
-      <c r="BO14">
-        <v>3.25</v>
-      </c>
-      <c r="BP14">
-        <v>60</v>
-      </c>
-      <c r="BQ14">
-        <v>4.6</v>
-      </c>
-      <c r="BR14">
-        <v>80</v>
-      </c>
-      <c r="BS14">
-        <v>4.7</v>
-      </c>
-      <c r="BT14">
-        <v>5.3</v>
-      </c>
-      <c r="BU14">
-        <v>2.58</v>
-      </c>
-      <c r="BV14">
-        <v>20</v>
-      </c>
-      <c r="BW14">
-        <v>4</v>
-      </c>
-      <c r="BX14">
-        <v>48</v>
-      </c>
-      <c r="BY14">
-        <v>4.5</v>
-      </c>
-      <c r="BZ14">
-        <v>50</v>
-      </c>
-      <c r="CA14">
-        <v>4.6</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>125</v>
+      <c r="BZ15">
+        <v>44</v>
+      </c>
+      <c r="CA15">
+        <v>4.8</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -400,7 +400,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 11:09:02</t>
+    <t>2026-08-04 13:15:54</t>
   </si>
 </sst>
 </file>
@@ -994,220 +994,220 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G2">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O2">
         <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
         <v>1.43</v>
       </c>
       <c r="R2">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="X2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2">
         <v>190</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN2">
         <v>5.3</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AQ2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR2">
         <v>48</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AT2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX2">
         <v>11</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF2">
         <v>4.2</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BI2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BM2">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ2">
+        <v>4.5</v>
+      </c>
+      <c r="BR2">
+        <v>19</v>
+      </c>
+      <c r="BS2">
+        <v>5.9</v>
+      </c>
+      <c r="BT2">
         <v>10.5</v>
       </c>
-      <c r="BQ2">
-        <v>6.2</v>
-      </c>
-      <c r="BR2">
-        <v>21</v>
-      </c>
-      <c r="BS2">
-        <v>4.6</v>
-      </c>
-      <c r="BT2">
-        <v>11</v>
-      </c>
       <c r="BU2">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1236,139 +1236,139 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W3">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X3">
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA3">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE3">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI3">
         <v>150</v>
       </c>
       <c r="AJ3">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP3">
         <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AW3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1377,85 +1377,85 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC3">
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE3">
         <v>18</v>
       </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BL3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BR3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT3">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA3">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="s">
         <v>128</v>
@@ -1478,19 +1478,19 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I4">
         <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1502,10 +1502,10 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1517,7 +1517,7 @@
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1723,55 +1723,55 @@
         <v>1.04</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H5">
         <v>1.04</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5">
+        <v>1.06</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.25</v>
+      </c>
+      <c r="O5">
         <v>1.02</v>
       </c>
-      <c r="K5">
-        <v>1000</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.24</v>
-      </c>
-      <c r="O5">
-        <v>1.01</v>
-      </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1885,61 +1885,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>128</v>
@@ -1962,22 +1962,22 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1986,22 +1986,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.29</v>
+        <v>2.56</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P6">
         <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2010,7 +2010,7 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="W6">
         <v>1.01</v>
@@ -2204,25 +2204,25 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="G7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="I7">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2234,7 +2234,7 @@
         <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
         <v>2.3</v>
@@ -2249,13 +2249,13 @@
         <v>1.91</v>
       </c>
       <c r="U7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X7">
         <v>12.5</v>
@@ -2267,10 +2267,10 @@
         <v>19</v>
       </c>
       <c r="AA7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AB7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC7">
         <v>8.6</v>
@@ -2282,10 +2282,10 @@
         <v>42</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH7">
         <v>24</v>
@@ -2294,10 +2294,10 @@
         <v>65</v>
       </c>
       <c r="AJ7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL7">
         <v>75</v>
@@ -2306,64 +2306,64 @@
         <v>170</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP7">
         <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT7">
         <v>3.35</v>
       </c>
       <c r="AU7">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AV7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ7">
         <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB7">
+        <v>4.4</v>
+      </c>
+      <c r="BC7">
         <v>4.3</v>
       </c>
-      <c r="BC7">
-        <v>4.2</v>
-      </c>
       <c r="BD7">
+        <v>4.4</v>
+      </c>
+      <c r="BE7">
+        <v>4.6</v>
+      </c>
+      <c r="BF7">
         <v>4.3</v>
       </c>
-      <c r="BE7">
-        <v>4.4</v>
-      </c>
-      <c r="BF7">
-        <v>4.2</v>
-      </c>
       <c r="BG7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2375,49 +2375,49 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BN7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ7">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BR7">
         <v>55</v>
       </c>
       <c r="BS7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BT7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU7">
+        <v>4.3</v>
+      </c>
+      <c r="BV7">
+        <v>29</v>
+      </c>
+      <c r="BW7">
         <v>4.1</v>
       </c>
-      <c r="BV7">
-        <v>27</v>
-      </c>
-      <c r="BW7">
-        <v>4.2</v>
-      </c>
       <c r="BX7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2446,220 +2446,220 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="G8">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Q8">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S8">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2688,166 +2688,166 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="G9">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="H9">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q9">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="R9">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>1.23</v>
+        <v>3.05</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>1.45</v>
+        <v>2.56</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R11">
         <v>1.25</v>
@@ -3414,13 +3414,13 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G12">
         <v>2.22</v>
       </c>
       <c r="H12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
         <v>4.6</v>
@@ -3438,19 +3438,19 @@
         <v>1.14</v>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P12">
         <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
         <v>6.2</v>
@@ -3462,13 +3462,13 @@
         <v>1.69</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W12">
         <v>1.81</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y12">
         <v>11</v>
@@ -3483,7 +3483,7 @@
         <v>6.6</v>
       </c>
       <c r="AC12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>21</v>
@@ -3504,7 +3504,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK12">
         <v>32</v>
@@ -3525,10 +3525,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS12">
         <v>38</v>
@@ -3537,7 +3537,7 @@
         <v>6</v>
       </c>
       <c r="AU12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
         <v>17.5</v>
@@ -3555,10 +3555,10 @@
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC12">
         <v>20</v>
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG12">
         <v>42</v>
@@ -3656,19 +3656,19 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G13">
         <v>990</v>
       </c>
       <c r="H13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I13">
         <v>990</v>
       </c>
       <c r="J13">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3686,7 +3686,7 @@
         <v>1.39</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q13">
         <v>1.39</v>
@@ -3707,7 +3707,7 @@
         <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3898,7 +3898,7 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="G14">
         <v>1.69</v>
@@ -3946,7 +3946,7 @@
         <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W14">
         <v>2.44</v>
@@ -3967,7 +3967,7 @@
         <v>7.2</v>
       </c>
       <c r="AC14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD14">
         <v>32</v>
@@ -4012,10 +4012,10 @@
         <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT14">
         <v>6</v>
@@ -4024,10 +4024,10 @@
         <v>7.8</v>
       </c>
       <c r="AV14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX14">
         <v>7.6</v>
@@ -4039,7 +4039,7 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB14">
         <v>13.5</v>
@@ -4048,16 +4048,16 @@
         <v>16</v>
       </c>
       <c r="BD14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF14">
         <v>8.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH14">
         <v>3.35</v>
@@ -4140,7 +4140,7 @@
         <v>127</v>
       </c>
       <c r="F15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G15">
         <v>5.2</v>
@@ -4149,13 +4149,13 @@
         <v>1.95</v>
       </c>
       <c r="I15">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="J15">
         <v>3.05</v>
       </c>
       <c r="K15">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L15">
         <v>1.45</v>
@@ -4164,7 +4164,7 @@
         <v>1.11</v>
       </c>
       <c r="N15">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O15">
         <v>1.48</v>
@@ -4179,7 +4179,7 @@
         <v>1.2</v>
       </c>
       <c r="S15">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T15">
         <v>2.12</v>
@@ -4188,13 +4188,13 @@
         <v>1.64</v>
       </c>
       <c r="V15">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W15">
         <v>1.23</v>
       </c>
       <c r="X15">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y15">
         <v>7.2</v>
@@ -4203,7 +4203,7 @@
         <v>12</v>
       </c>
       <c r="AA15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AB15">
         <v>13.5</v>
@@ -4212,7 +4212,7 @@
         <v>8</v>
       </c>
       <c r="AD15">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE15">
         <v>40</v>
@@ -4224,7 +4224,7 @@
         <v>21</v>
       </c>
       <c r="AH15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI15">
         <v>70</v>
@@ -4245,61 +4245,61 @@
         <v>160</v>
       </c>
       <c r="AO15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP15">
+        <v>4</v>
+      </c>
+      <c r="AQ15">
+        <v>3.5</v>
+      </c>
+      <c r="AR15">
+        <v>4.3</v>
+      </c>
+      <c r="AS15">
+        <v>5.7</v>
+      </c>
+      <c r="AT15">
         <v>4.5</v>
       </c>
-      <c r="AQ15">
-        <v>3.65</v>
-      </c>
-      <c r="AR15">
-        <v>4.5</v>
-      </c>
-      <c r="AS15">
-        <v>5.8</v>
-      </c>
-      <c r="AT15">
-        <v>4.7</v>
-      </c>
       <c r="AU15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AV15">
         <v>4.5</v>
       </c>
       <c r="AW15">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY15">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AZ15">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA15">
+        <v>6.2</v>
+      </c>
+      <c r="BB15">
         <v>6.6</v>
       </c>
-      <c r="BB15">
-        <v>7</v>
-      </c>
       <c r="BC15">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD15">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF15">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH15">
         <v>3.2</v>
@@ -4308,58 +4308,58 @@
         <v>2.28</v>
       </c>
       <c r="BJ15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BN15">
         <v>9.4</v>
       </c>
       <c r="BO15">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BP15">
         <v>60</v>
       </c>
       <c r="BQ15">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR15">
         <v>80</v>
       </c>
       <c r="BS15">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BT15">
         <v>5.3</v>
       </c>
       <c r="BU15">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BV15">
         <v>20</v>
       </c>
       <c r="BW15">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BX15">
         <v>48</v>
       </c>
       <c r="BY15">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BZ15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="CA15">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB15" t="s">
         <v>128</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
   <si>
     <t>League</t>
   </si>
@@ -301,6 +301,9 @@
     <t>18:00:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -343,12 +346,18 @@
     <t>Keflavik</t>
   </si>
   <si>
+    <t>CD Gualberto Villarroel</t>
+  </si>
+  <si>
     <t>Hafnarfjordur</t>
   </si>
   <si>
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Nacional Potosi</t>
+  </si>
+  <si>
     <t>Penarol</t>
   </si>
   <si>
@@ -385,12 +394,18 @@
     <t>KA Akureyri</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>KR Reykjavik</t>
   </si>
   <si>
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>The Strongest</t>
+  </si>
+  <si>
     <t>Wanderers (Uru)</t>
   </si>
   <si>
@@ -400,7 +415,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 13:15:54</t>
+    <t>2026-08-04 15:22:38</t>
   </si>
 </sst>
 </file>
@@ -732,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -988,226 +1003,226 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G2">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L2">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="Q2">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="S2">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
         <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="X2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2">
         <v>70</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK2">
         <v>14</v>
       </c>
       <c r="AL2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AO2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AQ2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AR2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AS2">
+        <v>42</v>
+      </c>
+      <c r="AT2">
+        <v>11.5</v>
+      </c>
+      <c r="AU2">
+        <v>10.5</v>
+      </c>
+      <c r="AV2">
+        <v>19</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2">
+        <v>16.5</v>
+      </c>
+      <c r="BA2">
+        <v>44</v>
+      </c>
+      <c r="BB2">
+        <v>13</v>
+      </c>
+      <c r="BC2">
+        <v>12.5</v>
+      </c>
+      <c r="BD2">
+        <v>21</v>
+      </c>
+      <c r="BE2">
+        <v>36</v>
+      </c>
+      <c r="BF2">
+        <v>5</v>
+      </c>
+      <c r="BG2">
+        <v>36</v>
+      </c>
+      <c r="BH2">
+        <v>5.2</v>
+      </c>
+      <c r="BI2">
+        <v>3.9</v>
+      </c>
+      <c r="BJ2">
         <v>10</v>
       </c>
-      <c r="AT2">
-        <v>13.5</v>
-      </c>
-      <c r="AU2">
-        <v>11.5</v>
-      </c>
-      <c r="AV2">
-        <v>21</v>
-      </c>
-      <c r="AW2">
-        <v>48</v>
-      </c>
-      <c r="AX2">
+      <c r="BK2">
+        <v>4.4</v>
+      </c>
+      <c r="BL2">
+        <v>90</v>
+      </c>
+      <c r="BM2">
+        <v>7.4</v>
+      </c>
+      <c r="BN2">
+        <v>4.8</v>
+      </c>
+      <c r="BO2">
+        <v>3.95</v>
+      </c>
+      <c r="BP2">
         <v>11</v>
       </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>14</v>
-      </c>
-      <c r="BC2">
-        <v>12</v>
-      </c>
-      <c r="BD2">
+      <c r="BQ2">
+        <v>4.6</v>
+      </c>
+      <c r="BR2">
         <v>20</v>
       </c>
-      <c r="BE2">
-        <v>48</v>
-      </c>
-      <c r="BF2">
-        <v>4.2</v>
-      </c>
-      <c r="BG2">
-        <v>34</v>
-      </c>
-      <c r="BH2">
-        <v>5.5</v>
-      </c>
-      <c r="BI2">
-        <v>4.2</v>
-      </c>
-      <c r="BJ2">
-        <v>9.6</v>
-      </c>
-      <c r="BK2">
-        <v>4.5</v>
-      </c>
-      <c r="BL2">
-        <v>80</v>
-      </c>
-      <c r="BM2">
-        <v>7.6</v>
-      </c>
-      <c r="BN2">
-        <v>5.1</v>
-      </c>
-      <c r="BO2">
-        <v>4.1</v>
-      </c>
-      <c r="BP2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ2">
-        <v>4.5</v>
-      </c>
-      <c r="BR2">
-        <v>19</v>
-      </c>
       <c r="BS2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT2">
         <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BV2">
+        <v>42</v>
+      </c>
+      <c r="BW2">
+        <v>6.8</v>
+      </c>
+      <c r="BX2">
         <v>40</v>
       </c>
-      <c r="BW2">
-        <v>7</v>
-      </c>
-      <c r="BX2">
-        <v>38</v>
-      </c>
       <c r="BY2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1216,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1230,10 +1245,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F3">
         <v>1.46</v>
@@ -1245,7 +1260,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
         <v>4.6</v>
@@ -1263,13 +1278,13 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
         <v>1.99</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
         <v>1.37</v>
@@ -1278,7 +1293,7 @@
         <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
         <v>1.77</v>
@@ -1299,13 +1314,13 @@
         <v>80</v>
       </c>
       <c r="AA3">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3">
         <v>34</v>
@@ -1338,7 +1353,7 @@
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO3">
         <v>220</v>
@@ -1353,7 +1368,7 @@
         <v>60</v>
       </c>
       <c r="AS3">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1365,7 +1380,7 @@
         <v>30</v>
       </c>
       <c r="AW3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
@@ -1377,7 +1392,7 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB3">
         <v>11</v>
@@ -1389,16 +1404,16 @@
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BF3">
         <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
@@ -1407,13 +1422,13 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>220</v>
       </c>
       <c r="BM3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3">
         <v>3.75</v>
@@ -1431,34 +1446,34 @@
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT3">
         <v>15</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>110</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>110</v>
       </c>
       <c r="BY3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1472,25 +1487,25 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1700,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1714,25 +1729,25 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G5">
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I5">
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1744,10 +1759,10 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="P5">
         <v>1.25</v>
@@ -1942,7 +1957,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1956,13 +1971,13 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G6">
         <v>990</v>
@@ -1974,7 +1989,7 @@
         <v>1.93</v>
       </c>
       <c r="J6">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1986,22 +2001,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
         <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2010,7 +2025,7 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
         <v>1.01</v>
@@ -2184,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2198,31 +2213,31 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I7">
         <v>3.1</v>
       </c>
       <c r="J7">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="K7">
         <v>3.4</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2234,7 +2249,7 @@
         <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
         <v>2.3</v>
@@ -2243,7 +2258,7 @@
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
         <v>1.91</v>
@@ -2252,10 +2267,10 @@
         <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
         <v>12.5</v>
@@ -2267,10 +2282,10 @@
         <v>19</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
         <v>8.6</v>
@@ -2285,7 +2300,7 @@
         <v>23</v>
       </c>
       <c r="AG7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH7">
         <v>24</v>
@@ -2297,19 +2312,19 @@
         <v>65</v>
       </c>
       <c r="AK7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN7">
         <v>55</v>
       </c>
       <c r="AO7">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP7">
         <v>7.6</v>
@@ -2318,52 +2333,52 @@
         <v>7</v>
       </c>
       <c r="AR7">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AS7">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT7">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AU7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AV7">
         <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY7">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA7">
+        <v>4.6</v>
+      </c>
+      <c r="BB7">
+        <v>4.6</v>
+      </c>
+      <c r="BC7">
+        <v>4.5</v>
+      </c>
+      <c r="BD7">
+        <v>4.7</v>
+      </c>
+      <c r="BE7">
+        <v>4.8</v>
+      </c>
+      <c r="BF7">
+        <v>4.6</v>
+      </c>
+      <c r="BG7">
         <v>4.4</v>
-      </c>
-      <c r="BB7">
-        <v>4.4</v>
-      </c>
-      <c r="BC7">
-        <v>4.3</v>
-      </c>
-      <c r="BD7">
-        <v>4.4</v>
-      </c>
-      <c r="BE7">
-        <v>4.6</v>
-      </c>
-      <c r="BF7">
-        <v>4.3</v>
-      </c>
-      <c r="BG7">
-        <v>4.3</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2375,16 +2390,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
         <v>4.4</v>
@@ -2399,7 +2414,7 @@
         <v>55</v>
       </c>
       <c r="BS7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT7">
         <v>6.8</v>
@@ -2408,16 +2423,16 @@
         <v>4.3</v>
       </c>
       <c r="BV7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX7">
         <v>55</v>
       </c>
       <c r="BY7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2426,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2440,31 +2455,31 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F8">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G8">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="H8">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I8">
         <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
         <v>1.09</v>
@@ -2473,16 +2488,16 @@
         <v>2.88</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
         <v>3.6</v>
@@ -2491,19 +2506,19 @@
         <v>2.14</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="X8">
         <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2512,154 +2527,154 @@
         <v>260</v>
       </c>
       <c r="AB8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE8">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI8">
         <v>150</v>
       </c>
       <c r="AJ8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK8">
         <v>24</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM8">
         <v>220</v>
       </c>
       <c r="AN8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO8">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP8">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AQ8">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR8">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AS8">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AU8">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AV8">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW8">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX8">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AY8">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AZ8">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA8">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB8">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BC8">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD8">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF8">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BI8">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
+        <v>2.42</v>
+      </c>
+      <c r="BN8">
+        <v>4.1</v>
+      </c>
+      <c r="BO8">
+        <v>2.94</v>
+      </c>
+      <c r="BP8">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8">
+        <v>5.7</v>
+      </c>
+      <c r="BR8">
+        <v>34</v>
+      </c>
+      <c r="BS8">
+        <v>2.28</v>
+      </c>
+      <c r="BT8">
+        <v>10.5</v>
+      </c>
+      <c r="BU8">
+        <v>5.2</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
         <v>2.38</v>
       </c>
-      <c r="BN8">
-        <v>4.2</v>
-      </c>
-      <c r="BO8">
-        <v>3.05</v>
-      </c>
-      <c r="BP8">
-        <v>13</v>
-      </c>
-      <c r="BQ8">
-        <v>6</v>
-      </c>
-      <c r="BR8">
-        <v>36</v>
-      </c>
-      <c r="BS8">
-        <v>2.26</v>
-      </c>
-      <c r="BT8">
-        <v>10</v>
-      </c>
-      <c r="BU8">
-        <v>5.3</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>2.32</v>
-      </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2668,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2682,28 +2697,28 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F9">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="G9">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H9">
         <v>5.5</v>
       </c>
       <c r="I9">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2712,19 +2727,19 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
         <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
         <v>3.05</v>
@@ -2736,40 +2751,40 @@
         <v>1.9</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="X9">
         <v>19</v>
       </c>
       <c r="Y9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC9">
         <v>11.5</v>
       </c>
       <c r="AD9">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF9">
         <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>24</v>
@@ -2778,76 +2793,76 @@
         <v>120</v>
       </c>
       <c r="AJ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL9">
         <v>46</v>
       </c>
       <c r="AM9">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO9">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AP9">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AR9">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS9">
+        <v>6</v>
+      </c>
+      <c r="AT9">
+        <v>3.6</v>
+      </c>
+      <c r="AU9">
+        <v>4</v>
+      </c>
+      <c r="AV9">
+        <v>5</v>
+      </c>
+      <c r="AW9">
+        <v>5.9</v>
+      </c>
+      <c r="AX9">
+        <v>4</v>
+      </c>
+      <c r="AY9">
+        <v>3.9</v>
+      </c>
+      <c r="AZ9">
+        <v>4.9</v>
+      </c>
+      <c r="BA9">
+        <v>5.9</v>
+      </c>
+      <c r="BB9">
+        <v>4.5</v>
+      </c>
+      <c r="BC9">
         <v>4.6</v>
       </c>
-      <c r="AT9">
-        <v>3.15</v>
-      </c>
-      <c r="AU9">
-        <v>3.3</v>
-      </c>
-      <c r="AV9">
+      <c r="BD9">
+        <v>5.5</v>
+      </c>
+      <c r="BE9">
+        <v>6</v>
+      </c>
+      <c r="BF9">
         <v>4</v>
       </c>
-      <c r="AW9">
-        <v>4.5</v>
-      </c>
-      <c r="AX9">
-        <v>3.3</v>
-      </c>
-      <c r="AY9">
-        <v>3.35</v>
-      </c>
-      <c r="AZ9">
-        <v>3.9</v>
-      </c>
-      <c r="BA9">
-        <v>4.5</v>
-      </c>
-      <c r="BB9">
-        <v>3.6</v>
-      </c>
-      <c r="BC9">
-        <v>3.8</v>
-      </c>
-      <c r="BD9">
-        <v>4.2</v>
-      </c>
-      <c r="BE9">
-        <v>4.5</v>
-      </c>
-      <c r="BF9">
-        <v>3.35</v>
-      </c>
       <c r="BG9">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2910,7 +2925,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2924,28 +2939,28 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2954,34 +2969,34 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="O10">
         <v>1.07</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="Q10">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.06</v>
+        <v>1.84</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U10">
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3152,12 +3167,12 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
@@ -3166,52 +3181,52 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="O11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S11">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3223,7 +3238,7 @@
         <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3337,69 +3352,69 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -3408,240 +3423,240 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F12">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O12">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="P12">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="R12">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
         <v>1000</v>
       </c>
       <c r="AM12">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -3650,719 +3665,1203 @@
         <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F13">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="G13">
-        <v>990</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J13">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="O13">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="P13">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="R13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S13">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE13">
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI13">
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL13">
         <v>1000</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB13" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F14">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
-        <v>1.69</v>
+        <v>990</v>
       </c>
       <c r="H14">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
-        <v>7.8</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L14">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S14">
-        <v>3.85</v>
+        <v>1.98</v>
       </c>
       <c r="T14">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
       </c>
       <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15">
+        <v>1.18</v>
+      </c>
+      <c r="G15">
+        <v>990</v>
+      </c>
+      <c r="H15">
+        <v>1.18</v>
+      </c>
+      <c r="I15">
+        <v>990</v>
+      </c>
+      <c r="J15">
+        <v>1.41</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.28</v>
+      </c>
+      <c r="O15">
+        <v>1.39</v>
+      </c>
+      <c r="P15">
+        <v>1.28</v>
+      </c>
+      <c r="Q15">
+        <v>1.39</v>
+      </c>
+      <c r="R15">
+        <v>1.14</v>
+      </c>
+      <c r="S15">
+        <v>1.41</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.17</v>
+      </c>
+      <c r="W15">
+        <v>1.17</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
         <v>99</v>
       </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15">
-        <v>3.9</v>
-      </c>
-      <c r="G15">
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16">
+        <v>1.67</v>
+      </c>
+      <c r="G16">
+        <v>1.69</v>
+      </c>
+      <c r="H16">
+        <v>6.4</v>
+      </c>
+      <c r="I16">
+        <v>7.6</v>
+      </c>
+      <c r="J16">
+        <v>3.85</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>1.37</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.25</v>
+      </c>
+      <c r="O16">
+        <v>1.37</v>
+      </c>
+      <c r="P16">
+        <v>1.78</v>
+      </c>
+      <c r="Q16">
+        <v>2.08</v>
+      </c>
+      <c r="R16">
+        <v>1.29</v>
+      </c>
+      <c r="S16">
+        <v>3.85</v>
+      </c>
+      <c r="T16">
+        <v>2.06</v>
+      </c>
+      <c r="U16">
+        <v>1.79</v>
+      </c>
+      <c r="V16">
+        <v>1.16</v>
+      </c>
+      <c r="W16">
+        <v>2.44</v>
+      </c>
+      <c r="X16">
+        <v>15.5</v>
+      </c>
+      <c r="Y16">
+        <v>24</v>
+      </c>
+      <c r="Z16">
+        <v>70</v>
+      </c>
+      <c r="AA16">
+        <v>270</v>
+      </c>
+      <c r="AB16">
+        <v>7.2</v>
+      </c>
+      <c r="AC16">
+        <v>11</v>
+      </c>
+      <c r="AD16">
+        <v>32</v>
+      </c>
+      <c r="AE16">
+        <v>140</v>
+      </c>
+      <c r="AF16">
+        <v>9.4</v>
+      </c>
+      <c r="AG16">
+        <v>12</v>
+      </c>
+      <c r="AH16">
+        <v>32</v>
+      </c>
+      <c r="AI16">
+        <v>140</v>
+      </c>
+      <c r="AJ16">
+        <v>17</v>
+      </c>
+      <c r="AK16">
+        <v>24</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
+        <v>210</v>
+      </c>
+      <c r="AN16">
+        <v>14.5</v>
+      </c>
+      <c r="AO16">
+        <v>210</v>
+      </c>
+      <c r="AP16">
+        <v>11</v>
+      </c>
+      <c r="AQ16">
+        <v>16.5</v>
+      </c>
+      <c r="AR16">
+        <v>5</v>
+      </c>
+      <c r="AS16">
+        <v>5.3</v>
+      </c>
+      <c r="AT16">
+        <v>6</v>
+      </c>
+      <c r="AU16">
+        <v>7.8</v>
+      </c>
+      <c r="AV16">
+        <v>4.6</v>
+      </c>
+      <c r="AW16">
         <v>5.2</v>
       </c>
-      <c r="H15">
-        <v>1.95</v>
-      </c>
-      <c r="I15">
-        <v>2.2</v>
-      </c>
-      <c r="J15">
-        <v>3.05</v>
-      </c>
-      <c r="K15">
+      <c r="AX16">
+        <v>7.6</v>
+      </c>
+      <c r="AY16">
+        <v>8.6</v>
+      </c>
+      <c r="AZ16">
+        <v>21</v>
+      </c>
+      <c r="BA16">
+        <v>5.2</v>
+      </c>
+      <c r="BB16">
+        <v>13.5</v>
+      </c>
+      <c r="BC16">
+        <v>16</v>
+      </c>
+      <c r="BD16">
+        <v>4.9</v>
+      </c>
+      <c r="BE16">
+        <v>5.3</v>
+      </c>
+      <c r="BF16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG16">
+        <v>5.3</v>
+      </c>
+      <c r="BH16">
+        <v>3.35</v>
+      </c>
+      <c r="BI16">
+        <v>2.58</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>5.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>9.6</v>
+      </c>
+      <c r="BN16">
+        <v>4.2</v>
+      </c>
+      <c r="BO16">
+        <v>3.15</v>
+      </c>
+      <c r="BP16">
+        <v>12</v>
+      </c>
+      <c r="BQ16">
+        <v>5.4</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>7.6</v>
+      </c>
+      <c r="BT16">
+        <v>10.5</v>
+      </c>
+      <c r="BU16">
+        <v>5.1</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ16">
+        <v>26</v>
+      </c>
+      <c r="CA16">
+        <v>7.2</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17">
+        <v>4.2</v>
+      </c>
+      <c r="G17">
+        <v>5.6</v>
+      </c>
+      <c r="H17">
+        <v>1.88</v>
+      </c>
+      <c r="I17">
+        <v>2.1</v>
+      </c>
+      <c r="J17">
+        <v>3.1</v>
+      </c>
+      <c r="K17">
         <v>3.45</v>
       </c>
-      <c r="L15">
+      <c r="L17">
         <v>1.45</v>
       </c>
-      <c r="M15">
+      <c r="M17">
         <v>1.11</v>
       </c>
-      <c r="N15">
+      <c r="N17">
         <v>2.68</v>
       </c>
-      <c r="O15">
+      <c r="O17">
         <v>1.48</v>
       </c>
-      <c r="P15">
+      <c r="P17">
         <v>1.55</v>
       </c>
-      <c r="Q15">
+      <c r="Q17">
         <v>2.42</v>
       </c>
-      <c r="R15">
+      <c r="R17">
         <v>1.2</v>
       </c>
-      <c r="S15">
-        <v>4.4</v>
-      </c>
-      <c r="T15">
-        <v>2.12</v>
-      </c>
-      <c r="U15">
-        <v>1.64</v>
-      </c>
-      <c r="V15">
-        <v>1.83</v>
-      </c>
-      <c r="W15">
-        <v>1.23</v>
-      </c>
-      <c r="X15">
+      <c r="S17">
+        <v>3.85</v>
+      </c>
+      <c r="T17">
+        <v>2.16</v>
+      </c>
+      <c r="U17">
+        <v>1.72</v>
+      </c>
+      <c r="V17">
+        <v>1.9</v>
+      </c>
+      <c r="W17">
+        <v>1.21</v>
+      </c>
+      <c r="X17">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y15">
-        <v>7.2</v>
-      </c>
-      <c r="Z15">
-        <v>12</v>
-      </c>
-      <c r="AA15">
-        <v>32</v>
-      </c>
-      <c r="AB15">
-        <v>13.5</v>
-      </c>
-      <c r="AC15">
+      <c r="Y17">
+        <v>7</v>
+      </c>
+      <c r="Z17">
+        <v>11.5</v>
+      </c>
+      <c r="AA17">
+        <v>25</v>
+      </c>
+      <c r="AB17">
+        <v>14</v>
+      </c>
+      <c r="AC17">
         <v>8</v>
       </c>
-      <c r="AD15">
-        <v>13.5</v>
-      </c>
-      <c r="AE15">
-        <v>40</v>
-      </c>
-      <c r="AF15">
-        <v>50</v>
-      </c>
-      <c r="AG15">
-        <v>21</v>
-      </c>
-      <c r="AH15">
-        <v>29</v>
-      </c>
-      <c r="AI15">
+      <c r="AD17">
+        <v>11.5</v>
+      </c>
+      <c r="AE17">
+        <v>28</v>
+      </c>
+      <c r="AF17">
+        <v>46</v>
+      </c>
+      <c r="AG17">
+        <v>23</v>
+      </c>
+      <c r="AH17">
+        <v>26</v>
+      </c>
+      <c r="AI17">
         <v>70</v>
       </c>
-      <c r="AJ15">
-        <v>160</v>
-      </c>
-      <c r="AK15">
-        <v>100</v>
-      </c>
-      <c r="AL15">
+      <c r="AJ17">
+        <v>180</v>
+      </c>
+      <c r="AK17">
         <v>120</v>
       </c>
-      <c r="AM15">
-        <v>230</v>
-      </c>
-      <c r="AN15">
-        <v>160</v>
-      </c>
-      <c r="AO15">
-        <v>30</v>
-      </c>
-      <c r="AP15">
+      <c r="AL17">
+        <v>130</v>
+      </c>
+      <c r="AM17">
+        <v>240</v>
+      </c>
+      <c r="AN17">
+        <v>180</v>
+      </c>
+      <c r="AO17">
+        <v>24</v>
+      </c>
+      <c r="AP17">
+        <v>4.5</v>
+      </c>
+      <c r="AQ17">
+        <v>3.8</v>
+      </c>
+      <c r="AR17">
+        <v>4.8</v>
+      </c>
+      <c r="AS17">
+        <v>6.2</v>
+      </c>
+      <c r="AT17">
+        <v>5.2</v>
+      </c>
+      <c r="AU17">
+        <v>4.1</v>
+      </c>
+      <c r="AV17">
+        <v>4.8</v>
+      </c>
+      <c r="AW17">
+        <v>6.4</v>
+      </c>
+      <c r="AX17">
+        <v>7</v>
+      </c>
+      <c r="AY17">
+        <v>6</v>
+      </c>
+      <c r="AZ17">
+        <v>6.2</v>
+      </c>
+      <c r="BA17">
+        <v>7.4</v>
+      </c>
+      <c r="BB17">
+        <v>8</v>
+      </c>
+      <c r="BC17">
+        <v>7.8</v>
+      </c>
+      <c r="BD17">
+        <v>7.8</v>
+      </c>
+      <c r="BE17">
+        <v>8</v>
+      </c>
+      <c r="BF17">
+        <v>8</v>
+      </c>
+      <c r="BG17">
+        <v>6.2</v>
+      </c>
+      <c r="BH17">
+        <v>3.2</v>
+      </c>
+      <c r="BI17">
+        <v>2.3</v>
+      </c>
+      <c r="BJ17">
+        <v>14</v>
+      </c>
+      <c r="BK17">
+        <v>3.75</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>5.1</v>
+      </c>
+      <c r="BN17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO17">
+        <v>3.4</v>
+      </c>
+      <c r="BP17">
+        <v>65</v>
+      </c>
+      <c r="BQ17">
+        <v>4.8</v>
+      </c>
+      <c r="BR17">
+        <v>85</v>
+      </c>
+      <c r="BS17">
+        <v>4.9</v>
+      </c>
+      <c r="BT17">
+        <v>5.1</v>
+      </c>
+      <c r="BU17">
+        <v>2.56</v>
+      </c>
+      <c r="BV17">
+        <v>19</v>
+      </c>
+      <c r="BW17">
         <v>4</v>
       </c>
-      <c r="AQ15">
-        <v>3.5</v>
-      </c>
-      <c r="AR15">
-        <v>4.3</v>
-      </c>
-      <c r="AS15">
-        <v>5.7</v>
-      </c>
-      <c r="AT15">
-        <v>4.5</v>
-      </c>
-      <c r="AU15">
-        <v>3.7</v>
-      </c>
-      <c r="AV15">
-        <v>4.5</v>
-      </c>
-      <c r="AW15">
-        <v>5.5</v>
-      </c>
-      <c r="AX15">
-        <v>5.8</v>
-      </c>
-      <c r="AY15">
-        <v>5.2</v>
-      </c>
-      <c r="AZ15">
-        <v>5.5</v>
-      </c>
-      <c r="BA15">
-        <v>6.2</v>
-      </c>
-      <c r="BB15">
-        <v>6.6</v>
-      </c>
-      <c r="BC15">
-        <v>6.4</v>
-      </c>
-      <c r="BD15">
-        <v>6.4</v>
-      </c>
-      <c r="BE15">
-        <v>6.6</v>
-      </c>
-      <c r="BF15">
-        <v>6.6</v>
-      </c>
-      <c r="BG15">
-        <v>5.6</v>
-      </c>
-      <c r="BH15">
-        <v>3.2</v>
-      </c>
-      <c r="BI15">
-        <v>2.28</v>
-      </c>
-      <c r="BJ15">
-        <v>14</v>
-      </c>
-      <c r="BK15">
-        <v>3.7</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>4.9</v>
-      </c>
-      <c r="BN15">
-        <v>9.4</v>
-      </c>
-      <c r="BO15">
-        <v>3.25</v>
-      </c>
-      <c r="BP15">
-        <v>60</v>
-      </c>
-      <c r="BQ15">
+      <c r="BX17">
+        <v>46</v>
+      </c>
+      <c r="BY17">
         <v>4.6</v>
       </c>
-      <c r="BR15">
-        <v>80</v>
-      </c>
-      <c r="BS15">
+      <c r="BZ17">
+        <v>48</v>
+      </c>
+      <c r="CA17">
         <v>4.7</v>
       </c>
-      <c r="BT15">
-        <v>5.3</v>
-      </c>
-      <c r="BU15">
-        <v>2.58</v>
-      </c>
-      <c r="BV15">
-        <v>20</v>
-      </c>
-      <c r="BW15">
-        <v>4</v>
-      </c>
-      <c r="BX15">
-        <v>48</v>
-      </c>
-      <c r="BY15">
-        <v>4.5</v>
-      </c>
-      <c r="BZ15">
-        <v>50</v>
-      </c>
-      <c r="CA15">
-        <v>4.6</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>128</v>
+      <c r="CB17" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -415,7 +415,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 15:22:38</t>
+    <t>2026-08-04 17:29:57</t>
   </si>
 </sst>
 </file>
@@ -1009,220 +1009,220 @@
         <v>117</v>
       </c>
       <c r="F2">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G2">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
         <v>5.5</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O2">
+        <v>1.14</v>
+      </c>
+      <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
+        <v>1.45</v>
+      </c>
+      <c r="R2">
+        <v>1.81</v>
+      </c>
+      <c r="S2">
+        <v>2.18</v>
+      </c>
+      <c r="T2">
+        <v>1.59</v>
+      </c>
+      <c r="U2">
+        <v>2.38</v>
+      </c>
+      <c r="V2">
         <v>1.17</v>
       </c>
-      <c r="P2">
-        <v>2.78</v>
-      </c>
-      <c r="Q2">
-        <v>1.5</v>
-      </c>
-      <c r="R2">
-        <v>1.69</v>
-      </c>
-      <c r="S2">
-        <v>2.3</v>
-      </c>
-      <c r="T2">
-        <v>1.6</v>
-      </c>
-      <c r="U2">
-        <v>2.36</v>
-      </c>
-      <c r="V2">
-        <v>1.18</v>
-      </c>
       <c r="W2">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK2">
         <v>14</v>
       </c>
       <c r="AL2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM2">
         <v>75</v>
       </c>
       <c r="AN2">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS2">
         <v>42</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
         <v>21</v>
       </c>
       <c r="BE2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BG2">
         <v>36</v>
       </c>
       <c r="BH2">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BI2">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BL2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BM2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
+        <v>3.65</v>
+      </c>
+      <c r="BP2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ2">
         <v>3.95</v>
       </c>
-      <c r="BP2">
-        <v>11</v>
-      </c>
-      <c r="BQ2">
-        <v>4.6</v>
-      </c>
       <c r="BR2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BS2">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BU2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1251,16 +1251,16 @@
         <v>118</v>
       </c>
       <c r="F3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G3">
         <v>1.47</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J3">
         <v>4.6</v>
@@ -1281,16 +1281,16 @@
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T3">
         <v>2.18</v>
@@ -1299,7 +1299,7 @@
         <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
         <v>3.1</v>
@@ -1308,25 +1308,25 @@
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA3">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE3">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AF3">
         <v>8.199999999999999</v>
@@ -1335,28 +1335,28 @@
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
         <v>44</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN3">
         <v>8.199999999999999</v>
       </c>
       <c r="AO3">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="AP3">
         <v>13.5</v>
@@ -1365,10 +1365,10 @@
         <v>22</v>
       </c>
       <c r="AR3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1404,16 +1404,16 @@
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BF3">
         <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
@@ -1422,13 +1422,13 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM3">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
         <v>3.75</v>
@@ -1437,40 +1437,40 @@
         <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
         <v>110</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="s">
         <v>133</v>
@@ -1493,19 +1493,19 @@
         <v>119</v>
       </c>
       <c r="F4">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G4">
         <v>990</v>
       </c>
       <c r="H4">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1517,10 +1517,10 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>1.26</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1541,10 +1541,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1735,19 +1735,19 @@
         <v>120</v>
       </c>
       <c r="F5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G5">
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I5">
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1977,19 +1977,19 @@
         <v>121</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="I6">
         <v>1.93</v>
       </c>
       <c r="J6">
-        <v>1.05</v>
+        <v>2.14</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2001,7 +2001,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O6">
         <v>1.46</v>
@@ -2219,7 +2219,7 @@
         <v>122</v>
       </c>
       <c r="F7">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G7">
         <v>3.1</v>
@@ -2231,7 +2231,7 @@
         <v>3.1</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="K7">
         <v>3.4</v>
@@ -2264,10 +2264,10 @@
         <v>1.91</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
         <v>1.47</v>
@@ -2461,88 +2461,88 @@
         <v>123</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P8">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="X8">
         <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA8">
         <v>260</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
         <v>29</v>
@@ -2551,7 +2551,7 @@
         <v>150</v>
       </c>
       <c r="AJ8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK8">
         <v>24</v>
@@ -2563,103 +2563,103 @@
         <v>220</v>
       </c>
       <c r="AN8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP8">
         <v>4.8</v>
       </c>
       <c r="AQ8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS8">
         <v>7.6</v>
       </c>
       <c r="AT8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AU8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AV8">
         <v>6.2</v>
       </c>
       <c r="AW8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX8">
         <v>4.2</v>
       </c>
       <c r="AY8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB8">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO8">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ8">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BT8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU8">
         <v>5.2</v>
@@ -2668,13 +2668,13 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
         <v>1.29</v>
@@ -2948,19 +2948,19 @@
         <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J10">
         <v>4.2</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2969,16 +2969,16 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O10">
         <v>1.07</v>
       </c>
       <c r="P10">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R10">
         <v>2</v>
@@ -2996,7 +2996,7 @@
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3047,64 +3047,64 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3187,22 +3187,22 @@
         <v>126</v>
       </c>
       <c r="F11">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>5.5</v>
       </c>
       <c r="J11">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3211,34 +3211,34 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
-        <v>1.34</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="R11">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U11">
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W11">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3429,22 +3429,22 @@
         <v>127</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3453,70 +3453,70 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.27</v>
+        <v>2.92</v>
       </c>
       <c r="O12">
         <v>1.03</v>
       </c>
       <c r="P12">
+        <v>4.2</v>
+      </c>
+      <c r="Q12">
+        <v>1.24</v>
+      </c>
+      <c r="R12">
+        <v>2.42</v>
+      </c>
+      <c r="S12">
+        <v>1.58</v>
+      </c>
+      <c r="T12">
         <v>1.25</v>
       </c>
-      <c r="Q12">
-        <v>1.03</v>
-      </c>
-      <c r="R12">
-        <v>1.25</v>
-      </c>
-      <c r="S12">
-        <v>1.05</v>
-      </c>
-      <c r="T12">
-        <v>1.11</v>
-      </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.74</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X12">
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB12">
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF12">
         <v>1000</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ12">
         <v>1000</v>
@@ -3525,7 +3525,7 @@
         <v>1000</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3534,61 +3534,61 @@
         <v>1000</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3674,7 +3674,7 @@
         <v>2.16</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H13">
         <v>4.4</v>
@@ -3683,7 +3683,7 @@
         <v>4.6</v>
       </c>
       <c r="J13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K13">
         <v>3.2</v>
@@ -3692,10 +3692,10 @@
         <v>1.55</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
         <v>1.6</v>
@@ -3704,25 +3704,25 @@
         <v>1.5</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R13">
         <v>1.17</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13">
         <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X13">
         <v>7.8</v>
@@ -3743,19 +3743,19 @@
         <v>7.6</v>
       </c>
       <c r="AD13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13">
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI13">
         <v>1000</v>
@@ -3773,25 +3773,25 @@
         <v>260</v>
       </c>
       <c r="AN13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS13">
         <v>38</v>
       </c>
       <c r="AT13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU13">
         <v>6.8</v>
@@ -3803,22 +3803,22 @@
         <v>34</v>
       </c>
       <c r="AX13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB13">
         <v>18</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD13">
         <v>34</v>
@@ -3833,10 +3833,10 @@
         <v>42</v>
       </c>
       <c r="BH13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
@@ -3854,22 +3854,22 @@
         <v>4.8</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU13">
         <v>4.7</v>
@@ -3878,7 +3878,7 @@
         <v>50</v>
       </c>
       <c r="BW13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13">
         <v>1000</v>
@@ -3890,7 +3890,7 @@
         <v>55</v>
       </c>
       <c r="CA13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB13" t="s">
         <v>133</v>
@@ -3913,22 +3913,22 @@
         <v>129</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
         <v>990</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3937,22 +3937,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O14">
         <v>1.15</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="R14">
         <v>1.24</v>
       </c>
       <c r="S14">
-        <v>1.98</v>
+        <v>1.14</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4078,55 +4078,55 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4155,19 +4155,19 @@
         <v>130</v>
       </c>
       <c r="F15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G15">
         <v>990</v>
       </c>
       <c r="H15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I15">
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4179,13 +4179,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O15">
         <v>1.39</v>
       </c>
       <c r="P15">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q15">
         <v>1.39</v>
@@ -4203,10 +4203,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4397,25 +4397,25 @@
         <v>131</v>
       </c>
       <c r="F16">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G16">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H16">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>3.85</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M16">
         <v>1.08</v>
@@ -4430,7 +4430,7 @@
         <v>1.78</v>
       </c>
       <c r="Q16">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
         <v>1.29</v>
@@ -4442,19 +4442,19 @@
         <v>2.06</v>
       </c>
       <c r="U16">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V16">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W16">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X16">
         <v>15.5</v>
       </c>
       <c r="Y16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z16">
         <v>70</v>
@@ -4490,7 +4490,7 @@
         <v>17</v>
       </c>
       <c r="AK16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL16">
         <v>55</v>
@@ -4499,7 +4499,7 @@
         <v>210</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO16">
         <v>210</v>
@@ -4511,10 +4511,10 @@
         <v>16.5</v>
       </c>
       <c r="AR16">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS16">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT16">
         <v>6</v>
@@ -4523,10 +4523,10 @@
         <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW16">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX16">
         <v>7.6</v>
@@ -4538,7 +4538,7 @@
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB16">
         <v>13.5</v>
@@ -4547,34 +4547,34 @@
         <v>16</v>
       </c>
       <c r="BD16">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE16">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF16">
         <v>8.800000000000001</v>
       </c>
       <c r="BG16">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH16">
         <v>3.35</v>
       </c>
       <c r="BI16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16">
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN16">
         <v>4.2</v>
@@ -4583,40 +4583,40 @@
         <v>3.15</v>
       </c>
       <c r="BP16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT16">
         <v>10.5</v>
       </c>
       <c r="BU16">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB16" t="s">
         <v>133</v>
@@ -4639,226 +4639,226 @@
         <v>132</v>
       </c>
       <c r="F17">
-        <v>4.2</v>
+        <v>1.23</v>
       </c>
       <c r="G17">
-        <v>5.6</v>
+        <v>990</v>
       </c>
       <c r="H17">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="I17">
-        <v>2.1</v>
+        <v>990</v>
       </c>
       <c r="J17">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="K17">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L17">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
         <v>1.48</v>
       </c>
       <c r="P17">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S17">
         <v>3.85</v>
       </c>
       <c r="T17">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>133</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="138">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
@@ -310,6 +313,9 @@
     <t>22:00:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -358,6 +364,9 @@
     <t>Nacional Potosi</t>
   </si>
   <si>
+    <t>Deportivo La Guaira</t>
+  </si>
+  <si>
     <t>Penarol</t>
   </si>
   <si>
@@ -406,6 +415,9 @@
     <t>The Strongest</t>
   </si>
   <si>
+    <t>Metropolitanos</t>
+  </si>
+  <si>
     <t>Wanderers (Uru)</t>
   </si>
   <si>
@@ -415,7 +427,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 17:29:57</t>
+    <t>2026-08-04 19:37:07</t>
   </si>
 </sst>
 </file>
@@ -747,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -997,34 +1009,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G2">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
         <v>1.24</v>
@@ -1033,37 +1045,37 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
         <v>3</v>
       </c>
       <c r="Q2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R2">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T2">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="X2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y2">
         <v>38</v>
@@ -1072,34 +1084,34 @@
         <v>70</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>410</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK2">
         <v>14</v>
@@ -1111,73 +1123,73 @@
         <v>75</v>
       </c>
       <c r="AN2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2">
         <v>30</v>
       </c>
       <c r="AR2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AS2">
         <v>42</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU2">
         <v>11</v>
       </c>
       <c r="AV2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
         <v>12</v>
       </c>
       <c r="BD2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK2">
         <v>8</v>
@@ -1186,25 +1198,25 @@
         <v>100</v>
       </c>
       <c r="BM2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BT2">
         <v>12</v>
@@ -1213,16 +1225,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1231,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1239,40 +1251,40 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>1.45</v>
       </c>
       <c r="G3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3">
         <v>1.39</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -1281,40 +1293,40 @@
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3">
         <v>3.45</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3">
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3">
         <v>85</v>
       </c>
       <c r="AA3">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
@@ -1326,7 +1338,7 @@
         <v>36</v>
       </c>
       <c r="AE3">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF3">
         <v>8.199999999999999</v>
@@ -1347,19 +1359,19 @@
         <v>16.5</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AN3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="AP3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
         <v>22</v>
@@ -1368,7 +1380,7 @@
         <v>65</v>
       </c>
       <c r="AS3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1398,22 +1410,22 @@
         <v>11</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD3">
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF3">
         <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
@@ -1428,25 +1440,25 @@
         <v>210</v>
       </c>
       <c r="BM3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
         <v>3.75</v>
       </c>
       <c r="BO3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
         <v>12</v>
@@ -1458,22 +1470,22 @@
         <v>110</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>100</v>
       </c>
       <c r="BY3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CA3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1481,34 +1493,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.15</v>
+        <v>2.02</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>8.6</v>
       </c>
       <c r="H4">
-        <v>1.15</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>1.28</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1520,19 +1532,19 @@
         <v>1.26</v>
       </c>
       <c r="O4">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
         <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1541,118 +1553,118 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1715,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1723,40 +1735,40 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>4.5</v>
       </c>
       <c r="H5">
-        <v>1.08</v>
+        <v>1.83</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>1.13</v>
+        <v>2.82</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
         <v>2.26</v>
@@ -1768,13 +1780,13 @@
         <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.63</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1783,118 +1795,118 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1957,7 +1969,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1965,31 +1977,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J6">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2010,7 +2022,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
         <v>1.18</v>
@@ -2025,7 +2037,7 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W6">
         <v>1.01</v>
@@ -2034,25 +2046,25 @@
         <v>1000</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6">
         <v>1000</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6">
         <v>1000</v>
@@ -2064,7 +2076,7 @@
         <v>1000</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2085,58 +2097,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2199,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2207,19 +2219,19 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G7">
         <v>3.1</v>
@@ -2228,16 +2240,16 @@
         <v>2.72</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J7">
         <v>2.96</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2273,7 +2285,7 @@
         <v>1.47</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
@@ -2297,7 +2309,7 @@
         <v>42</v>
       </c>
       <c r="AF7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7">
         <v>16</v>
@@ -2309,7 +2321,7 @@
         <v>65</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7">
         <v>48</v>
@@ -2318,22 +2330,22 @@
         <v>70</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN7">
         <v>55</v>
       </c>
       <c r="AO7">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP7">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7">
         <v>7</v>
       </c>
       <c r="AR7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS7">
         <v>4.6</v>
@@ -2342,43 +2354,43 @@
         <v>3.5</v>
       </c>
       <c r="AU7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX7">
         <v>4.1</v>
       </c>
       <c r="AY7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA7">
+        <v>4.7</v>
+      </c>
+      <c r="BB7">
+        <v>4.7</v>
+      </c>
+      <c r="BC7">
         <v>4.6</v>
-      </c>
-      <c r="BB7">
-        <v>4.6</v>
-      </c>
-      <c r="BC7">
-        <v>4.5</v>
       </c>
       <c r="BD7">
         <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7">
         <v>4.6</v>
       </c>
       <c r="BG7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2441,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2449,82 +2461,82 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="G8">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I8">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
         <v>4.1</v>
       </c>
       <c r="T8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
         <v>1.73</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="X8">
         <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z8">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AA8">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AB8">
         <v>6.8</v>
@@ -2536,10 +2548,10 @@
         <v>32</v>
       </c>
       <c r="AE8">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AF8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
@@ -2548,118 +2560,118 @@
         <v>29</v>
       </c>
       <c r="AI8">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ8">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM8">
         <v>220</v>
       </c>
       <c r="AN8">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AO8">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AP8">
+        <v>5.5</v>
+      </c>
+      <c r="AQ8">
+        <v>6.6</v>
+      </c>
+      <c r="AR8">
+        <v>8.6</v>
+      </c>
+      <c r="AS8">
+        <v>9.6</v>
+      </c>
+      <c r="AT8">
+        <v>4</v>
+      </c>
+      <c r="AU8">
         <v>4.8</v>
       </c>
-      <c r="AQ8">
+      <c r="AV8">
+        <v>7.6</v>
+      </c>
+      <c r="AW8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX8">
+        <v>4.6</v>
+      </c>
+      <c r="AY8">
+        <v>5.1</v>
+      </c>
+      <c r="AZ8">
+        <v>7.4</v>
+      </c>
+      <c r="BA8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8">
+        <v>6.2</v>
+      </c>
+      <c r="BC8">
+        <v>6.6</v>
+      </c>
+      <c r="BD8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8">
+        <v>9.4</v>
+      </c>
+      <c r="BF8">
         <v>5.7</v>
       </c>
-      <c r="AR8">
-        <v>6.8</v>
-      </c>
-      <c r="AS8">
-        <v>7.6</v>
-      </c>
-      <c r="AT8">
-        <v>3.6</v>
-      </c>
-      <c r="AU8">
-        <v>4.2</v>
-      </c>
-      <c r="AV8">
-        <v>6.2</v>
-      </c>
-      <c r="AW8">
-        <v>7.2</v>
-      </c>
-      <c r="AX8">
-        <v>4.2</v>
-      </c>
-      <c r="AY8">
-        <v>4.4</v>
-      </c>
-      <c r="AZ8">
-        <v>6</v>
-      </c>
-      <c r="BA8">
-        <v>7.4</v>
-      </c>
-      <c r="BB8">
-        <v>5.6</v>
-      </c>
-      <c r="BC8">
-        <v>5.9</v>
-      </c>
-      <c r="BD8">
-        <v>6.8</v>
-      </c>
-      <c r="BE8">
-        <v>7.4</v>
-      </c>
-      <c r="BF8">
-        <v>5.1</v>
-      </c>
       <c r="BG8">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI8">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BN8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO8">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BP8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BT8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU8">
         <v>5.2</v>
@@ -2668,13 +2680,13 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2683,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2691,34 +2703,34 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
         <v>1.68</v>
       </c>
       <c r="H9">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2727,28 +2739,28 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q9">
+        <v>1.72</v>
+      </c>
+      <c r="R9">
+        <v>1.34</v>
+      </c>
+      <c r="S9">
+        <v>2.8</v>
+      </c>
+      <c r="T9">
+        <v>1.89</v>
+      </c>
+      <c r="U9">
         <v>1.87</v>
-      </c>
-      <c r="R9">
-        <v>1.35</v>
-      </c>
-      <c r="S9">
-        <v>3.05</v>
-      </c>
-      <c r="T9">
-        <v>1.9</v>
-      </c>
-      <c r="U9">
-        <v>1.9</v>
       </c>
       <c r="V9">
         <v>1.16</v>
@@ -2757,112 +2769,112 @@
         <v>2.46</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z9">
         <v>65</v>
       </c>
       <c r="AA9">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AB9">
         <v>8.6</v>
       </c>
       <c r="AC9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE9">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI9">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK9">
         <v>18</v>
       </c>
       <c r="AL9">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP9">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AR9">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS9">
+        <v>7.4</v>
+      </c>
+      <c r="AT9">
+        <v>4.9</v>
+      </c>
+      <c r="AU9">
+        <v>5.8</v>
+      </c>
+      <c r="AV9">
         <v>6</v>
       </c>
-      <c r="AT9">
-        <v>3.6</v>
-      </c>
-      <c r="AU9">
-        <v>4</v>
-      </c>
-      <c r="AV9">
-        <v>5</v>
-      </c>
       <c r="AW9">
+        <v>7.2</v>
+      </c>
+      <c r="AX9">
+        <v>4.9</v>
+      </c>
+      <c r="AY9">
+        <v>6.2</v>
+      </c>
+      <c r="AZ9">
         <v>5.9</v>
       </c>
-      <c r="AX9">
-        <v>4</v>
-      </c>
-      <c r="AY9">
-        <v>3.9</v>
-      </c>
-      <c r="AZ9">
-        <v>4.9</v>
-      </c>
       <c r="BA9">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB9">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC9">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD9">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE9">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF9">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG9">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2925,7 +2937,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2933,31 +2945,31 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
         <v>4.9</v>
@@ -2981,7 +2993,7 @@
         <v>1.35</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
         <v>1.84</v>
@@ -2990,121 +3002,121 @@
         <v>1.36</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.66</v>
       </c>
       <c r="V10">
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10">
         <v>8.4</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="AQ10">
-        <v>1.14</v>
+        <v>2.06</v>
       </c>
       <c r="AR10">
-        <v>1.14</v>
+        <v>2.06</v>
       </c>
       <c r="AS10">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AT10">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AU10">
-        <v>1.14</v>
+        <v>1.87</v>
       </c>
       <c r="AV10">
-        <v>1.14</v>
+        <v>1.94</v>
       </c>
       <c r="AW10">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AX10">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="AY10">
-        <v>1.14</v>
+        <v>1.89</v>
       </c>
       <c r="AZ10">
-        <v>1.14</v>
+        <v>1.91</v>
       </c>
       <c r="BA10">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="BB10">
-        <v>1.14</v>
+        <v>2.08</v>
       </c>
       <c r="BC10">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="BD10">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="BE10">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BG10">
-        <v>1.14</v>
+        <v>3.3</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3167,7 +3179,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3175,31 +3187,31 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F11">
         <v>1.75</v>
       </c>
       <c r="G11">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
         <v>4.9</v>
@@ -3211,205 +3223,205 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="O11">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q11">
         <v>1.49</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T11">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3417,25 +3429,25 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G12">
         <v>4.6</v>
       </c>
       <c r="H12">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I12">
         <v>1.89</v>
@@ -3453,22 +3465,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="O12">
         <v>1.03</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q12">
         <v>1.24</v>
       </c>
       <c r="R12">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T12">
         <v>1.25</v>
@@ -3483,19 +3495,19 @@
         <v>1.27</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y12">
+        <v>85</v>
+      </c>
+      <c r="Z12">
+        <v>60</v>
+      </c>
+      <c r="AA12">
+        <v>80</v>
+      </c>
+      <c r="AB12">
         <v>950</v>
-      </c>
-      <c r="Z12">
-        <v>32</v>
-      </c>
-      <c r="AA12">
-        <v>36</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
       </c>
       <c r="AC12">
         <v>25</v>
@@ -3507,37 +3519,37 @@
         <v>24</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AH12">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AI12">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO12">
         <v>5.9</v>
       </c>
       <c r="AP12">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AQ12">
         <v>17.5</v>
@@ -3549,7 +3561,7 @@
         <v>15.5</v>
       </c>
       <c r="AT12">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="AU12">
         <v>11.5</v>
@@ -3561,7 +3573,7 @@
         <v>11</v>
       </c>
       <c r="AX12">
-        <v>2.12</v>
+        <v>23</v>
       </c>
       <c r="AY12">
         <v>13.5</v>
@@ -3573,19 +3585,19 @@
         <v>12.5</v>
       </c>
       <c r="BB12">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="BC12">
-        <v>2.12</v>
+        <v>16</v>
       </c>
       <c r="BD12">
         <v>18</v>
       </c>
       <c r="BE12">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="BF12">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12">
         <v>3.15</v>
@@ -3651,7 +3663,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3659,16 +3671,16 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F13">
         <v>2.16</v>
@@ -3680,10 +3692,10 @@
         <v>4.4</v>
       </c>
       <c r="I13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K13">
         <v>3.2</v>
@@ -3692,40 +3704,40 @@
         <v>1.55</v>
       </c>
       <c r="M13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q13">
         <v>2.78</v>
       </c>
       <c r="R13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V13">
         <v>1.28</v>
       </c>
       <c r="W13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X13">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y13">
         <v>11</v>
@@ -3737,46 +3749,46 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AF13">
         <v>12</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AJ13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK13">
         <v>32</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP13">
         <v>7</v>
@@ -3785,7 +3797,7 @@
         <v>9.6</v>
       </c>
       <c r="AR13">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS13">
         <v>38</v>
@@ -3794,19 +3806,19 @@
         <v>6.2</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX13">
         <v>10.5</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13">
         <v>19.5</v>
@@ -3821,58 +3833,58 @@
         <v>19.5</v>
       </c>
       <c r="BD13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE13">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BF13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BG13">
         <v>42</v>
       </c>
       <c r="BH13">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI13">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
         <v>4.8</v>
       </c>
       <c r="BO13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR13">
         <v>46</v>
       </c>
       <c r="BS13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV13">
         <v>50</v>
@@ -3884,7 +3896,7 @@
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>55</v>
@@ -3893,7 +3905,7 @@
         <v>9.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3901,178 +3913,178 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="H14">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="J14">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.28</v>
+        <v>2.46</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P14">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="R14">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4135,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4143,58 +4155,58 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="G15">
-        <v>990</v>
+        <v>2.18</v>
       </c>
       <c r="H15">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>1.46</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
+        <v>2.66</v>
+      </c>
+      <c r="O15">
         <v>1.31</v>
       </c>
-      <c r="O15">
-        <v>1.39</v>
-      </c>
       <c r="P15">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q15">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="R15">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S15">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4206,115 +4218,115 @@
         <v>1.18</v>
       </c>
       <c r="W15">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4371,255 +4383,255 @@
         <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F16">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="G16">
-        <v>1.68</v>
+        <v>990</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>1.21</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>990</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>1.47</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="O16">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P16">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="Q16">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="S16">
-        <v>3.85</v>
+        <v>1.41</v>
       </c>
       <c r="T16">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="W16">
-        <v>2.46</v>
+        <v>1.19</v>
       </c>
       <c r="X16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4627,241 +4639,483 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>1.66</v>
       </c>
       <c r="H17">
-        <v>1.72</v>
+        <v>6.8</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>1.3</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S17">
         <v>3.85</v>
       </c>
       <c r="T17">
+        <v>2.06</v>
+      </c>
+      <c r="U17">
+        <v>1.79</v>
+      </c>
+      <c r="V17">
+        <v>1.14</v>
+      </c>
+      <c r="W17">
+        <v>2.5</v>
+      </c>
+      <c r="X17">
+        <v>15.5</v>
+      </c>
+      <c r="Y17">
+        <v>21</v>
+      </c>
+      <c r="Z17">
+        <v>70</v>
+      </c>
+      <c r="AA17">
+        <v>270</v>
+      </c>
+      <c r="AB17">
+        <v>7.2</v>
+      </c>
+      <c r="AC17">
+        <v>11</v>
+      </c>
+      <c r="AD17">
+        <v>32</v>
+      </c>
+      <c r="AE17">
+        <v>140</v>
+      </c>
+      <c r="AF17">
+        <v>9.4</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>32</v>
+      </c>
+      <c r="AI17">
+        <v>140</v>
+      </c>
+      <c r="AJ17">
+        <v>17</v>
+      </c>
+      <c r="AK17">
+        <v>23</v>
+      </c>
+      <c r="AL17">
+        <v>55</v>
+      </c>
+      <c r="AM17">
+        <v>210</v>
+      </c>
+      <c r="AN17">
+        <v>14</v>
+      </c>
+      <c r="AO17">
+        <v>210</v>
+      </c>
+      <c r="AP17">
+        <v>11</v>
+      </c>
+      <c r="AQ17">
+        <v>16.5</v>
+      </c>
+      <c r="AR17">
+        <v>5.3</v>
+      </c>
+      <c r="AS17">
+        <v>5.6</v>
+      </c>
+      <c r="AT17">
+        <v>6</v>
+      </c>
+      <c r="AU17">
+        <v>7.8</v>
+      </c>
+      <c r="AV17">
+        <v>4.9</v>
+      </c>
+      <c r="AW17">
+        <v>5.5</v>
+      </c>
+      <c r="AX17">
+        <v>7.6</v>
+      </c>
+      <c r="AY17">
+        <v>8.6</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>5.5</v>
+      </c>
+      <c r="BB17">
+        <v>13.5</v>
+      </c>
+      <c r="BC17">
+        <v>16</v>
+      </c>
+      <c r="BD17">
+        <v>5.2</v>
+      </c>
+      <c r="BE17">
+        <v>5.6</v>
+      </c>
+      <c r="BF17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG17">
+        <v>5.6</v>
+      </c>
+      <c r="BH17">
+        <v>3.35</v>
+      </c>
+      <c r="BI17">
+        <v>2.6</v>
+      </c>
+      <c r="BJ17">
+        <v>12</v>
+      </c>
+      <c r="BK17">
+        <v>5.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>10</v>
+      </c>
+      <c r="BN17">
+        <v>4.2</v>
+      </c>
+      <c r="BO17">
+        <v>3.15</v>
+      </c>
+      <c r="BP17">
+        <v>11.5</v>
+      </c>
+      <c r="BQ17">
+        <v>5.5</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>7.8</v>
+      </c>
+      <c r="BT17">
+        <v>10.5</v>
+      </c>
+      <c r="BU17">
+        <v>5.2</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>9</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ17">
+        <v>25</v>
+      </c>
+      <c r="CA17">
+        <v>7.4</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>1.93</v>
+      </c>
+      <c r="I18">
+        <v>2.16</v>
+      </c>
+      <c r="J18">
+        <v>3.1</v>
+      </c>
+      <c r="K18">
+        <v>3.45</v>
+      </c>
+      <c r="L18">
+        <v>1.45</v>
+      </c>
+      <c r="M18">
         <v>1.11</v>
       </c>
-      <c r="U17">
-        <v>1.11</v>
-      </c>
-      <c r="V17">
-        <v>1.01</v>
-      </c>
-      <c r="W17">
+      <c r="N18">
+        <v>2.4</v>
+      </c>
+      <c r="O18">
+        <v>1.48</v>
+      </c>
+      <c r="P18">
+        <v>1.55</v>
+      </c>
+      <c r="Q18">
+        <v>2.44</v>
+      </c>
+      <c r="R18">
+        <v>1.2</v>
+      </c>
+      <c r="S18">
         <v>1.05</v>
       </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17">
-        <v>1.01</v>
-      </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
-      <c r="AT17">
-        <v>1.01</v>
-      </c>
-      <c r="AU17">
-        <v>1.01</v>
-      </c>
-      <c r="AV17">
-        <v>1.01</v>
-      </c>
-      <c r="AW17">
-        <v>1.01</v>
-      </c>
-      <c r="AX17">
-        <v>1.01</v>
-      </c>
-      <c r="AY17">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17">
-        <v>1.01</v>
-      </c>
-      <c r="BA17">
-        <v>1.01</v>
-      </c>
-      <c r="BB17">
-        <v>1.01</v>
-      </c>
-      <c r="BC17">
-        <v>1.01</v>
-      </c>
-      <c r="BD17">
-        <v>1.01</v>
-      </c>
-      <c r="BE17">
-        <v>1.01</v>
-      </c>
-      <c r="BF17">
-        <v>1.01</v>
-      </c>
-      <c r="BG17">
-        <v>1.01</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.04</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.04</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
-        <v>1.04</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>1.04</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.04</v>
-      </c>
-      <c r="BT17">
-        <v>1000</v>
-      </c>
-      <c r="BU17">
-        <v>1.04</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.04</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.04</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>1.04</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>133</v>
+      <c r="T18">
+        <v>2.14</v>
+      </c>
+      <c r="U18">
+        <v>1.74</v>
+      </c>
+      <c r="V18">
+        <v>1.86</v>
+      </c>
+      <c r="W18">
+        <v>1.21</v>
+      </c>
+      <c r="X18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y18">
+        <v>7.2</v>
+      </c>
+      <c r="Z18">
+        <v>12</v>
+      </c>
+      <c r="AA18">
+        <v>27</v>
+      </c>
+      <c r="AB18">
+        <v>13.5</v>
+      </c>
+      <c r="AC18">
+        <v>8</v>
+      </c>
+      <c r="AD18">
+        <v>12</v>
+      </c>
+      <c r="AE18">
+        <v>29</v>
+      </c>
+      <c r="AF18">
+        <v>50</v>
+      </c>
+      <c r="AG18">
+        <v>22</v>
+      </c>
+      <c r="AH18">
+        <v>26</v>
+      </c>
+      <c r="AI18">
+        <v>70</v>
+      </c>
+      <c r="AJ18">
+        <v>170</v>
+      </c>
+      <c r="AK18">
+        <v>110</v>
+      </c>
+      <c r="AL18">
+        <v>130</v>
+      </c>
+      <c r="AM18">
+        <v>230</v>
+      </c>
+      <c r="AN18">
+        <v>170</v>
+      </c>
+      <c r="AO18">
+        <v>25</v>
+      </c>
+      <c r="AP18">
+        <v>4.4</v>
+      </c>
+      <c r="AQ18">
+        <v>3.75</v>
+      </c>
+      <c r="AR18">
+        <v>4.8</v>
+      </c>
+      <c r="AS18">
+        <v>6</v>
+      </c>
+      <c r="AT18">
+        <v>5</v>
+      </c>
+      <c r="AU18">
+        <v>4</v>
+      </c>
+      <c r="AV18">
+        <v>4.8</v>
+      </c>
+      <c r="AW18">
+        <v>6.2</v>
+      </c>
+      <c r="AX18">
+        <v>6.6</v>
+      </c>
+      <c r="AY18">
+        <v>5.8</v>
+      </c>
+      <c r="AZ18">
+        <v>6</v>
+      </c>
+      <c r="BA18">
+        <v>7.2</v>
+      </c>
+      <c r="BB18">
+        <v>7.6</v>
+      </c>
+      <c r="BC18">
+        <v>7.4</v>
+      </c>
+      <c r="BD18">
+        <v>7.4</v>
+      </c>
+      <c r="BE18">
+        <v>7.6</v>
+      </c>
+      <c r="BF18">
+        <v>7.6</v>
+      </c>
+      <c r="BG18">
+        <v>6</v>
+      </c>
+      <c r="BH18">
+        <v>3.2</v>
+      </c>
+      <c r="BI18">
+        <v>2.3</v>
+      </c>
+      <c r="BJ18">
+        <v>14</v>
+      </c>
+      <c r="BK18">
+        <v>3.75</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>5</v>
+      </c>
+      <c r="BN18">
+        <v>9.6</v>
+      </c>
+      <c r="BO18">
+        <v>3.3</v>
+      </c>
+      <c r="BP18">
+        <v>60</v>
+      </c>
+      <c r="BQ18">
+        <v>4.7</v>
+      </c>
+      <c r="BR18">
+        <v>85</v>
+      </c>
+      <c r="BS18">
+        <v>4.8</v>
+      </c>
+      <c r="BT18">
+        <v>5.2</v>
+      </c>
+      <c r="BU18">
+        <v>2.58</v>
+      </c>
+      <c r="BV18">
+        <v>19.5</v>
+      </c>
+      <c r="BW18">
+        <v>4</v>
+      </c>
+      <c r="BX18">
+        <v>48</v>
+      </c>
+      <c r="BY18">
+        <v>4.6</v>
+      </c>
+      <c r="BZ18">
+        <v>50</v>
+      </c>
+      <c r="CA18">
+        <v>4.6</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -427,7 +427,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 19:37:07</t>
+    <t>2026-08-04 21:44:26</t>
   </si>
 </sst>
 </file>
@@ -1021,220 +1021,220 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="G2">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
+        <v>2.6</v>
+      </c>
+      <c r="O2">
+        <v>1.59</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.8</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>6</v>
+      </c>
+      <c r="T2">
+        <v>2.6</v>
+      </c>
+      <c r="U2">
+        <v>1.53</v>
+      </c>
+      <c r="V2">
+        <v>1.18</v>
+      </c>
+      <c r="W2">
+        <v>2.22</v>
+      </c>
+      <c r="X2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y2">
+        <v>17</v>
+      </c>
+      <c r="Z2">
+        <v>65</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>6.2</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>8.6</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>440</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2">
+        <v>4.4</v>
+      </c>
+      <c r="AR2">
+        <v>36</v>
+      </c>
+      <c r="AS2">
+        <v>140</v>
+      </c>
+      <c r="AT2">
+        <v>5.3</v>
+      </c>
+      <c r="AU2">
+        <v>1.91</v>
+      </c>
+      <c r="AV2">
+        <v>21</v>
+      </c>
+      <c r="AW2">
+        <v>70</v>
+      </c>
+      <c r="AX2">
+        <v>1.9</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>20</v>
+      </c>
+      <c r="BA2">
+        <v>130</v>
+      </c>
+      <c r="BB2">
+        <v>14</v>
+      </c>
+      <c r="BC2">
+        <v>20</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>250</v>
+      </c>
+      <c r="BF2">
+        <v>2.46</v>
+      </c>
+      <c r="BG2">
+        <v>2.44</v>
+      </c>
+      <c r="BH2">
+        <v>1.38</v>
+      </c>
+      <c r="BI2">
+        <v>1.33</v>
+      </c>
+      <c r="BJ2">
+        <v>950</v>
+      </c>
+      <c r="BK2">
+        <v>20</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5.7</v>
+      </c>
+      <c r="BN2">
         <v>6.8</v>
       </c>
-      <c r="O2">
-        <v>1.15</v>
-      </c>
-      <c r="P2">
-        <v>3</v>
-      </c>
-      <c r="Q2">
-        <v>1.46</v>
-      </c>
-      <c r="R2">
-        <v>1.79</v>
-      </c>
-      <c r="S2">
-        <v>2.16</v>
-      </c>
-      <c r="T2">
-        <v>1.65</v>
-      </c>
-      <c r="U2">
-        <v>2.32</v>
-      </c>
-      <c r="V2">
-        <v>1.15</v>
-      </c>
-      <c r="W2">
-        <v>3.05</v>
-      </c>
-      <c r="X2">
-        <v>38</v>
-      </c>
-      <c r="Y2">
-        <v>38</v>
-      </c>
-      <c r="Z2">
-        <v>70</v>
-      </c>
-      <c r="AA2">
-        <v>410</v>
-      </c>
-      <c r="AB2">
-        <v>14.5</v>
-      </c>
-      <c r="AC2">
-        <v>13.5</v>
-      </c>
-      <c r="AD2">
-        <v>28</v>
-      </c>
-      <c r="AE2">
-        <v>80</v>
-      </c>
-      <c r="AF2">
-        <v>12</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>70</v>
-      </c>
-      <c r="AJ2">
-        <v>14.5</v>
-      </c>
-      <c r="AK2">
-        <v>14</v>
-      </c>
-      <c r="AL2">
-        <v>25</v>
-      </c>
-      <c r="AM2">
-        <v>75</v>
-      </c>
-      <c r="AN2">
-        <v>5.1</v>
-      </c>
-      <c r="AO2">
-        <v>65</v>
-      </c>
-      <c r="AP2">
-        <v>28</v>
-      </c>
-      <c r="AQ2">
-        <v>30</v>
-      </c>
-      <c r="AR2">
-        <v>50</v>
-      </c>
-      <c r="AS2">
-        <v>42</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>11</v>
-      </c>
-      <c r="AV2">
-        <v>23</v>
-      </c>
-      <c r="AW2">
-        <v>60</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>9</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
-      <c r="BA2">
-        <v>50</v>
-      </c>
-      <c r="BB2">
-        <v>12.5</v>
-      </c>
-      <c r="BC2">
-        <v>12</v>
-      </c>
-      <c r="BD2">
-        <v>22</v>
-      </c>
-      <c r="BE2">
-        <v>55</v>
-      </c>
-      <c r="BF2">
-        <v>4.3</v>
-      </c>
-      <c r="BG2">
-        <v>38</v>
-      </c>
-      <c r="BH2">
-        <v>6.4</v>
-      </c>
-      <c r="BI2">
-        <v>4.8</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
-      <c r="BK2">
-        <v>8</v>
-      </c>
-      <c r="BL2">
-        <v>100</v>
-      </c>
-      <c r="BM2">
-        <v>7.8</v>
-      </c>
-      <c r="BN2">
-        <v>4.5</v>
-      </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BP2">
-        <v>8.4</v>
+        <v>470</v>
       </c>
       <c r="BQ2">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BR2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BU2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BV2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1263,175 +1263,175 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="G3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="R3">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z3">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AA3">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE3">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AF3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK3">
         <v>16.5</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>220</v>
       </c>
       <c r="AN3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO3">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="AP3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW3">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA3">
         <v>75</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
         <v>14.5</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="BF3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BI3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>8.199999999999999</v>
@@ -1440,28 +1440,28 @@
         <v>210</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>140</v>
       </c>
       <c r="BN3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BU3">
         <v>7.8</v>
@@ -1470,19 +1470,19 @@
         <v>110</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BX3">
         <v>100</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>137</v>
@@ -1511,7 +1511,7 @@
         <v>8.6</v>
       </c>
       <c r="H4">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
         <v>11</v>
@@ -1532,7 +1532,7 @@
         <v>1.26</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1556,7 +1556,7 @@
         <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
         <v>950</v>
@@ -1750,7 +1750,7 @@
         <v>1.81</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>1.83</v>
@@ -1780,7 +1780,7 @@
         <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1798,7 +1798,7 @@
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
         <v>950</v>
@@ -1989,22 +1989,22 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="I6">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2013,13 +2013,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.28</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
@@ -2037,10 +2037,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2073,7 +2073,7 @@
         <v>1000</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6">
         <v>500</v>
@@ -2097,58 +2097,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AQ6">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AR6">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AS6">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AT6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AU6">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AV6">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AW6">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AX6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AY6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AZ6">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BA6">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BB6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BD6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BE6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BF6">
         <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2231,22 +2231,22 @@
         <v>125</v>
       </c>
       <c r="F7">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="G7">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H7">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="I7">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="J7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.43</v>
@@ -2255,10 +2255,10 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P7">
         <v>1.64</v>
@@ -2267,52 +2267,52 @@
         <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA7">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB7">
         <v>11.5</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AF7">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AH7">
         <v>24</v>
@@ -2321,10 +2321,10 @@
         <v>65</v>
       </c>
       <c r="AJ7">
+        <v>85</v>
+      </c>
+      <c r="AK7">
         <v>60</v>
-      </c>
-      <c r="AK7">
-        <v>48</v>
       </c>
       <c r="AL7">
         <v>70</v>
@@ -2333,64 +2333,64 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AO7">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AP7">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR7">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AS7">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT7">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU7">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
         <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX7">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="AY7">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="BA7">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB7">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BC7">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE7">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF7">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BG7">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2402,46 +2402,46 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
+        <v>4.9</v>
+      </c>
+      <c r="BN7">
+        <v>7.6</v>
+      </c>
+      <c r="BO7">
         <v>4.8</v>
       </c>
-      <c r="BN7">
-        <v>6.8</v>
-      </c>
-      <c r="BO7">
+      <c r="BP7">
+        <v>36</v>
+      </c>
+      <c r="BQ7">
         <v>4.4</v>
       </c>
-      <c r="BP7">
-        <v>32</v>
-      </c>
-      <c r="BQ7">
-        <v>4.2</v>
-      </c>
       <c r="BR7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BW7">
         <v>4.2</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BY7">
         <v>4.5</v>
@@ -2473,46 +2473,46 @@
         <v>126</v>
       </c>
       <c r="F8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
         <v>2.16</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T8">
         <v>2.14</v>
@@ -2524,13 +2524,13 @@
         <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z8">
         <v>160</v>
@@ -2542,16 +2542,16 @@
         <v>6.8</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE8">
         <v>160</v>
       </c>
       <c r="AF8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
@@ -2563,115 +2563,115 @@
         <v>160</v>
       </c>
       <c r="AJ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL8">
         <v>120</v>
       </c>
       <c r="AM8">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO8">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP8">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AU8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AV8">
         <v>7.6</v>
       </c>
       <c r="AW8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX8">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY8">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8">
         <v>7.4</v>
       </c>
       <c r="BA8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB8">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BC8">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="BN8">
         <v>4.1</v>
       </c>
       <c r="BO8">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ8">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR8">
         <v>34</v>
       </c>
       <c r="BS8">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU8">
         <v>5.2</v>
@@ -2680,13 +2680,13 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>2.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>5.4</v>
       </c>
       <c r="I9">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>3.7</v>
       </c>
       <c r="K9">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2739,31 +2739,31 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
         <v>1.93</v>
       </c>
       <c r="Q9">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="T9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
         <v>1.87</v>
       </c>
       <c r="V9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
         <v>2.46</v>
@@ -2960,10 +2960,10 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I10">
         <v>3.5</v>
@@ -2972,7 +2972,7 @@
         <v>4.3</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2981,142 +2981,142 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
         <v>1.35</v>
       </c>
       <c r="R10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="U10">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="V10">
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X10">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Y10">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="Z10">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA10">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AB10">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AC10">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="AD10">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF10">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AG10">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AI10">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AJ10">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AL10">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>46</v>
       </c>
       <c r="AN10">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AP10">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AQ10">
-        <v>2.06</v>
+        <v>16</v>
       </c>
       <c r="AR10">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="AS10">
-        <v>2.04</v>
+        <v>7.2</v>
       </c>
       <c r="AT10">
-        <v>2.04</v>
+        <v>18.5</v>
       </c>
       <c r="AU10">
-        <v>1.87</v>
+        <v>11</v>
       </c>
       <c r="AV10">
-        <v>1.94</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>2.04</v>
+        <v>14.5</v>
       </c>
       <c r="AX10">
-        <v>2.02</v>
+        <v>18.5</v>
       </c>
       <c r="AY10">
-        <v>1.89</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>1.91</v>
+        <v>12</v>
       </c>
       <c r="BA10">
-        <v>2.04</v>
+        <v>24</v>
       </c>
       <c r="BB10">
-        <v>2.08</v>
+        <v>14.5</v>
       </c>
       <c r="BC10">
-        <v>1.98</v>
+        <v>16</v>
       </c>
       <c r="BD10">
-        <v>2.02</v>
+        <v>18.5</v>
       </c>
       <c r="BE10">
-        <v>2.04</v>
+        <v>32</v>
       </c>
       <c r="BF10">
-        <v>1.93</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>3.3</v>
+        <v>11.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3202,19 +3202,19 @@
         <v>1.75</v>
       </c>
       <c r="G11">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H11">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3223,28 +3223,28 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="O11">
         <v>1.14</v>
       </c>
       <c r="P11">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
         <v>1.49</v>
       </c>
       <c r="R11">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
         <v>2.26</v>
       </c>
       <c r="T11">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U11">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
         <v>1.25</v>
@@ -3307,55 +3307,55 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11">
+        <v>1.97</v>
+      </c>
+      <c r="AR11">
+        <v>1.24</v>
+      </c>
+      <c r="AS11">
+        <v>1.24</v>
+      </c>
+      <c r="AT11">
+        <v>1.2</v>
+      </c>
+      <c r="AU11">
+        <v>1.21</v>
+      </c>
+      <c r="AV11">
+        <v>1.23</v>
+      </c>
+      <c r="AW11">
+        <v>1.24</v>
+      </c>
+      <c r="AX11">
+        <v>1.22</v>
+      </c>
+      <c r="AY11">
+        <v>1.21</v>
+      </c>
+      <c r="AZ11">
+        <v>1.22</v>
+      </c>
+      <c r="BA11">
         <v>1.25</v>
       </c>
-      <c r="AR11">
-        <v>1.25</v>
-      </c>
-      <c r="AS11">
-        <v>1.26</v>
-      </c>
-      <c r="AT11">
-        <v>1.22</v>
-      </c>
-      <c r="AU11">
-        <v>1.23</v>
-      </c>
-      <c r="AV11">
-        <v>1.25</v>
-      </c>
-      <c r="AW11">
-        <v>1.26</v>
-      </c>
-      <c r="AX11">
-        <v>1.23</v>
-      </c>
-      <c r="AY11">
-        <v>1.22</v>
-      </c>
-      <c r="AZ11">
+      <c r="BB11">
         <v>1.24</v>
       </c>
-      <c r="BA11">
-        <v>1.26</v>
-      </c>
-      <c r="BB11">
-        <v>1.25</v>
-      </c>
       <c r="BC11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BD11">
         <v>1.24</v>
       </c>
       <c r="BE11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG11">
         <v>1.55</v>
@@ -3441,22 +3441,22 @@
         <v>130</v>
       </c>
       <c r="F12">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H12">
         <v>1.75</v>
       </c>
       <c r="I12">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3465,34 +3465,34 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="O12">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q12">
         <v>1.24</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S12">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T12">
         <v>1.25</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W12">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X12">
         <v>950</v>
@@ -3525,7 +3525,7 @@
         <v>65</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>36</v>
@@ -3549,7 +3549,7 @@
         <v>5.9</v>
       </c>
       <c r="AP12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AQ12">
         <v>17.5</v>
@@ -3573,7 +3573,7 @@
         <v>11</v>
       </c>
       <c r="AX12">
-        <v>23</v>
+        <v>2.94</v>
       </c>
       <c r="AY12">
         <v>13.5</v>
@@ -3585,7 +3585,7 @@
         <v>12.5</v>
       </c>
       <c r="BB12">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BC12">
         <v>16</v>
@@ -3683,7 +3683,7 @@
         <v>131</v>
       </c>
       <c r="F13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G13">
         <v>2.22</v>
@@ -3707,7 +3707,7 @@
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O13">
         <v>1.59</v>
@@ -3728,7 +3728,7 @@
         <v>2.28</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
         <v>1.28</v>
@@ -3737,31 +3737,31 @@
         <v>1.82</v>
       </c>
       <c r="X13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>11</v>
       </c>
       <c r="Z13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13">
         <v>19</v>
       </c>
       <c r="AE13">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AF13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3770,7 +3770,7 @@
         <v>28</v>
       </c>
       <c r="AI13">
-        <v>530</v>
+        <v>110</v>
       </c>
       <c r="AJ13">
         <v>28</v>
@@ -3779,22 +3779,22 @@
         <v>32</v>
       </c>
       <c r="AL13">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO13">
-        <v>490</v>
+        <v>130</v>
       </c>
       <c r="AP13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR13">
         <v>22</v>
@@ -3809,7 +3809,7 @@
         <v>7</v>
       </c>
       <c r="AV13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW13">
         <v>38</v>
@@ -3821,25 +3821,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA13">
         <v>40</v>
       </c>
       <c r="BB13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BC13">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BD13">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BE13">
         <v>110</v>
       </c>
       <c r="BF13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG13">
         <v>42</v>
@@ -3925,166 +3925,166 @@
         <v>132</v>
       </c>
       <c r="F14">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G14">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="I14">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="Q14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S14">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="T14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U14">
         <v>2.58</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="X14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y14">
         <v>19</v>
       </c>
       <c r="Z14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA14">
-        <v>260</v>
+        <v>44</v>
       </c>
       <c r="AB14">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AC14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE14">
+        <v>28</v>
+      </c>
+      <c r="AF14">
+        <v>22</v>
+      </c>
+      <c r="AG14">
+        <v>13.5</v>
+      </c>
+      <c r="AH14">
+        <v>15.5</v>
+      </c>
+      <c r="AI14">
         <v>34</v>
       </c>
-      <c r="AF14">
-        <v>18</v>
-      </c>
-      <c r="AG14">
-        <v>12</v>
-      </c>
-      <c r="AH14">
-        <v>16</v>
-      </c>
-      <c r="AI14">
-        <v>38</v>
-      </c>
       <c r="AJ14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL14">
         <v>30</v>
       </c>
       <c r="AM14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO14">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AP14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR14">
         <v>5.9</v>
       </c>
       <c r="AS14">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU14">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV14">
         <v>5</v>
       </c>
       <c r="AW14">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX14">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AY14">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA14">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC14">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BE14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF14">
         <v>4.9</v>
       </c>
       <c r="BG14">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4170,7 +4170,7 @@
         <v>1.84</v>
       </c>
       <c r="G15">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H15">
         <v>3.9</v>
@@ -4182,7 +4182,7 @@
         <v>3.2</v>
       </c>
       <c r="K15">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L15">
         <v>1.37</v>
@@ -4200,7 +4200,7 @@
         <v>1.56</v>
       </c>
       <c r="Q15">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="R15">
         <v>1.18</v>
@@ -4218,7 +4218,7 @@
         <v>1.18</v>
       </c>
       <c r="W15">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="X15">
         <v>950</v>
@@ -4236,7 +4236,7 @@
         <v>950</v>
       </c>
       <c r="AC15">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD15">
         <v>950</v>
@@ -4275,55 +4275,55 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AQ15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AR15">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AS15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AU15">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AV15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AW15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AX15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AY15">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AZ15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BA15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BB15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BC15">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BD15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BE15">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF15">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG15">
         <v>1.55</v>
@@ -4409,58 +4409,58 @@
         <v>134</v>
       </c>
       <c r="F16">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>1.8</v>
       </c>
       <c r="H16">
-        <v>1.21</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
         <v>990</v>
       </c>
       <c r="J16">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="O16">
         <v>1.39</v>
       </c>
       <c r="P16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
         <v>1.14</v>
       </c>
       <c r="S16">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W16">
-        <v>1.19</v>
+        <v>2.24</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4475,7 +4475,7 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16">
         <v>1000</v>
@@ -4529,7 +4529,7 @@
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU16">
         <v>1.01</v>
@@ -4654,13 +4654,13 @@
         <v>1.61</v>
       </c>
       <c r="G17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>3.85</v>
@@ -4669,7 +4669,7 @@
         <v>4</v>
       </c>
       <c r="L17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M17">
         <v>1.08</v>
@@ -4678,31 +4678,31 @@
         <v>3.25</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
         <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
         <v>3.85</v>
       </c>
       <c r="T17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U17">
         <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W17">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X17">
         <v>15.5</v>
@@ -4720,7 +4720,7 @@
         <v>7.2</v>
       </c>
       <c r="AC17">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>32</v>
@@ -4729,7 +4729,7 @@
         <v>140</v>
       </c>
       <c r="AF17">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG17">
         <v>12</v>
@@ -4765,10 +4765,10 @@
         <v>16.5</v>
       </c>
       <c r="AR17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS17">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT17">
         <v>6</v>
@@ -4777,10 +4777,10 @@
         <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX17">
         <v>7.6</v>
@@ -4792,7 +4792,7 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB17">
         <v>13.5</v>
@@ -4801,16 +4801,16 @@
         <v>16</v>
       </c>
       <c r="BD17">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE17">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF17">
         <v>8.800000000000001</v>
       </c>
       <c r="BG17">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH17">
         <v>3.35</v>
@@ -4893,22 +4893,22 @@
         <v>136</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H18">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I18">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J18">
         <v>3.1</v>
       </c>
       <c r="K18">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L18">
         <v>1.45</v>
@@ -4923,10 +4923,10 @@
         <v>1.48</v>
       </c>
       <c r="P18">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q18">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R18">
         <v>1.2</v>
@@ -4935,16 +4935,16 @@
         <v>1.05</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
         <v>1.74</v>
       </c>
       <c r="V18">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W18">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X18">
         <v>9.800000000000001</v>
@@ -4953,109 +4953,109 @@
         <v>7.2</v>
       </c>
       <c r="Z18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA18">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC18">
         <v>8</v>
       </c>
       <c r="AD18">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE18">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AF18">
         <v>50</v>
       </c>
       <c r="AG18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI18">
         <v>70</v>
       </c>
       <c r="AJ18">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AK18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL18">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM18">
         <v>230</v>
       </c>
       <c r="AN18">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ18">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AR18">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS18">
+        <v>5.4</v>
+      </c>
+      <c r="AT18">
+        <v>4.7</v>
+      </c>
+      <c r="AU18">
         <v>6</v>
       </c>
-      <c r="AT18">
-        <v>5</v>
-      </c>
-      <c r="AU18">
-        <v>4</v>
-      </c>
       <c r="AV18">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW18">
+        <v>9</v>
+      </c>
+      <c r="AX18">
+        <v>5.7</v>
+      </c>
+      <c r="AY18">
+        <v>5.1</v>
+      </c>
+      <c r="AZ18">
+        <v>5.3</v>
+      </c>
+      <c r="BA18">
+        <v>6</v>
+      </c>
+      <c r="BB18">
+        <v>6.4</v>
+      </c>
+      <c r="BC18">
         <v>6.2</v>
       </c>
-      <c r="AX18">
+      <c r="BD18">
+        <v>6.2</v>
+      </c>
+      <c r="BE18">
         <v>6.6</v>
       </c>
-      <c r="AY18">
-        <v>5.8</v>
-      </c>
-      <c r="AZ18">
-        <v>6</v>
-      </c>
-      <c r="BA18">
-        <v>7.2</v>
-      </c>
-      <c r="BB18">
-        <v>7.6</v>
-      </c>
-      <c r="BC18">
-        <v>7.4</v>
-      </c>
-      <c r="BD18">
-        <v>7.4</v>
-      </c>
-      <c r="BE18">
-        <v>7.6</v>
-      </c>
       <c r="BF18">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BH18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI18">
         <v>2.3</v>
@@ -5064,37 +5064,37 @@
         <v>14</v>
       </c>
       <c r="BK18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP18">
         <v>60</v>
       </c>
       <c r="BQ18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR18">
         <v>85</v>
       </c>
       <c r="BS18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT18">
         <v>5.2</v>
       </c>
       <c r="BU18">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BV18">
         <v>19.5</v>
@@ -5103,10 +5103,10 @@
         <v>4</v>
       </c>
       <c r="BX18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ18">
         <v>50</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="135">
   <si>
     <t>League</t>
   </si>
@@ -256,21 +256,21 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>Chinese League 2</t>
-  </si>
-  <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
-    <t>Icelandic Urvalsdeild</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -283,9 +283,6 @@
     <t>2026-08-05</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>01:20:00</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>23:25:00</t>
   </si>
   <si>
-    <t>Guabira</t>
-  </si>
-  <si>
     <t>Millonarios</t>
   </si>
   <si>
@@ -376,9 +370,6 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
     <t>Deportivo Pasto</t>
   </si>
   <si>
@@ -427,7 +418,7 @@
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>2026-08-04 21:44:26</t>
+    <t>2026-08-04 23:50:59</t>
   </si>
 </sst>
 </file>
@@ -759,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1015,82 +1006,82 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F2">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>180</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>730</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>55</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>70</v>
       </c>
       <c r="L2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.22</v>
+        <v>50</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1099,142 +1090,142 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM2">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="AR2">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>140</v>
+        <v>19.5</v>
       </c>
       <c r="AT2">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AU2">
-        <v>1.91</v>
+        <v>26</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>70</v>
+        <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BA2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BC2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE2">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>2.46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="BH2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1243,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1257,240 +1248,240 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F3">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="G3">
-        <v>1.43</v>
+        <v>8.6</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>4.9</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z3">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA3">
+        <v>900</v>
+      </c>
+      <c r="AB3">
+        <v>950</v>
+      </c>
+      <c r="AC3">
+        <v>42</v>
+      </c>
+      <c r="AD3">
+        <v>950</v>
+      </c>
+      <c r="AE3">
         <v>500</v>
       </c>
-      <c r="AB3">
-        <v>7.6</v>
-      </c>
-      <c r="AC3">
-        <v>12</v>
-      </c>
-      <c r="AD3">
-        <v>38</v>
-      </c>
-      <c r="AE3">
-        <v>190</v>
-      </c>
       <c r="AF3">
-        <v>7.6</v>
+        <v>500</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI3">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
-        <v>11.5</v>
+        <v>900</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM3">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>7.2</v>
+        <v>600</v>
       </c>
       <c r="AO3">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="AP3">
-        <v>15</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3">
-        <v>25</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
-        <v>70</v>
+        <v>1.23</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>1.24</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>1.22</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>1.14</v>
       </c>
       <c r="AV3">
-        <v>32</v>
+        <v>1.22</v>
       </c>
       <c r="AW3">
-        <v>18</v>
+        <v>1.24</v>
       </c>
       <c r="AX3">
-        <v>7</v>
+        <v>1.23</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>1.22</v>
       </c>
       <c r="BA3">
-        <v>75</v>
+        <v>1.24</v>
       </c>
       <c r="BB3">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="BC3">
-        <v>14.5</v>
+        <v>1.24</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>1.24</v>
       </c>
       <c r="BE3">
-        <v>120</v>
+        <v>1.24</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="BG3">
-        <v>140</v>
+        <v>1.55</v>
       </c>
       <c r="BH3">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>140</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>88</v>
@@ -1499,52 +1490,52 @@
         <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="G4">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N4">
         <v>1.26</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="P4">
         <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>2.66</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1553,10 +1544,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>950</v>
@@ -1604,7 +1595,7 @@
         <v>500</v>
       </c>
       <c r="AM4">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN4">
         <v>600</v>
@@ -1613,52 +1604,52 @@
         <v>600</v>
       </c>
       <c r="AP4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4">
+        <v>1.2</v>
+      </c>
+      <c r="AR4">
+        <v>1.21</v>
+      </c>
+      <c r="AS4">
         <v>1.22</v>
       </c>
-      <c r="AR4">
-        <v>1.23</v>
-      </c>
-      <c r="AS4">
-        <v>1.24</v>
-      </c>
       <c r="AT4">
+        <v>1.2</v>
+      </c>
+      <c r="AU4">
+        <v>1.13</v>
+      </c>
+      <c r="AV4">
+        <v>1.21</v>
+      </c>
+      <c r="AW4">
         <v>1.22</v>
       </c>
-      <c r="AU4">
-        <v>1.14</v>
-      </c>
-      <c r="AV4">
+      <c r="AX4">
+        <v>1.21</v>
+      </c>
+      <c r="AY4">
+        <v>1.21</v>
+      </c>
+      <c r="AZ4">
+        <v>1.2</v>
+      </c>
+      <c r="BA4">
         <v>1.22</v>
       </c>
-      <c r="AW4">
-        <v>1.24</v>
-      </c>
-      <c r="AX4">
-        <v>1.23</v>
-      </c>
-      <c r="AY4">
+      <c r="BB4">
         <v>1.22</v>
       </c>
-      <c r="AZ4">
+      <c r="BC4">
         <v>1.22</v>
       </c>
-      <c r="BA4">
-        <v>1.24</v>
-      </c>
-      <c r="BB4">
-        <v>1.24</v>
-      </c>
-      <c r="BC4">
-        <v>1.24</v>
-      </c>
       <c r="BD4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BE4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF4">
         <v>1.55</v>
@@ -1721,18 +1712,18 @@
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>88</v>
@@ -1741,52 +1732,52 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>4.7</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>990</v>
       </c>
       <c r="H5">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>1.89</v>
       </c>
       <c r="J5">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>19</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="O5">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
-        <v>2.66</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>1.05</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1795,10 +1786,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="W5">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>950</v>
@@ -1816,7 +1807,7 @@
         <v>950</v>
       </c>
       <c r="AC5">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AD5">
         <v>950</v>
@@ -1837,76 +1828,76 @@
         <v>500</v>
       </c>
       <c r="AJ5">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AK5">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AL5">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AM5">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AN5">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AR5">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AS5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AT5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AU5">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AV5">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AW5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AX5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AY5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AZ5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BA5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BB5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BD5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BE5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF5">
         <v>1.55</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1963,246 +1954,246 @@
         <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F6">
+        <v>3.35</v>
+      </c>
+      <c r="G6">
+        <v>3.8</v>
+      </c>
+      <c r="H6">
+        <v>2.34</v>
+      </c>
+      <c r="I6">
+        <v>2.56</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>3.5</v>
+      </c>
+      <c r="L6">
+        <v>1.43</v>
+      </c>
+      <c r="M6">
+        <v>1.1</v>
+      </c>
+      <c r="N6">
+        <v>2.88</v>
+      </c>
+      <c r="O6">
+        <v>1.44</v>
+      </c>
+      <c r="P6">
+        <v>1.64</v>
+      </c>
+      <c r="Q6">
+        <v>2.3</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>4.4</v>
+      </c>
+      <c r="T6">
+        <v>1.92</v>
+      </c>
+      <c r="U6">
+        <v>1.92</v>
+      </c>
+      <c r="V6">
+        <v>1.64</v>
+      </c>
+      <c r="W6">
+        <v>1.36</v>
+      </c>
+      <c r="X6">
+        <v>12.5</v>
+      </c>
+      <c r="Y6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z6">
+        <v>18</v>
+      </c>
+      <c r="AA6">
+        <v>44</v>
+      </c>
+      <c r="AB6">
+        <v>11.5</v>
+      </c>
+      <c r="AC6">
+        <v>8.4</v>
+      </c>
+      <c r="AD6">
+        <v>12</v>
+      </c>
+      <c r="AE6">
+        <v>34</v>
+      </c>
+      <c r="AF6">
+        <v>29</v>
+      </c>
+      <c r="AG6">
+        <v>19</v>
+      </c>
+      <c r="AH6">
+        <v>25</v>
+      </c>
+      <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>85</v>
+      </c>
+      <c r="AK6">
+        <v>60</v>
+      </c>
+      <c r="AL6">
+        <v>70</v>
+      </c>
+      <c r="AM6">
+        <v>500</v>
+      </c>
+      <c r="AN6">
+        <v>75</v>
+      </c>
+      <c r="AO6">
+        <v>36</v>
+      </c>
+      <c r="AP6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ6">
+        <v>7.2</v>
+      </c>
+      <c r="AR6">
+        <v>12.5</v>
+      </c>
+      <c r="AS6">
+        <v>14</v>
+      </c>
+      <c r="AT6">
+        <v>9.6</v>
+      </c>
+      <c r="AU6">
+        <v>6.2</v>
+      </c>
+      <c r="AV6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW6">
+        <v>4.9</v>
+      </c>
+      <c r="AX6">
+        <v>20</v>
+      </c>
+      <c r="AY6">
+        <v>13</v>
+      </c>
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
+        <v>5.3</v>
+      </c>
+      <c r="BB6">
+        <v>5.5</v>
+      </c>
+      <c r="BC6">
+        <v>5.3</v>
+      </c>
+      <c r="BD6">
+        <v>5.4</v>
+      </c>
+      <c r="BE6">
+        <v>5.1</v>
+      </c>
+      <c r="BF6">
+        <v>5.4</v>
+      </c>
+      <c r="BG6">
+        <v>5</v>
+      </c>
+      <c r="BH6">
+        <v>3.35</v>
+      </c>
+      <c r="BI6">
+        <v>2.38</v>
+      </c>
+      <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>3.6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>4.9</v>
+      </c>
+      <c r="BN6">
+        <v>7.6</v>
+      </c>
+      <c r="BO6">
+        <v>4.8</v>
+      </c>
+      <c r="BP6">
+        <v>36</v>
+      </c>
+      <c r="BQ6">
+        <v>4.4</v>
+      </c>
+      <c r="BR6">
+        <v>60</v>
+      </c>
+      <c r="BS6">
+        <v>4.6</v>
+      </c>
+      <c r="BT6">
+        <v>6.2</v>
+      </c>
+      <c r="BU6">
+        <v>4</v>
+      </c>
+      <c r="BV6">
+        <v>25</v>
+      </c>
+      <c r="BW6">
+        <v>4.2</v>
+      </c>
+      <c r="BX6">
+        <v>48</v>
+      </c>
+      <c r="BY6">
         <v>4.5</v>
-      </c>
-      <c r="G6">
-        <v>990</v>
-      </c>
-      <c r="H6">
-        <v>1.39</v>
-      </c>
-      <c r="I6">
-        <v>1.88</v>
-      </c>
-      <c r="J6">
-        <v>2.96</v>
-      </c>
-      <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>2.52</v>
-      </c>
-      <c r="O6">
-        <v>1.48</v>
-      </c>
-      <c r="P6">
-        <v>1.44</v>
-      </c>
-      <c r="Q6">
-        <v>1.73</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>1.05</v>
-      </c>
-      <c r="T6">
-        <v>1.11</v>
-      </c>
-      <c r="U6">
-        <v>1.11</v>
-      </c>
-      <c r="V6">
-        <v>2.14</v>
-      </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>950</v>
-      </c>
-      <c r="Z6">
-        <v>500</v>
-      </c>
-      <c r="AA6">
-        <v>900</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>950</v>
-      </c>
-      <c r="AD6">
-        <v>950</v>
-      </c>
-      <c r="AE6">
-        <v>500</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>950</v>
-      </c>
-      <c r="AI6">
-        <v>500</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.18</v>
-      </c>
-      <c r="AQ6">
-        <v>1.14</v>
-      </c>
-      <c r="AR6">
-        <v>1.14</v>
-      </c>
-      <c r="AS6">
-        <v>1.17</v>
-      </c>
-      <c r="AT6">
-        <v>1.18</v>
-      </c>
-      <c r="AU6">
-        <v>1.15</v>
-      </c>
-      <c r="AV6">
-        <v>1.14</v>
-      </c>
-      <c r="AW6">
-        <v>1.16</v>
-      </c>
-      <c r="AX6">
-        <v>1.18</v>
-      </c>
-      <c r="AY6">
-        <v>1.18</v>
-      </c>
-      <c r="AZ6">
-        <v>1.16</v>
-      </c>
-      <c r="BA6">
-        <v>1.17</v>
-      </c>
-      <c r="BB6">
-        <v>1.18</v>
-      </c>
-      <c r="BC6">
-        <v>1.18</v>
-      </c>
-      <c r="BD6">
-        <v>1.18</v>
-      </c>
-      <c r="BE6">
-        <v>1.18</v>
-      </c>
-      <c r="BF6">
-        <v>1.55</v>
-      </c>
-      <c r="BG6">
-        <v>1.18</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.04</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.04</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2211,240 +2202,240 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F7">
-        <v>3.35</v>
+        <v>1.56</v>
       </c>
       <c r="G7">
-        <v>3.8</v>
+        <v>1.65</v>
       </c>
       <c r="H7">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>2.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="W7">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
+        <v>21</v>
+      </c>
+      <c r="Z7">
+        <v>160</v>
+      </c>
+      <c r="AA7">
+        <v>300</v>
+      </c>
+      <c r="AB7">
+        <v>6.8</v>
+      </c>
+      <c r="AC7">
+        <v>9.6</v>
+      </c>
+      <c r="AD7">
+        <v>30</v>
+      </c>
+      <c r="AE7">
+        <v>160</v>
+      </c>
+      <c r="AF7">
+        <v>8.6</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>29</v>
+      </c>
+      <c r="AI7">
+        <v>160</v>
+      </c>
+      <c r="AJ7">
+        <v>16</v>
+      </c>
+      <c r="AK7">
+        <v>20</v>
+      </c>
+      <c r="AL7">
+        <v>120</v>
+      </c>
+      <c r="AM7">
+        <v>580</v>
+      </c>
+      <c r="AN7">
+        <v>13</v>
+      </c>
+      <c r="AO7">
+        <v>260</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>16.5</v>
+      </c>
+      <c r="AR7">
+        <v>9.4</v>
+      </c>
+      <c r="AS7">
+        <v>10</v>
+      </c>
+      <c r="AT7">
+        <v>5.8</v>
+      </c>
+      <c r="AU7">
+        <v>8</v>
+      </c>
+      <c r="AV7">
+        <v>13.5</v>
+      </c>
+      <c r="AW7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX7">
+        <v>7.2</v>
+      </c>
+      <c r="AY7">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7">
+        <v>13</v>
+      </c>
+      <c r="BA7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB7">
+        <v>13</v>
+      </c>
+      <c r="BC7">
+        <v>16.5</v>
+      </c>
+      <c r="BD7">
         <v>9</v>
       </c>
-      <c r="Z7">
-        <v>18</v>
-      </c>
-      <c r="AA7">
-        <v>44</v>
-      </c>
-      <c r="AB7">
-        <v>11.5</v>
-      </c>
-      <c r="AC7">
-        <v>8.4</v>
-      </c>
-      <c r="AD7">
-        <v>12</v>
-      </c>
-      <c r="AE7">
-        <v>34</v>
-      </c>
-      <c r="AF7">
-        <v>29</v>
-      </c>
-      <c r="AG7">
-        <v>19</v>
-      </c>
-      <c r="AH7">
-        <v>24</v>
-      </c>
-      <c r="AI7">
-        <v>65</v>
-      </c>
-      <c r="AJ7">
-        <v>85</v>
-      </c>
-      <c r="AK7">
-        <v>60</v>
-      </c>
-      <c r="AL7">
-        <v>70</v>
-      </c>
-      <c r="AM7">
-        <v>500</v>
-      </c>
-      <c r="AN7">
-        <v>75</v>
-      </c>
-      <c r="AO7">
-        <v>36</v>
-      </c>
-      <c r="AP7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ7">
-        <v>7.2</v>
-      </c>
-      <c r="AR7">
-        <v>12.5</v>
-      </c>
-      <c r="AS7">
-        <v>5.6</v>
-      </c>
-      <c r="AT7">
-        <v>9.6</v>
-      </c>
-      <c r="AU7">
-        <v>6.2</v>
-      </c>
-      <c r="AV7">
+      <c r="BE7">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW7">
-        <v>4.8</v>
-      </c>
-      <c r="AX7">
-        <v>20</v>
-      </c>
-      <c r="AY7">
-        <v>13</v>
-      </c>
-      <c r="AZ7">
-        <v>17</v>
-      </c>
-      <c r="BA7">
-        <v>5.8</v>
-      </c>
-      <c r="BB7">
-        <v>34</v>
-      </c>
-      <c r="BC7">
-        <v>32</v>
-      </c>
-      <c r="BD7">
-        <v>5.2</v>
-      </c>
-      <c r="BE7">
-        <v>5.4</v>
-      </c>
       <c r="BF7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BH7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="BP7">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR7">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BU7">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BV7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2453,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2467,235 +2458,235 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G8">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="U8">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="V8">
         <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X8">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z8">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AA8">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AB8">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AC8">
+        <v>10.5</v>
+      </c>
+      <c r="AD8">
+        <v>28</v>
+      </c>
+      <c r="AE8">
+        <v>260</v>
+      </c>
+      <c r="AF8">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AD8">
-        <v>30</v>
-      </c>
-      <c r="AE8">
-        <v>160</v>
-      </c>
-      <c r="AF8">
-        <v>8.6</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI8">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="AJ8">
         <v>16</v>
       </c>
       <c r="AK8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL8">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AO8">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="AP8">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR8">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AS8">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AT8">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU8">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AV8">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AW8">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX8">
+        <v>4.9</v>
+      </c>
+      <c r="AY8">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8">
+        <v>5.9</v>
+      </c>
+      <c r="BA8">
         <v>7.2</v>
       </c>
-      <c r="AY8">
-        <v>8.6</v>
-      </c>
-      <c r="AZ8">
+      <c r="BB8">
+        <v>5.2</v>
+      </c>
+      <c r="BC8">
+        <v>5.4</v>
+      </c>
+      <c r="BD8">
+        <v>6.4</v>
+      </c>
+      <c r="BE8">
         <v>7.4</v>
       </c>
-      <c r="BA8">
-        <v>9.6</v>
-      </c>
-      <c r="BB8">
-        <v>12</v>
-      </c>
-      <c r="BC8">
-        <v>16.5</v>
-      </c>
-      <c r="BD8">
-        <v>8.4</v>
-      </c>
-      <c r="BE8">
-        <v>9.6</v>
-      </c>
       <c r="BF8">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BG8">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BH8">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2709,172 +2700,172 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="P9">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="S9">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="T9">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="U9">
+        <v>3.15</v>
+      </c>
+      <c r="V9">
+        <v>1.4</v>
+      </c>
+      <c r="W9">
         <v>1.87</v>
       </c>
-      <c r="V9">
-        <v>1.14</v>
-      </c>
-      <c r="W9">
-        <v>2.46</v>
-      </c>
       <c r="X9">
+        <v>55</v>
+      </c>
+      <c r="Y9">
+        <v>36</v>
+      </c>
+      <c r="Z9">
+        <v>42</v>
+      </c>
+      <c r="AA9">
+        <v>70</v>
+      </c>
+      <c r="AB9">
+        <v>23</v>
+      </c>
+      <c r="AC9">
+        <v>13.5</v>
+      </c>
+      <c r="AD9">
         <v>17</v>
       </c>
-      <c r="Y9">
-        <v>24</v>
-      </c>
-      <c r="Z9">
-        <v>65</v>
-      </c>
-      <c r="AA9">
-        <v>700</v>
-      </c>
-      <c r="AB9">
-        <v>8.6</v>
-      </c>
-      <c r="AC9">
-        <v>10.5</v>
-      </c>
-      <c r="AD9">
-        <v>28</v>
-      </c>
       <c r="AE9">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="AF9">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AI9">
-        <v>260</v>
+        <v>29</v>
       </c>
       <c r="AJ9">
+        <v>34</v>
+      </c>
+      <c r="AK9">
+        <v>19</v>
+      </c>
+      <c r="AL9">
+        <v>22</v>
+      </c>
+      <c r="AM9">
+        <v>46</v>
+      </c>
+      <c r="AN9">
+        <v>7</v>
+      </c>
+      <c r="AO9">
+        <v>14</v>
+      </c>
+      <c r="AP9">
+        <v>7.2</v>
+      </c>
+      <c r="AQ9">
         <v>16</v>
       </c>
-      <c r="AK9">
+      <c r="AR9">
         <v>18</v>
-      </c>
-      <c r="AL9">
-        <v>40</v>
-      </c>
-      <c r="AM9">
-        <v>580</v>
-      </c>
-      <c r="AN9">
-        <v>10.5</v>
-      </c>
-      <c r="AO9">
-        <v>180</v>
-      </c>
-      <c r="AP9">
-        <v>5.3</v>
-      </c>
-      <c r="AQ9">
-        <v>5.8</v>
-      </c>
-      <c r="AR9">
-        <v>6.8</v>
       </c>
       <c r="AS9">
         <v>7.4</v>
       </c>
       <c r="AT9">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="AU9">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AV9">
+        <v>14</v>
+      </c>
+      <c r="AW9">
+        <v>14.5</v>
+      </c>
+      <c r="AX9">
+        <v>18.5</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>12</v>
+      </c>
+      <c r="BA9">
+        <v>24</v>
+      </c>
+      <c r="BB9">
+        <v>14.5</v>
+      </c>
+      <c r="BC9">
+        <v>16</v>
+      </c>
+      <c r="BD9">
+        <v>18.5</v>
+      </c>
+      <c r="BE9">
+        <v>32</v>
+      </c>
+      <c r="BF9">
         <v>6</v>
       </c>
-      <c r="AW9">
-        <v>7.2</v>
-      </c>
-      <c r="AX9">
-        <v>4.9</v>
-      </c>
-      <c r="AY9">
-        <v>6.2</v>
-      </c>
-      <c r="AZ9">
-        <v>5.9</v>
-      </c>
-      <c r="BA9">
-        <v>7.2</v>
-      </c>
-      <c r="BB9">
-        <v>5.2</v>
-      </c>
-      <c r="BC9">
-        <v>5.4</v>
-      </c>
-      <c r="BD9">
-        <v>6.4</v>
-      </c>
-      <c r="BE9">
-        <v>7.4</v>
-      </c>
-      <c r="BF9">
-        <v>4.4</v>
-      </c>
       <c r="BG9">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2937,7 +2928,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2951,28 +2942,28 @@
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="H10">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2981,142 +2972,142 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="R10">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="S10">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="T10">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="U10">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="X10">
+        <v>29</v>
+      </c>
+      <c r="Y10">
+        <v>26</v>
+      </c>
+      <c r="Z10">
+        <v>46</v>
+      </c>
+      <c r="AA10">
+        <v>330</v>
+      </c>
+      <c r="AB10">
+        <v>14.5</v>
+      </c>
+      <c r="AC10">
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <v>22</v>
+      </c>
+      <c r="AE10">
         <v>55</v>
       </c>
-      <c r="Y10">
-        <v>36</v>
-      </c>
-      <c r="Z10">
-        <v>42</v>
-      </c>
-      <c r="AA10">
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
+        <v>11.5</v>
+      </c>
+      <c r="AH10">
+        <v>17.5</v>
+      </c>
+      <c r="AI10">
+        <v>48</v>
+      </c>
+      <c r="AJ10">
+        <v>22</v>
+      </c>
+      <c r="AK10">
+        <v>18</v>
+      </c>
+      <c r="AL10">
+        <v>28</v>
+      </c>
+      <c r="AM10">
         <v>70</v>
       </c>
-      <c r="AB10">
-        <v>23</v>
-      </c>
-      <c r="AC10">
-        <v>13.5</v>
-      </c>
-      <c r="AD10">
-        <v>17</v>
-      </c>
-      <c r="AE10">
-        <v>36</v>
-      </c>
-      <c r="AF10">
-        <v>22</v>
-      </c>
-      <c r="AG10">
-        <v>13</v>
-      </c>
-      <c r="AH10">
-        <v>15</v>
-      </c>
-      <c r="AI10">
-        <v>29</v>
-      </c>
-      <c r="AJ10">
-        <v>36</v>
-      </c>
-      <c r="AK10">
-        <v>19</v>
-      </c>
-      <c r="AL10">
-        <v>22</v>
-      </c>
-      <c r="AM10">
-        <v>46</v>
-      </c>
       <c r="AN10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO10">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AP10">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10">
-        <v>16</v>
+        <v>5.4</v>
       </c>
       <c r="AR10">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AS10">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT10">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU10">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AV10">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AW10">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AX10">
-        <v>18.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AZ10">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BA10">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="BB10">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC10">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BD10">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE10">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="BG10">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3179,12 +3170,12 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -3193,172 +3184,172 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F11">
+        <v>3.65</v>
+      </c>
+      <c r="G11">
+        <v>4.2</v>
+      </c>
+      <c r="H11">
         <v>1.75</v>
       </c>
-      <c r="G11">
-        <v>1.92</v>
-      </c>
-      <c r="H11">
-        <v>3.85</v>
-      </c>
       <c r="I11">
+        <v>1.87</v>
+      </c>
+      <c r="J11">
         <v>5</v>
       </c>
-      <c r="J11">
-        <v>4</v>
-      </c>
       <c r="K11">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.96</v>
+        <v>11</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>2.44</v>
       </c>
       <c r="S11">
-        <v>2.26</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="V11">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="W11">
-        <v>2.08</v>
+        <v>1.31</v>
       </c>
       <c r="X11">
         <v>950</v>
       </c>
       <c r="Y11">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Z11">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA11">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB11">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AC11">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AD11">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AE11">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AF11">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AG11">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AH11">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AI11">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
         <v>500</v>
       </c>
       <c r="AK11">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>34</v>
       </c>
       <c r="AN11">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AP11">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="AR11">
-        <v>1.24</v>
+        <v>20</v>
       </c>
       <c r="AS11">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="AT11">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU11">
-        <v>1.21</v>
+        <v>15</v>
       </c>
       <c r="AV11">
-        <v>1.23</v>
+        <v>12</v>
       </c>
       <c r="AW11">
-        <v>1.24</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>1.22</v>
+        <v>8.6</v>
       </c>
       <c r="AY11">
-        <v>1.21</v>
+        <v>18</v>
       </c>
       <c r="AZ11">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>1.25</v>
+        <v>16</v>
       </c>
       <c r="BB11">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="BC11">
-        <v>1.24</v>
+        <v>8</v>
       </c>
       <c r="BD11">
-        <v>1.24</v>
+        <v>14.5</v>
       </c>
       <c r="BE11">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="BF11">
-        <v>1.22</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>3.95</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3421,12 +3412,12 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -3435,482 +3426,482 @@
         <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12">
+        <v>2.16</v>
+      </c>
+      <c r="G12">
+        <v>2.2</v>
+      </c>
+      <c r="H12">
+        <v>4.3</v>
+      </c>
+      <c r="I12">
+        <v>4.5</v>
+      </c>
+      <c r="J12">
+        <v>3.1</v>
+      </c>
+      <c r="K12">
+        <v>3.2</v>
+      </c>
+      <c r="L12">
+        <v>1.55</v>
+      </c>
+      <c r="M12">
+        <v>1.14</v>
+      </c>
+      <c r="N12">
+        <v>2.58</v>
+      </c>
+      <c r="O12">
+        <v>1.59</v>
+      </c>
+      <c r="P12">
+        <v>1.53</v>
+      </c>
+      <c r="Q12">
+        <v>2.8</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>5.9</v>
+      </c>
+      <c r="T12">
+        <v>2.34</v>
+      </c>
+      <c r="U12">
+        <v>1.73</v>
+      </c>
+      <c r="V12">
+        <v>1.28</v>
+      </c>
+      <c r="W12">
+        <v>1.83</v>
+      </c>
+      <c r="X12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <v>30</v>
+      </c>
+      <c r="AA12">
+        <v>120</v>
+      </c>
+      <c r="AB12">
+        <v>6.6</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>19</v>
+      </c>
+      <c r="AE12">
+        <v>80</v>
+      </c>
+      <c r="AF12">
+        <v>11.5</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>28</v>
+      </c>
+      <c r="AI12">
+        <v>110</v>
+      </c>
+      <c r="AJ12">
+        <v>29</v>
+      </c>
+      <c r="AK12">
+        <v>32</v>
+      </c>
+      <c r="AL12">
+        <v>150</v>
+      </c>
+      <c r="AM12">
+        <v>220</v>
+      </c>
+      <c r="AN12">
+        <v>32</v>
+      </c>
+      <c r="AO12">
         <v>130</v>
       </c>
-      <c r="F12">
-        <v>3.65</v>
-      </c>
-      <c r="G12">
-        <v>4.2</v>
-      </c>
-      <c r="H12">
-        <v>1.75</v>
-      </c>
-      <c r="I12">
-        <v>1.87</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>5.7</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
+      <c r="AP12">
+        <v>7.4</v>
+      </c>
+      <c r="AQ12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR12">
+        <v>26</v>
+      </c>
+      <c r="AS12">
+        <v>38</v>
+      </c>
+      <c r="AT12">
+        <v>6.2</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>16.5</v>
+      </c>
+      <c r="AW12">
+        <v>38</v>
+      </c>
+      <c r="AX12">
+        <v>10.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>23</v>
+      </c>
+      <c r="BA12">
+        <v>40</v>
+      </c>
+      <c r="BB12">
+        <v>25</v>
+      </c>
+      <c r="BC12">
+        <v>27</v>
+      </c>
+      <c r="BD12">
+        <v>55</v>
+      </c>
+      <c r="BE12">
+        <v>110</v>
+      </c>
+      <c r="BF12">
+        <v>26</v>
+      </c>
+      <c r="BG12">
+        <v>42</v>
+      </c>
+      <c r="BH12">
+        <v>2.72</v>
+      </c>
+      <c r="BI12">
+        <v>2.24</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>6</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>11</v>
       </c>
-      <c r="O12">
-        <v>1.07</v>
-      </c>
-      <c r="P12">
-        <v>4.5</v>
-      </c>
-      <c r="Q12">
-        <v>1.24</v>
-      </c>
-      <c r="R12">
-        <v>2.44</v>
-      </c>
-      <c r="S12">
-        <v>1.58</v>
-      </c>
-      <c r="T12">
-        <v>1.25</v>
-      </c>
-      <c r="U12">
-        <v>2.8</v>
-      </c>
-      <c r="V12">
-        <v>2.14</v>
-      </c>
-      <c r="W12">
-        <v>1.31</v>
-      </c>
-      <c r="X12">
-        <v>950</v>
-      </c>
-      <c r="Y12">
-        <v>85</v>
-      </c>
-      <c r="Z12">
-        <v>60</v>
-      </c>
-      <c r="AA12">
-        <v>80</v>
-      </c>
-      <c r="AB12">
-        <v>950</v>
-      </c>
-      <c r="AC12">
-        <v>25</v>
-      </c>
-      <c r="AD12">
-        <v>19.5</v>
-      </c>
-      <c r="AE12">
-        <v>24</v>
-      </c>
-      <c r="AF12">
-        <v>500</v>
-      </c>
-      <c r="AG12">
-        <v>65</v>
-      </c>
-      <c r="AH12">
-        <v>21</v>
-      </c>
-      <c r="AI12">
-        <v>36</v>
-      </c>
-      <c r="AJ12">
-        <v>900</v>
-      </c>
-      <c r="AK12">
-        <v>500</v>
-      </c>
-      <c r="AL12">
-        <v>500</v>
-      </c>
-      <c r="AM12">
-        <v>580</v>
-      </c>
-      <c r="AN12">
-        <v>18.5</v>
-      </c>
-      <c r="AO12">
-        <v>5.9</v>
-      </c>
-      <c r="AP12">
-        <v>3.05</v>
-      </c>
-      <c r="AQ12">
-        <v>17.5</v>
-      </c>
-      <c r="AR12">
-        <v>14.5</v>
-      </c>
-      <c r="AS12">
-        <v>15.5</v>
-      </c>
-      <c r="AT12">
-        <v>20</v>
-      </c>
-      <c r="AU12">
-        <v>11.5</v>
-      </c>
-      <c r="AV12">
-        <v>10.5</v>
-      </c>
-      <c r="AW12">
-        <v>11</v>
-      </c>
-      <c r="AX12">
-        <v>2.94</v>
-      </c>
-      <c r="AY12">
-        <v>13.5</v>
-      </c>
-      <c r="AZ12">
-        <v>12</v>
-      </c>
-      <c r="BA12">
-        <v>12.5</v>
-      </c>
-      <c r="BB12">
-        <v>2.98</v>
-      </c>
-      <c r="BC12">
-        <v>16</v>
-      </c>
-      <c r="BD12">
-        <v>18</v>
-      </c>
-      <c r="BE12">
-        <v>20</v>
-      </c>
-      <c r="BF12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG12">
-        <v>3.15</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="G13">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="H13">
-        <v>4.4</v>
+        <v>2.66</v>
       </c>
       <c r="I13">
+        <v>3.1</v>
+      </c>
+      <c r="J13">
+        <v>3.75</v>
+      </c>
+      <c r="K13">
+        <v>4.6</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13">
+        <v>1.17</v>
+      </c>
+      <c r="P13">
+        <v>2.42</v>
+      </c>
+      <c r="Q13">
+        <v>1.53</v>
+      </c>
+      <c r="R13">
+        <v>1.59</v>
+      </c>
+      <c r="S13">
+        <v>2.28</v>
+      </c>
+      <c r="T13">
+        <v>1.49</v>
+      </c>
+      <c r="U13">
+        <v>2.58</v>
+      </c>
+      <c r="V13">
+        <v>1.47</v>
+      </c>
+      <c r="W13">
+        <v>1.6</v>
+      </c>
+      <c r="X13">
+        <v>28</v>
+      </c>
+      <c r="Y13">
+        <v>19</v>
+      </c>
+      <c r="Z13">
+        <v>25</v>
+      </c>
+      <c r="AA13">
+        <v>44</v>
+      </c>
+      <c r="AB13">
+        <v>17.5</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>14.5</v>
+      </c>
+      <c r="AE13">
+        <v>28</v>
+      </c>
+      <c r="AF13">
+        <v>22</v>
+      </c>
+      <c r="AG13">
+        <v>13.5</v>
+      </c>
+      <c r="AH13">
+        <v>15.5</v>
+      </c>
+      <c r="AI13">
+        <v>34</v>
+      </c>
+      <c r="AJ13">
+        <v>36</v>
+      </c>
+      <c r="AK13">
+        <v>25</v>
+      </c>
+      <c r="AL13">
+        <v>30</v>
+      </c>
+      <c r="AM13">
+        <v>60</v>
+      </c>
+      <c r="AN13">
+        <v>13.5</v>
+      </c>
+      <c r="AO13">
+        <v>16.5</v>
+      </c>
+      <c r="AP13">
+        <v>6</v>
+      </c>
+      <c r="AQ13">
+        <v>5.5</v>
+      </c>
+      <c r="AR13">
+        <v>5.9</v>
+      </c>
+      <c r="AS13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT13">
+        <v>5.4</v>
+      </c>
+      <c r="AU13">
         <v>4.5</v>
       </c>
-      <c r="J13">
-        <v>3.1</v>
-      </c>
-      <c r="K13">
-        <v>3.2</v>
-      </c>
-      <c r="L13">
-        <v>1.55</v>
-      </c>
-      <c r="M13">
-        <v>1.14</v>
-      </c>
-      <c r="N13">
-        <v>2.58</v>
-      </c>
-      <c r="O13">
-        <v>1.59</v>
-      </c>
-      <c r="P13">
-        <v>1.53</v>
-      </c>
-      <c r="Q13">
-        <v>2.78</v>
-      </c>
-      <c r="R13">
-        <v>1.18</v>
-      </c>
-      <c r="S13">
+      <c r="AV13">
+        <v>5</v>
+      </c>
+      <c r="AW13">
         <v>6</v>
       </c>
-      <c r="T13">
-        <v>2.28</v>
-      </c>
-      <c r="U13">
-        <v>1.73</v>
-      </c>
-      <c r="V13">
-        <v>1.28</v>
-      </c>
-      <c r="W13">
-        <v>1.82</v>
-      </c>
-      <c r="X13">
-        <v>8</v>
-      </c>
-      <c r="Y13">
-        <v>11</v>
-      </c>
-      <c r="Z13">
-        <v>30</v>
-      </c>
-      <c r="AA13">
-        <v>110</v>
-      </c>
-      <c r="AB13">
-        <v>6.6</v>
-      </c>
-      <c r="AC13">
-        <v>7.6</v>
-      </c>
-      <c r="AD13">
-        <v>19</v>
-      </c>
-      <c r="AE13">
-        <v>80</v>
-      </c>
-      <c r="AF13">
-        <v>11.5</v>
-      </c>
-      <c r="AG13">
-        <v>12</v>
-      </c>
-      <c r="AH13">
-        <v>28</v>
-      </c>
-      <c r="AI13">
-        <v>110</v>
-      </c>
-      <c r="AJ13">
-        <v>28</v>
-      </c>
-      <c r="AK13">
-        <v>32</v>
-      </c>
-      <c r="AL13">
-        <v>70</v>
-      </c>
-      <c r="AM13">
-        <v>220</v>
-      </c>
-      <c r="AN13">
-        <v>34</v>
-      </c>
-      <c r="AO13">
-        <v>130</v>
-      </c>
-      <c r="AP13">
-        <v>7.4</v>
-      </c>
-      <c r="AQ13">
-        <v>10</v>
-      </c>
-      <c r="AR13">
-        <v>22</v>
-      </c>
-      <c r="AS13">
-        <v>38</v>
-      </c>
-      <c r="AT13">
+      <c r="AX13">
+        <v>5.7</v>
+      </c>
+      <c r="AY13">
+        <v>4.9</v>
+      </c>
+      <c r="AZ13">
+        <v>5.2</v>
+      </c>
+      <c r="BA13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB13">
+        <v>6.4</v>
+      </c>
+      <c r="BC13">
+        <v>5.9</v>
+      </c>
+      <c r="BD13">
         <v>6.2</v>
       </c>
-      <c r="AU13">
-        <v>7</v>
-      </c>
-      <c r="AV13">
-        <v>16.5</v>
-      </c>
-      <c r="AW13">
-        <v>38</v>
-      </c>
-      <c r="AX13">
-        <v>10.5</v>
-      </c>
-      <c r="AY13">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13">
-        <v>23</v>
-      </c>
-      <c r="BA13">
-        <v>40</v>
-      </c>
-      <c r="BB13">
-        <v>25</v>
-      </c>
-      <c r="BC13">
-        <v>27</v>
-      </c>
-      <c r="BD13">
-        <v>55</v>
-      </c>
       <c r="BE13">
-        <v>110</v>
+        <v>6.8</v>
       </c>
       <c r="BF13">
-        <v>26</v>
+        <v>4.9</v>
       </c>
       <c r="BG13">
-        <v>42</v>
+        <v>5.3</v>
       </c>
       <c r="BH13">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -3919,240 +3910,240 @@
         <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="G14">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
-        <v>2.64</v>
+        <v>3.9</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="P14">
-        <v>2.42</v>
+        <v>1.56</v>
       </c>
       <c r="Q14">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="R14">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="T14">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="W14">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y14">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="Z14">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA14">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AB14">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AD14">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AE14">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF14">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AH14">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AI14">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ14">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK14">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL14">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AM14">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AO14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>6</v>
+        <v>1.16</v>
       </c>
       <c r="AQ14">
-        <v>5.5</v>
+        <v>1.16</v>
       </c>
       <c r="AR14">
-        <v>5.9</v>
+        <v>1.15</v>
       </c>
       <c r="AS14">
-        <v>8.800000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AT14">
-        <v>5.4</v>
+        <v>1.16</v>
       </c>
       <c r="AU14">
+        <v>1.13</v>
+      </c>
+      <c r="AV14">
+        <v>1.15</v>
+      </c>
+      <c r="AW14">
+        <v>1.16</v>
+      </c>
+      <c r="AX14">
+        <v>1.14</v>
+      </c>
+      <c r="AY14">
+        <v>1.13</v>
+      </c>
+      <c r="AZ14">
+        <v>1.16</v>
+      </c>
+      <c r="BA14">
+        <v>1.16</v>
+      </c>
+      <c r="BB14">
+        <v>1.16</v>
+      </c>
+      <c r="BC14">
+        <v>1.14</v>
+      </c>
+      <c r="BD14">
+        <v>1.16</v>
+      </c>
+      <c r="BE14">
+        <v>1.16</v>
+      </c>
+      <c r="BF14">
+        <v>1.14</v>
+      </c>
+      <c r="BG14">
+        <v>1.55</v>
+      </c>
+      <c r="BH14">
+        <v>3.35</v>
+      </c>
+      <c r="BI14">
+        <v>2.52</v>
+      </c>
+      <c r="BJ14">
+        <v>12.5</v>
+      </c>
+      <c r="BK14">
+        <v>4.7</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>7.4</v>
+      </c>
+      <c r="BN14">
         <v>4.5</v>
       </c>
-      <c r="AV14">
-        <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX14">
-        <v>5.7</v>
-      </c>
-      <c r="AY14">
-        <v>4.9</v>
-      </c>
-      <c r="AZ14">
-        <v>5.2</v>
-      </c>
-      <c r="BA14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB14">
+      <c r="BO14">
+        <v>3.55</v>
+      </c>
+      <c r="BP14">
+        <v>15</v>
+      </c>
+      <c r="BQ14">
+        <v>5.1</v>
+      </c>
+      <c r="BR14">
+        <v>40</v>
+      </c>
+      <c r="BS14">
         <v>6.4</v>
       </c>
-      <c r="BC14">
-        <v>5.9</v>
-      </c>
-      <c r="BD14">
-        <v>6.2</v>
-      </c>
-      <c r="BE14">
+      <c r="BT14">
+        <v>9</v>
+      </c>
+      <c r="BU14">
+        <v>4.1</v>
+      </c>
+      <c r="BV14">
+        <v>55</v>
+      </c>
+      <c r="BW14">
+        <v>6.6</v>
+      </c>
+      <c r="BX14">
+        <v>70</v>
+      </c>
+      <c r="BY14">
         <v>6.8</v>
       </c>
-      <c r="BF14">
-        <v>4.9</v>
-      </c>
-      <c r="BG14">
-        <v>5.3</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.04</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.04</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.04</v>
-      </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -4161,172 +4152,172 @@
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F15">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="G15">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="H15">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.09</v>
+      </c>
+      <c r="N15">
+        <v>1.66</v>
+      </c>
+      <c r="O15">
+        <v>1.39</v>
+      </c>
+      <c r="P15">
+        <v>1.38</v>
+      </c>
+      <c r="Q15">
+        <v>2.16</v>
+      </c>
+      <c r="R15">
+        <v>1.23</v>
+      </c>
+      <c r="S15">
+        <v>2.22</v>
+      </c>
+      <c r="T15">
+        <v>2.2</v>
+      </c>
+      <c r="U15">
         <v>1.37</v>
       </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.66</v>
-      </c>
-      <c r="O15">
-        <v>1.31</v>
-      </c>
-      <c r="P15">
-        <v>1.56</v>
-      </c>
-      <c r="Q15">
-        <v>1.98</v>
-      </c>
-      <c r="R15">
-        <v>1.18</v>
-      </c>
-      <c r="S15">
-        <v>2.8</v>
-      </c>
-      <c r="T15">
-        <v>1.11</v>
-      </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
       <c r="V15">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="W15">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="X15">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
         <v>950</v>
       </c>
       <c r="AC15">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AD15">
         <v>950</v>
       </c>
       <c r="AE15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AG15">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AH15">
         <v>950</v>
       </c>
       <c r="AI15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AQ15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AR15">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AS15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AT15">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AU15">
-        <v>1.13</v>
+        <v>5.7</v>
       </c>
       <c r="AV15">
-        <v>1.14</v>
+        <v>11</v>
       </c>
       <c r="AW15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AX15">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="AY15">
-        <v>1.12</v>
+        <v>5.4</v>
       </c>
       <c r="AZ15">
-        <v>1.16</v>
+        <v>10.5</v>
       </c>
       <c r="BA15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BB15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BC15">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="BD15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BE15">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BF15">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="BG15">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4383,18 +4374,18 @@
         <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
@@ -4403,240 +4394,240 @@
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16">
+        <v>1.61</v>
+      </c>
+      <c r="G16">
+        <v>1.67</v>
+      </c>
+      <c r="H16">
+        <v>6.6</v>
+      </c>
+      <c r="I16">
+        <v>7.6</v>
+      </c>
+      <c r="J16">
+        <v>3.85</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>1.36</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.25</v>
+      </c>
+      <c r="O16">
+        <v>1.38</v>
+      </c>
+      <c r="P16">
+        <v>1.78</v>
+      </c>
+      <c r="Q16">
+        <v>2.12</v>
+      </c>
+      <c r="R16">
+        <v>1.3</v>
+      </c>
+      <c r="S16">
+        <v>3.85</v>
+      </c>
+      <c r="T16">
+        <v>2.08</v>
+      </c>
+      <c r="U16">
+        <v>1.79</v>
+      </c>
+      <c r="V16">
+        <v>1.15</v>
+      </c>
+      <c r="W16">
+        <v>2.48</v>
+      </c>
+      <c r="X16">
+        <v>15.5</v>
+      </c>
+      <c r="Y16">
+        <v>21</v>
+      </c>
+      <c r="Z16">
+        <v>70</v>
+      </c>
+      <c r="AA16">
+        <v>270</v>
+      </c>
+      <c r="AB16">
+        <v>7.2</v>
+      </c>
+      <c r="AC16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD16">
+        <v>32</v>
+      </c>
+      <c r="AE16">
+        <v>140</v>
+      </c>
+      <c r="AF16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG16">
+        <v>12</v>
+      </c>
+      <c r="AH16">
+        <v>32</v>
+      </c>
+      <c r="AI16">
+        <v>140</v>
+      </c>
+      <c r="AJ16">
+        <v>16.5</v>
+      </c>
+      <c r="AK16">
+        <v>23</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
+        <v>210</v>
+      </c>
+      <c r="AN16">
+        <v>12.5</v>
+      </c>
+      <c r="AO16">
+        <v>210</v>
+      </c>
+      <c r="AP16">
+        <v>11</v>
+      </c>
+      <c r="AQ16">
+        <v>16.5</v>
+      </c>
+      <c r="AR16">
+        <v>6</v>
+      </c>
+      <c r="AS16">
+        <v>6.4</v>
+      </c>
+      <c r="AT16">
+        <v>6.2</v>
+      </c>
+      <c r="AU16">
+        <v>7.8</v>
+      </c>
+      <c r="AV16">
+        <v>5.5</v>
+      </c>
+      <c r="AW16">
+        <v>6.4</v>
+      </c>
+      <c r="AX16">
+        <v>7.6</v>
+      </c>
+      <c r="AY16">
+        <v>8.6</v>
+      </c>
+      <c r="AZ16">
+        <v>21</v>
+      </c>
+      <c r="BA16">
+        <v>6.4</v>
+      </c>
+      <c r="BB16">
+        <v>13.5</v>
+      </c>
+      <c r="BC16">
+        <v>16</v>
+      </c>
+      <c r="BD16">
+        <v>5.9</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>10</v>
+      </c>
+      <c r="BG16">
+        <v>6.4</v>
+      </c>
+      <c r="BH16">
+        <v>3.35</v>
+      </c>
+      <c r="BI16">
+        <v>2.6</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>5.6</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>10</v>
+      </c>
+      <c r="BN16">
+        <v>4.2</v>
+      </c>
+      <c r="BO16">
+        <v>3.15</v>
+      </c>
+      <c r="BP16">
+        <v>11.5</v>
+      </c>
+      <c r="BQ16">
+        <v>5.5</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>7.8</v>
+      </c>
+      <c r="BT16">
+        <v>10.5</v>
+      </c>
+      <c r="BU16">
+        <v>5.2</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>9</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ16">
+        <v>25</v>
+      </c>
+      <c r="CA16">
+        <v>7.4</v>
+      </c>
+      <c r="CB16" t="s">
         <v>134</v>
-      </c>
-      <c r="F16">
-        <v>1.63</v>
-      </c>
-      <c r="G16">
-        <v>1.8</v>
-      </c>
-      <c r="H16">
-        <v>4.9</v>
-      </c>
-      <c r="I16">
-        <v>990</v>
-      </c>
-      <c r="J16">
-        <v>3.6</v>
-      </c>
-      <c r="K16">
-        <v>4.2</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.04</v>
-      </c>
-      <c r="N16">
-        <v>1.66</v>
-      </c>
-      <c r="O16">
-        <v>1.39</v>
-      </c>
-      <c r="P16">
-        <v>1.25</v>
-      </c>
-      <c r="Q16">
-        <v>2.08</v>
-      </c>
-      <c r="R16">
-        <v>1.14</v>
-      </c>
-      <c r="S16">
-        <v>2.22</v>
-      </c>
-      <c r="T16">
-        <v>2.2</v>
-      </c>
-      <c r="U16">
-        <v>1.11</v>
-      </c>
-      <c r="V16">
-        <v>1.12</v>
-      </c>
-      <c r="W16">
-        <v>2.24</v>
-      </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>950</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16">
-        <v>1.01</v>
-      </c>
-      <c r="AR16">
-        <v>1.01</v>
-      </c>
-      <c r="AS16">
-        <v>1.01</v>
-      </c>
-      <c r="AT16">
-        <v>3.35</v>
-      </c>
-      <c r="AU16">
-        <v>1.01</v>
-      </c>
-      <c r="AV16">
-        <v>1.01</v>
-      </c>
-      <c r="AW16">
-        <v>1.01</v>
-      </c>
-      <c r="AX16">
-        <v>1.01</v>
-      </c>
-      <c r="AY16">
-        <v>1.01</v>
-      </c>
-      <c r="AZ16">
-        <v>1.01</v>
-      </c>
-      <c r="BA16">
-        <v>1.01</v>
-      </c>
-      <c r="BB16">
-        <v>1.01</v>
-      </c>
-      <c r="BC16">
-        <v>1.01</v>
-      </c>
-      <c r="BD16">
-        <v>1.01</v>
-      </c>
-      <c r="BE16">
-        <v>1.01</v>
-      </c>
-      <c r="BF16">
-        <v>1.01</v>
-      </c>
-      <c r="BG16">
-        <v>1.01</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.04</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.04</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
@@ -4645,477 +4636,235 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F17">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="G17">
-        <v>1.67</v>
+        <v>5.2</v>
       </c>
       <c r="H17">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="I17">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="L17">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="P17">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>1.2</v>
+      </c>
+      <c r="S17">
+        <v>4.3</v>
+      </c>
+      <c r="T17">
         <v>2.12</v>
       </c>
-      <c r="R17">
-        <v>1.3</v>
-      </c>
-      <c r="S17">
-        <v>3.85</v>
-      </c>
-      <c r="T17">
-        <v>2.08</v>
-      </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
-        <v>1.15</v>
+        <v>1.86</v>
       </c>
       <c r="W17">
-        <v>2.48</v>
+        <v>1.23</v>
       </c>
       <c r="X17">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y17">
+        <v>7.2</v>
+      </c>
+      <c r="Z17">
+        <v>14</v>
+      </c>
+      <c r="AA17">
+        <v>38</v>
+      </c>
+      <c r="AB17">
+        <v>13</v>
+      </c>
+      <c r="AC17">
+        <v>7.8</v>
+      </c>
+      <c r="AD17">
+        <v>13.5</v>
+      </c>
+      <c r="AE17">
+        <v>40</v>
+      </c>
+      <c r="AF17">
+        <v>50</v>
+      </c>
+      <c r="AG17">
         <v>21</v>
       </c>
-      <c r="Z17">
+      <c r="AH17">
+        <v>25</v>
+      </c>
+      <c r="AI17">
         <v>70</v>
       </c>
-      <c r="AA17">
-        <v>270</v>
-      </c>
-      <c r="AB17">
-        <v>7.2</v>
-      </c>
-      <c r="AC17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17">
-        <v>32</v>
-      </c>
-      <c r="AE17">
-        <v>140</v>
-      </c>
-      <c r="AF17">
-        <v>10.5</v>
-      </c>
-      <c r="AG17">
-        <v>12</v>
-      </c>
-      <c r="AH17">
-        <v>32</v>
-      </c>
-      <c r="AI17">
-        <v>140</v>
-      </c>
       <c r="AJ17">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="AK17">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="AL17">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM17">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AN17">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="AO17">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="AP17">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AQ17">
-        <v>16.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR17">
+        <v>4.5</v>
+      </c>
+      <c r="AS17">
         <v>5.4</v>
       </c>
-      <c r="AS17">
-        <v>5.8</v>
-      </c>
       <c r="AT17">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AU17">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="AV17">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW17">
         <v>5.7</v>
       </c>
       <c r="AX17">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AY17">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AZ17">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BA17">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB17">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC17">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BD17">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BE17">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BG17">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH17">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI17">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BJ17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK17">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BN17">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BO17">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP17">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BQ17">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS17">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT17">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BU17">
-        <v>5.2</v>
+        <v>2.56</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY17">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BZ17">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="CA17">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:80">
-      <c r="A18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18">
-        <v>3.95</v>
-      </c>
-      <c r="G18">
-        <v>5.2</v>
-      </c>
-      <c r="H18">
-        <v>1.95</v>
-      </c>
-      <c r="I18">
-        <v>2.2</v>
-      </c>
-      <c r="J18">
-        <v>3.1</v>
-      </c>
-      <c r="K18">
-        <v>3.55</v>
-      </c>
-      <c r="L18">
-        <v>1.45</v>
-      </c>
-      <c r="M18">
-        <v>1.11</v>
-      </c>
-      <c r="N18">
-        <v>2.4</v>
-      </c>
-      <c r="O18">
-        <v>1.48</v>
-      </c>
-      <c r="P18">
-        <v>1.56</v>
-      </c>
-      <c r="Q18">
-        <v>2.42</v>
-      </c>
-      <c r="R18">
-        <v>1.2</v>
-      </c>
-      <c r="S18">
-        <v>1.05</v>
-      </c>
-      <c r="T18">
-        <v>2.08</v>
-      </c>
-      <c r="U18">
-        <v>1.74</v>
-      </c>
-      <c r="V18">
-        <v>1.83</v>
-      </c>
-      <c r="W18">
-        <v>1.24</v>
-      </c>
-      <c r="X18">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y18">
-        <v>7.2</v>
-      </c>
-      <c r="Z18">
-        <v>14</v>
-      </c>
-      <c r="AA18">
-        <v>38</v>
-      </c>
-      <c r="AB18">
-        <v>15.5</v>
-      </c>
-      <c r="AC18">
-        <v>8</v>
-      </c>
-      <c r="AD18">
-        <v>13.5</v>
-      </c>
-      <c r="AE18">
-        <v>40</v>
-      </c>
-      <c r="AF18">
-        <v>50</v>
-      </c>
-      <c r="AG18">
-        <v>21</v>
-      </c>
-      <c r="AH18">
-        <v>25</v>
-      </c>
-      <c r="AI18">
-        <v>70</v>
-      </c>
-      <c r="AJ18">
-        <v>150</v>
-      </c>
-      <c r="AK18">
-        <v>100</v>
-      </c>
-      <c r="AL18">
-        <v>120</v>
-      </c>
-      <c r="AM18">
-        <v>230</v>
-      </c>
-      <c r="AN18">
-        <v>160</v>
-      </c>
-      <c r="AO18">
-        <v>26</v>
-      </c>
-      <c r="AP18">
-        <v>4</v>
-      </c>
-      <c r="AQ18">
-        <v>3.45</v>
-      </c>
-      <c r="AR18">
-        <v>4.5</v>
-      </c>
-      <c r="AS18">
-        <v>5.4</v>
-      </c>
-      <c r="AT18">
-        <v>4.7</v>
-      </c>
-      <c r="AU18">
-        <v>6</v>
-      </c>
-      <c r="AV18">
-        <v>4.5</v>
-      </c>
-      <c r="AW18">
-        <v>9</v>
-      </c>
-      <c r="AX18">
-        <v>5.7</v>
-      </c>
-      <c r="AY18">
-        <v>5.1</v>
-      </c>
-      <c r="AZ18">
-        <v>5.3</v>
-      </c>
-      <c r="BA18">
-        <v>6</v>
-      </c>
-      <c r="BB18">
-        <v>6.4</v>
-      </c>
-      <c r="BC18">
-        <v>6.2</v>
-      </c>
-      <c r="BD18">
-        <v>6.2</v>
-      </c>
-      <c r="BE18">
-        <v>6.6</v>
-      </c>
-      <c r="BF18">
-        <v>6.4</v>
-      </c>
-      <c r="BG18">
-        <v>5.3</v>
-      </c>
-      <c r="BH18">
-        <v>3.25</v>
-      </c>
-      <c r="BI18">
-        <v>2.3</v>
-      </c>
-      <c r="BJ18">
-        <v>14</v>
-      </c>
-      <c r="BK18">
-        <v>3.7</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>4.9</v>
-      </c>
-      <c r="BN18">
-        <v>9.4</v>
-      </c>
-      <c r="BO18">
-        <v>3.25</v>
-      </c>
-      <c r="BP18">
-        <v>60</v>
-      </c>
-      <c r="BQ18">
-        <v>4.6</v>
-      </c>
-      <c r="BR18">
-        <v>85</v>
-      </c>
-      <c r="BS18">
-        <v>4.7</v>
-      </c>
-      <c r="BT18">
-        <v>5.2</v>
-      </c>
-      <c r="BU18">
-        <v>2.56</v>
-      </c>
-      <c r="BV18">
-        <v>19.5</v>
-      </c>
-      <c r="BW18">
-        <v>4</v>
-      </c>
-      <c r="BX18">
-        <v>46</v>
-      </c>
-      <c r="BY18">
-        <v>4.5</v>
-      </c>
-      <c r="BZ18">
-        <v>50</v>
-      </c>
-      <c r="CA18">
-        <v>4.6</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -400,7 +400,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-08-05 01:57:35</t>
+    <t>2026-08-05 04:04:30</t>
   </si>
 </sst>
 </file>
@@ -994,64 +994,64 @@
         <v>114</v>
       </c>
       <c r="F2">
+        <v>2.28</v>
+      </c>
+      <c r="G2">
+        <v>2.36</v>
+      </c>
+      <c r="H2">
+        <v>3.5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>3.1</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.15</v>
+      </c>
+      <c r="O2">
+        <v>1.39</v>
+      </c>
+      <c r="P2">
+        <v>1.68</v>
+      </c>
+      <c r="Q2">
+        <v>2.2</v>
+      </c>
+      <c r="R2">
+        <v>1.25</v>
+      </c>
+      <c r="S2">
+        <v>4.6</v>
+      </c>
+      <c r="T2">
         <v>1.92</v>
       </c>
-      <c r="G2">
-        <v>3.55</v>
-      </c>
-      <c r="H2">
-        <v>2.62</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>2.96</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>1.63</v>
-      </c>
-      <c r="O2">
-        <v>1.07</v>
-      </c>
-      <c r="P2">
-        <v>1.25</v>
-      </c>
-      <c r="Q2">
-        <v>1.46</v>
-      </c>
-      <c r="R2">
-        <v>1.2</v>
-      </c>
-      <c r="S2">
-        <v>2.4</v>
-      </c>
-      <c r="T2">
-        <v>1.11</v>
-      </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z2">
         <v>500</v>
@@ -1060,112 +1060,112 @@
         <v>900</v>
       </c>
       <c r="AB2">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK2">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP2">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2">
-        <v>1.24</v>
+        <v>3.55</v>
       </c>
       <c r="AR2">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="AS2">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AT2">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="AU2">
-        <v>1.15</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="AW2">
-        <v>1.25</v>
+        <v>3.65</v>
       </c>
       <c r="AX2">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="AY2">
-        <v>1.24</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2">
-        <v>1.23</v>
+        <v>3.25</v>
       </c>
       <c r="BA2">
-        <v>1.26</v>
+        <v>5.5</v>
       </c>
       <c r="BB2">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="BC2">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="BD2">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="BE2">
         <v>70</v>
       </c>
       <c r="BF2">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="BG2">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1174,40 +1174,40 @@
         <v>85</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1236,100 +1236,100 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>2.76</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
         <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB3">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF3">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL3">
         <v>500</v>
@@ -1344,118 +1344,118 @@
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.24</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3">
-        <v>1.22</v>
+        <v>4.3</v>
       </c>
       <c r="AR3">
-        <v>1.23</v>
+        <v>5.7</v>
       </c>
       <c r="AS3">
-        <v>1.24</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
-        <v>1.22</v>
+        <v>4.2</v>
       </c>
       <c r="AU3">
-        <v>1.14</v>
+        <v>3.9</v>
       </c>
       <c r="AV3">
-        <v>1.22</v>
+        <v>5.4</v>
       </c>
       <c r="AW3">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="AX3">
-        <v>1.23</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
-        <v>1.22</v>
+        <v>5.3</v>
       </c>
       <c r="AZ3">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="BA3">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="BC3">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="BD3">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
         <v>140</v>
       </c>
       <c r="BF3">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="CB3" t="s">
         <v>128</v>
@@ -1478,97 +1478,97 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>6.4</v>
       </c>
       <c r="H4">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="I4">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
         <v>1.53</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="Z4">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AA4">
+        <v>24</v>
+      </c>
+      <c r="AB4">
+        <v>15</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>12</v>
+      </c>
+      <c r="AE4">
+        <v>28</v>
+      </c>
+      <c r="AF4">
+        <v>46</v>
+      </c>
+      <c r="AG4">
+        <v>26</v>
+      </c>
+      <c r="AH4">
+        <v>29</v>
+      </c>
+      <c r="AI4">
+        <v>65</v>
+      </c>
+      <c r="AJ4">
         <v>900</v>
-      </c>
-      <c r="AB4">
-        <v>950</v>
-      </c>
-      <c r="AC4">
-        <v>950</v>
-      </c>
-      <c r="AD4">
-        <v>950</v>
-      </c>
-      <c r="AE4">
-        <v>500</v>
-      </c>
-      <c r="AF4">
-        <v>500</v>
-      </c>
-      <c r="AG4">
-        <v>950</v>
-      </c>
-      <c r="AH4">
-        <v>950</v>
-      </c>
-      <c r="AI4">
-        <v>500</v>
-      </c>
-      <c r="AJ4">
-        <v>700</v>
       </c>
       <c r="AK4">
         <v>700</v>
@@ -1583,115 +1583,115 @@
         <v>700</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP4">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AR4">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="AS4">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="AT4">
-        <v>1.19</v>
+        <v>4.8</v>
       </c>
       <c r="AU4">
-        <v>1.16</v>
+        <v>3.85</v>
       </c>
       <c r="AV4">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AW4">
-        <v>1.17</v>
+        <v>5.7</v>
       </c>
       <c r="AX4">
-        <v>1.19</v>
+        <v>6.2</v>
       </c>
       <c r="AY4">
-        <v>1.19</v>
+        <v>5.6</v>
       </c>
       <c r="AZ4">
-        <v>1.18</v>
+        <v>5.7</v>
       </c>
       <c r="BA4">
-        <v>1.19</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>1.19</v>
+        <v>6.8</v>
       </c>
       <c r="BC4">
-        <v>1.19</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>1.19</v>
+        <v>6.8</v>
       </c>
       <c r="BE4">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BG4">
-        <v>1.19</v>
+        <v>5.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1720,100 +1720,100 @@
         <v>117</v>
       </c>
       <c r="F5">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="G5">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="H5">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="I5">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="O5">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P5">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="W5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y5">
         <v>9.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA5">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL5">
         <v>70</v>
@@ -1822,118 +1822,118 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
         <v>7.2</v>
       </c>
       <c r="AR5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS5">
         <v>14</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AX5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AY5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
+        <v>5.9</v>
+      </c>
+      <c r="BB5">
+        <v>6</v>
+      </c>
+      <c r="BC5">
+        <v>5.9</v>
+      </c>
+      <c r="BD5">
+        <v>5.3</v>
+      </c>
+      <c r="BE5">
         <v>5.6</v>
       </c>
-      <c r="BB5">
+      <c r="BF5">
         <v>5.3</v>
       </c>
-      <c r="BC5">
-        <v>5.6</v>
-      </c>
-      <c r="BD5">
-        <v>5.2</v>
-      </c>
-      <c r="BE5">
-        <v>5.4</v>
-      </c>
-      <c r="BF5">
-        <v>5.2</v>
-      </c>
       <c r="BG5">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH5">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BN5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO5">
         <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BQ5">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS5">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
         <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
         <v>25</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1962,46 +1962,46 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="G6">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
         <v>2.14</v>
@@ -2010,52 +2010,52 @@
         <v>1.73</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA6">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AB6">
         <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE6">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AF6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL6">
         <v>50</v>
@@ -2064,67 +2064,67 @@
         <v>700</v>
       </c>
       <c r="AN6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AO6">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="AP6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>34</v>
+      </c>
+      <c r="AS6">
         <v>10.5</v>
-      </c>
-      <c r="AQ6">
-        <v>16.5</v>
-      </c>
-      <c r="AR6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS6">
-        <v>10</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG6">
         <v>10</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
         <v>2.6</v>
@@ -2133,49 +2133,49 @@
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BN6">
         <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BP6">
         <v>12</v>
       </c>
       <c r="BQ6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
         <v>34</v>
       </c>
       <c r="BS6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.800000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2204,10 +2204,10 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H7">
         <v>4.4</v>
@@ -2216,7 +2216,7 @@
         <v>5.5</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -2225,7 +2225,7 @@
         <v>1.39</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
         <v>3.3</v>
@@ -2234,34 +2234,34 @@
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
         <v>40</v>
@@ -2279,10 +2279,10 @@
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AF7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2291,10 +2291,10 @@
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AK7">
         <v>21</v>
@@ -2303,67 +2303,67 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AN7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS7">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="AT7">
         <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB7">
         <v>15.5</v>
       </c>
       <c r="BC7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE7">
-        <v>5.5</v>
+        <v>44</v>
       </c>
       <c r="BF7">
         <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BH7">
         <v>3.55</v>
@@ -2387,7 +2387,7 @@
         <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
@@ -2446,22 +2446,22 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.21</v>
@@ -2470,31 +2470,31 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O8">
         <v>1.11</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
         <v>1.86</v>
@@ -2503,25 +2503,25 @@
         <v>55</v>
       </c>
       <c r="Y8">
+        <v>32</v>
+      </c>
+      <c r="Z8">
+        <v>46</v>
+      </c>
+      <c r="AA8">
+        <v>65</v>
+      </c>
+      <c r="AB8">
+        <v>26</v>
+      </c>
+      <c r="AC8">
+        <v>12.5</v>
+      </c>
+      <c r="AD8">
+        <v>16.5</v>
+      </c>
+      <c r="AE8">
         <v>34</v>
-      </c>
-      <c r="Z8">
-        <v>36</v>
-      </c>
-      <c r="AA8">
-        <v>70</v>
-      </c>
-      <c r="AB8">
-        <v>22</v>
-      </c>
-      <c r="AC8">
-        <v>13.5</v>
-      </c>
-      <c r="AD8">
-        <v>17</v>
-      </c>
-      <c r="AE8">
-        <v>36</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2530,13 +2530,13 @@
         <v>13</v>
       </c>
       <c r="AH8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8">
         <v>19</v>
@@ -2545,28 +2545,28 @@
         <v>22</v>
       </c>
       <c r="AM8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN8">
         <v>7</v>
       </c>
       <c r="AO8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP8">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AQ8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AR8">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AS8">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="AT8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU8">
         <v>11</v>
@@ -2575,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="AW8">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AX8">
         <v>18.5</v>
@@ -2587,10 +2587,10 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BB8">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC8">
         <v>16</v>
@@ -2599,19 +2599,19 @@
         <v>18.5</v>
       </c>
       <c r="BE8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH8">
         <v>6.8</v>
       </c>
       <c r="BI8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8">
         <v>8.4</v>
@@ -2620,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="BL8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BM8">
         <v>5.4</v>
@@ -2659,13 +2659,13 @@
         <v>27</v>
       </c>
       <c r="BY8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ8">
         <v>10.5</v>
       </c>
       <c r="CA8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="s">
         <v>128</v>
@@ -2688,13 +2688,13 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G9">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -2706,16 +2706,16 @@
         <v>4.5</v>
       </c>
       <c r="L9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M9">
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
         <v>2.5</v>
@@ -2724,10 +2724,10 @@
         <v>1.51</v>
       </c>
       <c r="R9">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T9">
         <v>1.54</v>
@@ -2790,124 +2790,124 @@
         <v>70</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO9">
         <v>40</v>
       </c>
       <c r="AP9">
+        <v>5.6</v>
+      </c>
+      <c r="AQ9">
         <v>5.5</v>
-      </c>
-      <c r="AQ9">
-        <v>5.4</v>
       </c>
       <c r="AR9">
         <v>6</v>
       </c>
       <c r="AS9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY9">
         <v>4.3</v>
       </c>
       <c r="AZ9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA9">
         <v>6</v>
       </c>
       <c r="BB9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF9">
         <v>3.7</v>
       </c>
       <c r="BG9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB9" t="s">
         <v>128</v>
@@ -2930,127 +2930,127 @@
         <v>122</v>
       </c>
       <c r="F10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G10">
         <v>4.1</v>
       </c>
       <c r="H10">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="I10">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="O10">
         <v>1.07</v>
       </c>
       <c r="P10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S10">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T10">
+        <v>1.33</v>
+      </c>
+      <c r="U10">
+        <v>3.7</v>
+      </c>
+      <c r="V10">
+        <v>2.22</v>
+      </c>
+      <c r="W10">
         <v>1.32</v>
       </c>
-      <c r="U10">
-        <v>3.55</v>
-      </c>
-      <c r="V10">
-        <v>2.18</v>
-      </c>
-      <c r="W10">
-        <v>1.33</v>
-      </c>
       <c r="X10">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Y10">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AA10">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AB10">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AC10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF10">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AG10">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AH10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI10">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AJ10">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AK10">
         <v>38</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AM10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN10">
         <v>14</v>
       </c>
       <c r="AO10">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AP10">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AQ10">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AR10">
         <v>20</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="AU10">
         <v>15</v>
@@ -3062,7 +3062,7 @@
         <v>14.5</v>
       </c>
       <c r="AX10">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AY10">
         <v>18</v>
@@ -3074,82 +3074,82 @@
         <v>16</v>
       </c>
       <c r="BB10">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BC10">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BD10">
         <v>24</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BF10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB10" t="s">
         <v>128</v>
@@ -3172,7 +3172,7 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
         <v>2.22</v>
@@ -3196,7 +3196,7 @@
         <v>1.15</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O11">
         <v>1.64</v>
@@ -3205,13 +3205,13 @@
         <v>1.49</v>
       </c>
       <c r="Q11">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R11">
         <v>1.17</v>
       </c>
       <c r="S11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
         <v>2.36</v>
@@ -3220,13 +3220,13 @@
         <v>1.69</v>
       </c>
       <c r="V11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y11">
         <v>10.5</v>
@@ -3238,7 +3238,7 @@
         <v>120</v>
       </c>
       <c r="AB11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
@@ -3256,7 +3256,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI11">
         <v>260</v>
@@ -3292,7 +3292,7 @@
         <v>38</v>
       </c>
       <c r="AT11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU11">
         <v>7</v>
@@ -3313,7 +3313,7 @@
         <v>26</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB11">
         <v>25</v>
@@ -3328,7 +3328,7 @@
         <v>110</v>
       </c>
       <c r="BF11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BG11">
         <v>44</v>
@@ -3349,7 +3349,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
@@ -3361,13 +3361,13 @@
         <v>19</v>
       </c>
       <c r="BQ11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT11">
         <v>7.8</v>
@@ -3379,7 +3379,7 @@
         <v>50</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3388,7 +3388,7 @@
         <v>10.5</v>
       </c>
       <c r="BZ11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA11">
         <v>10</v>
@@ -3417,10 +3417,10 @@
         <v>2.32</v>
       </c>
       <c r="G12">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H12">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="I12">
         <v>3.1</v>
@@ -3441,7 +3441,7 @@
         <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
         <v>2.42</v>
@@ -3450,7 +3450,7 @@
         <v>1.52</v>
       </c>
       <c r="R12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S12">
         <v>2.26</v>
@@ -3531,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="AS12">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AT12">
         <v>5.4</v>
@@ -3576,58 +3576,58 @@
         <v>5.3</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3656,10 +3656,10 @@
         <v>125</v>
       </c>
       <c r="F13">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G13">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H13">
         <v>4.6</v>
@@ -3671,7 +3671,7 @@
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
         <v>1.48</v>
@@ -3680,13 +3680,13 @@
         <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q13">
         <v>2.26</v>
@@ -3698,10 +3698,10 @@
         <v>4.2</v>
       </c>
       <c r="T13">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V13">
         <v>1.23</v>
@@ -3716,7 +3716,7 @@
         <v>16.5</v>
       </c>
       <c r="Z13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -3728,7 +3728,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE13">
         <v>210</v>
@@ -3749,7 +3749,7 @@
         <v>26</v>
       </c>
       <c r="AK13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13">
         <v>55</v>
@@ -3758,82 +3758,82 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO13">
         <v>300</v>
       </c>
       <c r="AP13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AR13">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS13">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU13">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="AW13">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX13">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="AY13">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BA13">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB13">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BC13">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE13">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF13">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH13">
         <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN13">
         <v>4.5</v>
@@ -3845,19 +3845,19 @@
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV13">
         <v>55</v>
@@ -3866,16 +3866,16 @@
         <v>6.6</v>
       </c>
       <c r="BX13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ13">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB13" t="s">
         <v>128</v>
@@ -3898,10 +3898,10 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G14">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H14">
         <v>5.4</v>
@@ -3910,10 +3910,10 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3922,16 +3922,16 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="O14">
         <v>1.39</v>
       </c>
       <c r="P14">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="Q14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R14">
         <v>1.14</v>
@@ -3946,7 +3946,7 @@
         <v>1.37</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
         <v>2.2</v>
@@ -3967,19 +3967,19 @@
         <v>950</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE14">
         <v>1000</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -4006,58 +4006,58 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AR14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AS14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU14">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AV14">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AW14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AX14">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AY14">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AZ14">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BA14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BB14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BC14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BD14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BE14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BF14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BG14">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4170,7 +4170,7 @@
         <v>1.38</v>
       </c>
       <c r="P15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q15">
         <v>2.16</v>
@@ -4182,7 +4182,7 @@
         <v>4</v>
       </c>
       <c r="T15">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U15">
         <v>1.79</v>
@@ -4224,7 +4224,7 @@
         <v>12</v>
       </c>
       <c r="AH15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI15">
         <v>140</v>
@@ -4254,10 +4254,10 @@
         <v>16.5</v>
       </c>
       <c r="AR15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT15">
         <v>6.2</v>
@@ -4266,10 +4266,10 @@
         <v>7.8</v>
       </c>
       <c r="AV15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX15">
         <v>7.6</v>
@@ -4281,7 +4281,7 @@
         <v>21</v>
       </c>
       <c r="BA15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB15">
         <v>13.5</v>
@@ -4290,22 +4290,22 @@
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF15">
         <v>10</v>
       </c>
       <c r="BG15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH15">
         <v>3.35</v>
       </c>
       <c r="BI15">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ15">
         <v>12</v>
@@ -4320,10 +4320,10 @@
         <v>10</v>
       </c>
       <c r="BN15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP15">
         <v>11.5</v>
@@ -4338,16 +4338,16 @@
         <v>7.8</v>
       </c>
       <c r="BT15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU15">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX15">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -400,7 +400,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-08-05 04:04:30</t>
+    <t>2026-08-05 06:11:50</t>
   </si>
 </sst>
 </file>
@@ -994,220 +994,220 @@
         <v>114</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="G2">
+        <v>8.4</v>
+      </c>
+      <c r="H2">
+        <v>1.62</v>
+      </c>
+      <c r="I2">
+        <v>1.72</v>
+      </c>
+      <c r="J2">
+        <v>3.55</v>
+      </c>
+      <c r="K2">
+        <v>4.1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.5</v>
+      </c>
+      <c r="O2">
+        <v>1.23</v>
+      </c>
+      <c r="P2">
+        <v>1.76</v>
+      </c>
+      <c r="Q2">
+        <v>2.16</v>
+      </c>
+      <c r="R2">
+        <v>1.21</v>
+      </c>
+      <c r="S2">
+        <v>4.7</v>
+      </c>
+      <c r="T2">
+        <v>1.05</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
         <v>2.36</v>
       </c>
-      <c r="H2">
-        <v>3.5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>3.1</v>
-      </c>
-      <c r="K2">
-        <v>3.45</v>
-      </c>
-      <c r="L2">
-        <v>1.44</v>
-      </c>
-      <c r="M2">
-        <v>1.09</v>
-      </c>
-      <c r="N2">
-        <v>3.15</v>
-      </c>
-      <c r="O2">
-        <v>1.39</v>
-      </c>
-      <c r="P2">
-        <v>1.68</v>
-      </c>
-      <c r="Q2">
-        <v>2.2</v>
-      </c>
-      <c r="R2">
-        <v>1.25</v>
-      </c>
-      <c r="S2">
-        <v>4.6</v>
-      </c>
-      <c r="T2">
-        <v>1.92</v>
-      </c>
-      <c r="U2">
-        <v>1.92</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>5.4</v>
       </c>
       <c r="Z2">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>140</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>790</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>990</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="AO2">
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AR2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS2">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AT2">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW2">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AX2">
         <v>3.05</v>
       </c>
       <c r="AY2">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="BA2">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="BB2">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="BC2">
-        <v>3.45</v>
+        <v>32</v>
       </c>
       <c r="BD2">
+        <v>42</v>
+      </c>
+      <c r="BE2">
+        <v>110</v>
+      </c>
+      <c r="BF2">
+        <v>3.95</v>
+      </c>
+      <c r="BG2">
+        <v>24</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
         <v>3.6</v>
       </c>
-      <c r="BE2">
-        <v>70</v>
-      </c>
-      <c r="BF2">
-        <v>3.3</v>
-      </c>
-      <c r="BG2">
-        <v>3.7</v>
-      </c>
-      <c r="BH2">
-        <v>3.35</v>
-      </c>
-      <c r="BI2">
-        <v>2.46</v>
-      </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>85</v>
+        <v>3.6</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>1.38</v>
       </c>
       <c r="BU2">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>890</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="BY2">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1236,226 +1236,226 @@
         <v>115</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="P3">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="Q3">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.44</v>
       </c>
       <c r="X3">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
+        <v>19</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>990</v>
+      </c>
+      <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
         <v>20</v>
       </c>
-      <c r="AA3">
-        <v>160</v>
-      </c>
-      <c r="AB3">
-        <v>8.4</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>16.5</v>
-      </c>
-      <c r="AE3">
-        <v>260</v>
-      </c>
-      <c r="AF3">
-        <v>19.5</v>
-      </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>990</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3">
-        <v>4.3</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
-        <v>5.7</v>
+        <v>1.31</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>1.41</v>
       </c>
       <c r="AT3">
-        <v>4.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU3">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="AV3">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="AW3">
-        <v>7</v>
+        <v>1.41</v>
       </c>
       <c r="AX3">
-        <v>5.7</v>
+        <v>1.32</v>
       </c>
       <c r="AY3">
-        <v>5.3</v>
+        <v>1.41</v>
       </c>
       <c r="AZ3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>95</v>
       </c>
       <c r="BB3">
-        <v>7</v>
+        <v>1.41</v>
       </c>
       <c r="BC3">
-        <v>7</v>
+        <v>1.41</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>95</v>
       </c>
       <c r="BE3">
-        <v>140</v>
+        <v>1.55</v>
       </c>
       <c r="BF3">
-        <v>7.2</v>
+        <v>80</v>
       </c>
       <c r="BG3">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BH3">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="BI3">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>1.88</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>590</v>
       </c>
       <c r="BO3">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="BP3">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.97</v>
+        <v>30</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="BS3">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>690</v>
       </c>
       <c r="BU3">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="CB3" t="s">
         <v>128</v>
@@ -1478,55 +1478,55 @@
         <v>116</v>
       </c>
       <c r="F4">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="G4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J4">
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W4">
         <v>1.19</v>
@@ -1535,16 +1535,16 @@
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10.5</v>
       </c>
       <c r="AA4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC4">
         <v>8.4</v>
@@ -1553,127 +1553,127 @@
         <v>12</v>
       </c>
       <c r="AE4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AG4">
         <v>26</v>
       </c>
       <c r="AH4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AK4">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AL4">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AM4">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AN4">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="AO4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP4">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AR4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AS4">
+        <v>4.9</v>
+      </c>
+      <c r="AT4">
+        <v>4.4</v>
+      </c>
+      <c r="AU4">
+        <v>3.5</v>
+      </c>
+      <c r="AV4">
+        <v>4</v>
+      </c>
+      <c r="AW4">
+        <v>5</v>
+      </c>
+      <c r="AX4">
+        <v>5.4</v>
+      </c>
+      <c r="AY4">
+        <v>4.9</v>
+      </c>
+      <c r="AZ4">
+        <v>4.9</v>
+      </c>
+      <c r="BA4">
         <v>5.5</v>
       </c>
-      <c r="AT4">
+      <c r="BB4">
+        <v>5.8</v>
+      </c>
+      <c r="BC4">
+        <v>5.7</v>
+      </c>
+      <c r="BD4">
+        <v>5.8</v>
+      </c>
+      <c r="BE4">
+        <v>5.9</v>
+      </c>
+      <c r="BF4">
+        <v>5.8</v>
+      </c>
+      <c r="BG4">
+        <v>4.9</v>
+      </c>
+      <c r="BH4">
+        <v>2.94</v>
+      </c>
+      <c r="BI4">
+        <v>2.3</v>
+      </c>
+      <c r="BJ4">
+        <v>12.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.7</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>2.28</v>
+      </c>
+      <c r="BN4">
+        <v>9</v>
+      </c>
+      <c r="BO4">
         <v>4.8</v>
       </c>
-      <c r="AU4">
-        <v>3.85</v>
-      </c>
-      <c r="AV4">
-        <v>4.5</v>
-      </c>
-      <c r="AW4">
-        <v>5.7</v>
-      </c>
-      <c r="AX4">
-        <v>6.2</v>
-      </c>
-      <c r="AY4">
-        <v>5.6</v>
-      </c>
-      <c r="AZ4">
-        <v>5.7</v>
-      </c>
-      <c r="BA4">
-        <v>6.4</v>
-      </c>
-      <c r="BB4">
-        <v>6.8</v>
-      </c>
-      <c r="BC4">
-        <v>6.8</v>
-      </c>
-      <c r="BD4">
-        <v>6.8</v>
-      </c>
-      <c r="BE4">
-        <v>7</v>
-      </c>
-      <c r="BF4">
-        <v>7</v>
-      </c>
-      <c r="BG4">
-        <v>5.5</v>
-      </c>
-      <c r="BH4">
-        <v>2.84</v>
-      </c>
-      <c r="BI4">
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>2.22</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
         <v>2.24</v>
-      </c>
-      <c r="BJ4">
-        <v>13</v>
-      </c>
-      <c r="BK4">
-        <v>5.8</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>2.22</v>
-      </c>
-      <c r="BN4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO4">
-        <v>4.9</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>2.16</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>2.18</v>
       </c>
       <c r="BT4">
         <v>4.4</v>
@@ -1682,16 +1682,16 @@
         <v>3.1</v>
       </c>
       <c r="BV4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW4">
         <v>6.2</v>
       </c>
       <c r="BX4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1723,124 +1723,124 @@
         <v>3.15</v>
       </c>
       <c r="G5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
         <v>2.42</v>
       </c>
       <c r="I5">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O5">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S5">
         <v>4.7</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W5">
         <v>1.39</v>
       </c>
       <c r="X5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>18.5</v>
       </c>
       <c r="AA5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>75</v>
       </c>
       <c r="AK5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1849,43 +1849,43 @@
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX5">
         <v>18.5</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB5">
+        <v>6.4</v>
+      </c>
+      <c r="BC5">
+        <v>6.2</v>
+      </c>
+      <c r="BD5">
+        <v>6.4</v>
+      </c>
+      <c r="BE5">
         <v>6</v>
       </c>
-      <c r="BC5">
-        <v>5.9</v>
-      </c>
-      <c r="BD5">
-        <v>5.3</v>
-      </c>
-      <c r="BE5">
-        <v>5.6</v>
-      </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>26</v>
       </c>
       <c r="BG5">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -1927,7 +1927,7 @@
         <v>25</v>
       </c>
       <c r="BW5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX5">
         <v>48</v>
@@ -1962,220 +1962,220 @@
         <v>118</v>
       </c>
       <c r="F6">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="G6">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
+        <v>24</v>
+      </c>
+      <c r="Z6">
+        <v>80</v>
+      </c>
+      <c r="AA6">
+        <v>390</v>
+      </c>
+      <c r="AB6">
+        <v>7.4</v>
+      </c>
+      <c r="AC6">
+        <v>10.5</v>
+      </c>
+      <c r="AD6">
+        <v>36</v>
+      </c>
+      <c r="AE6">
+        <v>190</v>
+      </c>
+      <c r="AF6">
+        <v>8.6</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>30</v>
+      </c>
+      <c r="AI6">
+        <v>170</v>
+      </c>
+      <c r="AJ6">
+        <v>14.5</v>
+      </c>
+      <c r="AK6">
+        <v>18</v>
+      </c>
+      <c r="AL6">
+        <v>44</v>
+      </c>
+      <c r="AM6">
+        <v>190</v>
+      </c>
+      <c r="AN6">
+        <v>10.5</v>
+      </c>
+      <c r="AO6">
+        <v>280</v>
+      </c>
+      <c r="AP6">
+        <v>11</v>
+      </c>
+      <c r="AQ6">
         <v>19</v>
       </c>
-      <c r="Z6">
-        <v>75</v>
-      </c>
-      <c r="AA6">
-        <v>280</v>
-      </c>
-      <c r="AB6">
-        <v>6.8</v>
-      </c>
-      <c r="AC6">
+      <c r="AR6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT6">
+        <v>6</v>
+      </c>
+      <c r="AU6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6">
+        <v>18.5</v>
+      </c>
+      <c r="AW6">
         <v>9</v>
       </c>
-      <c r="AD6">
-        <v>28</v>
-      </c>
-      <c r="AE6">
-        <v>200</v>
-      </c>
-      <c r="AF6">
-        <v>9.4</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>28</v>
-      </c>
-      <c r="AI6">
-        <v>200</v>
-      </c>
-      <c r="AJ6">
-        <v>17.5</v>
-      </c>
-      <c r="AK6">
+      <c r="AX6">
+        <v>7.2</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
         <v>22</v>
       </c>
-      <c r="AL6">
-        <v>50</v>
-      </c>
-      <c r="AM6">
-        <v>700</v>
-      </c>
-      <c r="AN6">
-        <v>14.5</v>
-      </c>
-      <c r="AO6">
-        <v>360</v>
-      </c>
-      <c r="AP6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6">
+      <c r="BA6">
+        <v>9.6</v>
+      </c>
+      <c r="BB6">
+        <v>11.5</v>
+      </c>
+      <c r="BC6">
         <v>15</v>
       </c>
-      <c r="AR6">
-        <v>34</v>
-      </c>
-      <c r="AS6">
-        <v>10.5</v>
-      </c>
-      <c r="AT6">
-        <v>5.7</v>
-      </c>
-      <c r="AU6">
-        <v>7.6</v>
-      </c>
-      <c r="AV6">
-        <v>19.5</v>
-      </c>
-      <c r="AW6">
-        <v>36</v>
-      </c>
-      <c r="AX6">
-        <v>7.8</v>
-      </c>
-      <c r="AY6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>19.5</v>
-      </c>
-      <c r="BA6">
-        <v>38</v>
-      </c>
-      <c r="BB6">
-        <v>14.5</v>
-      </c>
-      <c r="BC6">
-        <v>18</v>
-      </c>
       <c r="BD6">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="BE6">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.96</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO6">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ6">
         <v>5.7</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT6">
+        <v>11.5</v>
+      </c>
+      <c r="BU6">
+        <v>5.8</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
         <v>10.5</v>
       </c>
-      <c r="BU6">
-        <v>5.3</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>2.88</v>
-      </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2204,64 +2204,64 @@
         <v>119</v>
       </c>
       <c r="F7">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G7">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H7">
         <v>4.4</v>
       </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>4</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R7">
         <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z7">
         <v>40</v>
@@ -2270,13 +2270,13 @@
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>9</v>
       </c>
       <c r="AD7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE7">
         <v>110</v>
@@ -2303,7 +2303,7 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AN7">
         <v>14.5</v>
@@ -2312,46 +2312,46 @@
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7">
         <v>7.6</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BB7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD7">
         <v>23</v>
@@ -2360,13 +2360,13 @@
         <v>44</v>
       </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BH7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI7">
         <v>2.7</v>
@@ -2375,7 +2375,7 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2387,43 +2387,43 @@
         <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
         <v>30</v>
       </c>
       <c r="BS7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT7">
         <v>8.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
         <v>46</v>
       </c>
       <c r="BW7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX7">
         <v>60</v>
       </c>
       <c r="BY7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7">
         <v>26</v>
       </c>
       <c r="CA7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="s">
         <v>128</v>
@@ -2449,7 +2449,7 @@
         <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
         <v>3.3</v>
@@ -2506,7 +2506,7 @@
         <v>32</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA8">
         <v>65</v>
@@ -2518,7 +2518,7 @@
         <v>12.5</v>
       </c>
       <c r="AD8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE8">
         <v>34</v>
@@ -2533,13 +2533,13 @@
         <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ8">
         <v>32</v>
       </c>
       <c r="AK8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL8">
         <v>22</v>
@@ -2551,7 +2551,7 @@
         <v>7</v>
       </c>
       <c r="AO8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
         <v>36</v>
@@ -2584,10 +2584,10 @@
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8">
         <v>25</v>
@@ -2602,7 +2602,7 @@
         <v>30</v>
       </c>
       <c r="BF8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG8">
         <v>12</v>
@@ -2688,16 +2688,16 @@
         <v>121</v>
       </c>
       <c r="F9">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2706,67 +2706,67 @@
         <v>4.5</v>
       </c>
       <c r="L9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M9">
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="T9">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z9">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA9">
-        <v>330</v>
+        <v>95</v>
       </c>
       <c r="AB9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2790,124 +2790,124 @@
         <v>70</v>
       </c>
       <c r="AN9">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP9">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS9">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT9">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AV9">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="AW9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX9">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BB9">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BD9">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BE9">
+        <v>7</v>
+      </c>
+      <c r="BF9">
+        <v>6.8</v>
+      </c>
+      <c r="BG9">
         <v>6.4</v>
       </c>
-      <c r="BF9">
-        <v>3.7</v>
-      </c>
-      <c r="BG9">
-        <v>6</v>
-      </c>
       <c r="BH9">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BI9">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BL9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM9">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN9">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO9">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BR9">
         <v>23</v>
       </c>
       <c r="BS9">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT9">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="BV9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW9">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY9">
+        <v>5.8</v>
+      </c>
+      <c r="BZ9">
+        <v>17</v>
+      </c>
+      <c r="CA9">
         <v>4.8</v>
-      </c>
-      <c r="BZ9">
-        <v>15.5</v>
-      </c>
-      <c r="CA9">
-        <v>4</v>
       </c>
       <c r="CB9" t="s">
         <v>128</v>
@@ -2966,7 +2966,7 @@
         <v>1.23</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S10">
         <v>1.58</v>
@@ -2987,13 +2987,13 @@
         <v>85</v>
       </c>
       <c r="Y10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA10">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AB10">
         <v>46</v>
@@ -3005,13 +3005,13 @@
         <v>14</v>
       </c>
       <c r="AE10">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AF10">
         <v>55</v>
       </c>
       <c r="AG10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH10">
         <v>15</v>
@@ -3050,19 +3050,19 @@
         <v>22</v>
       </c>
       <c r="AT10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AU10">
         <v>15</v>
       </c>
       <c r="AV10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW10">
         <v>14.5</v>
       </c>
       <c r="AX10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AY10">
         <v>18</v>
@@ -3071,31 +3071,31 @@
         <v>13</v>
       </c>
       <c r="BA10">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BB10">
         <v>44</v>
       </c>
       <c r="BC10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BD10">
         <v>24</v>
       </c>
       <c r="BE10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BF10">
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH10">
         <v>7.2</v>
       </c>
       <c r="BI10">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ10">
         <v>8.6</v>
@@ -3131,7 +3131,7 @@
         <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV10">
         <v>11</v>
@@ -3143,13 +3143,13 @@
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10">
         <v>7.2</v>
       </c>
       <c r="CA10">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB10" t="s">
         <v>128</v>
@@ -3172,16 +3172,16 @@
         <v>123</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
         <v>3.1</v>
@@ -3190,43 +3190,43 @@
         <v>3.15</v>
       </c>
       <c r="L11">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M11">
         <v>1.15</v>
       </c>
       <c r="N11">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P11">
         <v>1.49</v>
       </c>
       <c r="Q11">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T11">
         <v>2.36</v>
       </c>
       <c r="U11">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y11">
         <v>10.5</v>
@@ -3238,16 +3238,16 @@
         <v>120</v>
       </c>
       <c r="AB11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>11.5</v>
@@ -3262,7 +3262,7 @@
         <v>260</v>
       </c>
       <c r="AJ11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK11">
         <v>34</v>
@@ -3274,31 +3274,31 @@
         <v>500</v>
       </c>
       <c r="AN11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP11">
         <v>7</v>
       </c>
       <c r="AQ11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW11">
         <v>38</v>
@@ -3310,31 +3310,31 @@
         <v>11</v>
       </c>
       <c r="AZ11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA11">
         <v>46</v>
       </c>
       <c r="BB11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD11">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE11">
         <v>110</v>
       </c>
       <c r="BF11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BG11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH11">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI11">
         <v>2.24</v>
@@ -3343,55 +3343,55 @@
         <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
         <v>6</v>
       </c>
       <c r="BV11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BW11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>55</v>
       </c>
       <c r="CA11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
         <v>128</v>
@@ -3414,94 +3414,94 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G12">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H12">
         <v>2.72</v>
       </c>
       <c r="I12">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="O12">
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="Q12">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T12">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U12">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
         <v>1.6</v>
       </c>
       <c r="X12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF12">
         <v>22</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH12">
         <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
         <v>36</v>
@@ -3519,115 +3519,115 @@
         <v>13.5</v>
       </c>
       <c r="AO12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP12">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR12">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AS12">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AT12">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU12">
+        <v>8.4</v>
+      </c>
+      <c r="AV12">
+        <v>11</v>
+      </c>
+      <c r="AW12">
+        <v>21</v>
+      </c>
+      <c r="AX12">
+        <v>17</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>12.5</v>
+      </c>
+      <c r="BA12">
+        <v>15</v>
+      </c>
+      <c r="BB12">
+        <v>18.5</v>
+      </c>
+      <c r="BC12">
+        <v>19.5</v>
+      </c>
+      <c r="BD12">
+        <v>15</v>
+      </c>
+      <c r="BE12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>11</v>
+      </c>
+      <c r="BG12">
+        <v>13</v>
+      </c>
+      <c r="BH12">
+        <v>4.7</v>
+      </c>
+      <c r="BI12">
+        <v>3.15</v>
+      </c>
+      <c r="BJ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK12">
         <v>4.6</v>
       </c>
-      <c r="AV12">
-        <v>5.1</v>
-      </c>
-      <c r="AW12">
-        <v>6</v>
-      </c>
-      <c r="AX12">
-        <v>5.8</v>
-      </c>
-      <c r="AY12">
-        <v>4.9</v>
-      </c>
-      <c r="AZ12">
-        <v>5.2</v>
-      </c>
-      <c r="BA12">
-        <v>6.4</v>
-      </c>
-      <c r="BB12">
-        <v>6.4</v>
-      </c>
-      <c r="BC12">
-        <v>6</v>
-      </c>
-      <c r="BD12">
-        <v>6.2</v>
-      </c>
-      <c r="BE12">
-        <v>6.8</v>
-      </c>
-      <c r="BF12">
-        <v>4.9</v>
-      </c>
-      <c r="BG12">
-        <v>5.3</v>
-      </c>
-      <c r="BH12">
-        <v>4.8</v>
-      </c>
-      <c r="BI12">
-        <v>3.05</v>
-      </c>
-      <c r="BJ12">
-        <v>9</v>
-      </c>
-      <c r="BK12">
-        <v>4.3</v>
-      </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN12">
         <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BP12">
         <v>17.5</v>
       </c>
       <c r="BQ12">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR12">
         <v>25</v>
       </c>
       <c r="BS12">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU12">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BX12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY12">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3659,13 +3659,13 @@
         <v>1.89</v>
       </c>
       <c r="G13">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H13">
         <v>4.6</v>
       </c>
       <c r="I13">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J13">
         <v>3.3</v>
@@ -3674,49 +3674,49 @@
         <v>3.6</v>
       </c>
       <c r="L13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P13">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R13">
         <v>1.25</v>
       </c>
       <c r="S13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T13">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U13">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V13">
         <v>1.23</v>
       </c>
       <c r="W13">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -3725,13 +3725,13 @@
         <v>8.4</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>210</v>
+        <v>470</v>
       </c>
       <c r="AF13">
         <v>12.5</v>
@@ -3740,16 +3740,16 @@
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI13">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AJ13">
         <v>26</v>
       </c>
       <c r="AK13">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL13">
         <v>55</v>
@@ -3758,10 +3758,10 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AO13">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="AP13">
         <v>9</v>
@@ -3770,7 +3770,7 @@
         <v>11</v>
       </c>
       <c r="AR13">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS13">
         <v>6.6</v>
@@ -3797,7 +3797,7 @@
         <v>17</v>
       </c>
       <c r="BA13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB13">
         <v>17</v>
@@ -3806,16 +3806,16 @@
         <v>18</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF13">
         <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13">
         <v>3.35</v>
@@ -3845,10 +3845,10 @@
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS13">
         <v>6.4</v>
@@ -3860,10 +3860,10 @@
         <v>4.2</v>
       </c>
       <c r="BV13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
@@ -3898,10 +3898,10 @@
         <v>126</v>
       </c>
       <c r="F14">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H14">
         <v>5.4</v>
@@ -3910,7 +3910,7 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3919,13 +3919,13 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
         <v>1.69</v>
       </c>
       <c r="O14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P14">
         <v>1.66</v>
@@ -3937,19 +3937,19 @@
         <v>1.14</v>
       </c>
       <c r="S14">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="T14">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="U14">
         <v>1.37</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W14">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -3964,7 +3964,7 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC14">
         <v>17.5</v>
@@ -4018,7 +4018,7 @@
         <v>1.3</v>
       </c>
       <c r="AT14">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU14">
         <v>6</v>
@@ -4030,7 +4030,7 @@
         <v>1.3</v>
       </c>
       <c r="AX14">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="AY14">
         <v>1.23</v>
@@ -4140,193 +4140,193 @@
         <v>127</v>
       </c>
       <c r="F15">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="G15">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="H15">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q15">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T15">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U15">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V15">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W15">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="X15">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z15">
         <v>70</v>
       </c>
       <c r="AA15">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="AB15">
         <v>7.2</v>
       </c>
       <c r="AC15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE15">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AF15">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI15">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ15">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL15">
+        <v>50</v>
+      </c>
+      <c r="AM15">
+        <v>220</v>
+      </c>
+      <c r="AN15">
+        <v>10.5</v>
+      </c>
+      <c r="AO15">
+        <v>260</v>
+      </c>
+      <c r="AP15">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15">
+        <v>18</v>
+      </c>
+      <c r="AR15">
         <v>55</v>
       </c>
-      <c r="AM15">
-        <v>210</v>
-      </c>
-      <c r="AN15">
-        <v>12.5</v>
-      </c>
-      <c r="AO15">
-        <v>210</v>
-      </c>
-      <c r="AP15">
-        <v>11</v>
-      </c>
-      <c r="AQ15">
-        <v>16.5</v>
-      </c>
-      <c r="AR15">
-        <v>6.2</v>
-      </c>
       <c r="AS15">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU15">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV15">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="AW15">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX15">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY15">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA15">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB15">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC15">
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF15">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH15">
         <v>3.35</v>
       </c>
       <c r="BI15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
+        <v>11.5</v>
+      </c>
+      <c r="BN15">
+        <v>3.85</v>
+      </c>
+      <c r="BO15">
+        <v>3.1</v>
+      </c>
+      <c r="BP15">
         <v>10</v>
-      </c>
-      <c r="BN15">
-        <v>4.2</v>
-      </c>
-      <c r="BO15">
-        <v>3.15</v>
-      </c>
-      <c r="BP15">
-        <v>11.5</v>
       </c>
       <c r="BQ15">
         <v>5.5</v>
@@ -4335,31 +4335,31 @@
         <v>1000</v>
       </c>
       <c r="BS15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT15">
+        <v>12.5</v>
+      </c>
+      <c r="BU15">
+        <v>6.2</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>11</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>11</v>
+      </c>
+      <c r="BZ15">
+        <v>22</v>
+      </c>
+      <c r="CA15">
         <v>7.8</v>
-      </c>
-      <c r="BT15">
-        <v>10.5</v>
-      </c>
-      <c r="BU15">
-        <v>5.2</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>9</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ15">
-        <v>25</v>
-      </c>
-      <c r="CA15">
-        <v>7.4</v>
       </c>
       <c r="CB15" t="s">
         <v>128</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -382,7 +382,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-08-05 08:18:51</t>
+    <t>2026-08-05 10:26:28</t>
   </si>
 </sst>
 </file>
@@ -976,220 +976,220 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="I2">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>300</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.08</v>
+      </c>
+      <c r="Q2">
+        <v>6.4</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>100</v>
+      </c>
+      <c r="T2">
+        <v>1.04</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>100</v>
+      </c>
+      <c r="W2">
+        <v>1.01</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
         <v>1.55</v>
       </c>
-      <c r="P2">
-        <v>1.51</v>
-      </c>
-      <c r="Q2">
-        <v>2.68</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
-        <v>5.5</v>
-      </c>
-      <c r="T2">
-        <v>2.24</v>
-      </c>
-      <c r="U2">
-        <v>1.63</v>
-      </c>
-      <c r="V2">
-        <v>2.02</v>
-      </c>
-      <c r="W2">
-        <v>1.2</v>
-      </c>
-      <c r="X2">
-        <v>9</v>
-      </c>
-      <c r="Y2">
-        <v>6.4</v>
-      </c>
-      <c r="Z2">
-        <v>10.5</v>
-      </c>
       <c r="AA2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>4.6</v>
+        <v>1.06</v>
       </c>
       <c r="AS2">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="AT2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>2.94</v>
       </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY2">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BB2">
         <v>7</v>
       </c>
       <c r="BC2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BE2">
-        <v>130</v>
+        <v>2.06</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BG2">
-        <v>5.6</v>
+        <v>2.06</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1218,220 +1218,220 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="I3">
-        <v>2.62</v>
+        <v>1.02</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>34</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>970</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>12</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>17</v>
+      </c>
+      <c r="AS3">
+        <v>12</v>
+      </c>
+      <c r="AT3">
         <v>11</v>
       </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
-      <c r="AD3">
+      <c r="AU3">
+        <v>13.5</v>
+      </c>
+      <c r="AV3">
         <v>12</v>
       </c>
-      <c r="AE3">
-        <v>34</v>
-      </c>
-      <c r="AF3">
-        <v>27</v>
-      </c>
-      <c r="AG3">
-        <v>15</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>80</v>
-      </c>
-      <c r="AK3">
-        <v>60</v>
-      </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>60</v>
-      </c>
-      <c r="AO3">
-        <v>38</v>
-      </c>
-      <c r="AP3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ3">
-        <v>7.6</v>
-      </c>
-      <c r="AR3">
-        <v>16.5</v>
-      </c>
-      <c r="AS3">
-        <v>32</v>
-      </c>
-      <c r="AT3">
-        <v>9.4</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>10.5</v>
-      </c>
       <c r="AW3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AX3">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="BB3">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BE3">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="BF3">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1460,220 +1460,220 @@
         <v>112</v>
       </c>
       <c r="F4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="G4">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O4">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="P4">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="Q4">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="R4">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>200</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>1.07</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>14</v>
+        <v>2.62</v>
       </c>
       <c r="AQ4">
-        <v>21</v>
+        <v>2.62</v>
       </c>
       <c r="AR4">
-        <v>34</v>
+        <v>2.62</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AV4">
-        <v>26</v>
+        <v>2.62</v>
       </c>
       <c r="AW4">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BA4">
-        <v>80</v>
+        <v>2.62</v>
       </c>
       <c r="BB4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BE4">
-        <v>130</v>
+        <v>4.7</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="BG4">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1702,94 +1702,94 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
         <v>1.93</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
         <v>1.83</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA5">
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
         <v>22</v>
@@ -1801,58 +1801,58 @@
         <v>38</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5">
         <v>14</v>
       </c>
       <c r="AO5">
-        <v>290</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
         <v>14</v>
       </c>
       <c r="AR5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AS5">
         <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
         <v>38</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC5">
         <v>16</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE5">
         <v>32</v>
@@ -1861,25 +1861,25 @@
         <v>11</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI5">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.6</v>
@@ -1888,7 +1888,7 @@
         <v>3.45</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ5">
         <v>6</v>
@@ -1897,31 +1897,31 @@
         <v>29</v>
       </c>
       <c r="BS5">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>4.8</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
         <v>122</v>
@@ -1944,88 +1944,88 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="H6">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J6">
         <v>4.1</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
+        <v>3.05</v>
+      </c>
+      <c r="Q6">
+        <v>1.45</v>
+      </c>
+      <c r="R6">
+        <v>1.84</v>
+      </c>
+      <c r="S6">
+        <v>2.14</v>
+      </c>
+      <c r="T6">
+        <v>1.46</v>
+      </c>
+      <c r="U6">
         <v>2.98</v>
       </c>
-      <c r="Q6">
-        <v>1.47</v>
-      </c>
-      <c r="R6">
-        <v>1.77</v>
-      </c>
-      <c r="S6">
-        <v>2.22</v>
-      </c>
-      <c r="T6">
-        <v>1.47</v>
-      </c>
-      <c r="U6">
-        <v>2.94</v>
-      </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>14</v>
@@ -2034,82 +2034,82 @@
         <v>32</v>
       </c>
       <c r="AJ6">
+        <v>27</v>
+      </c>
+      <c r="AK6">
+        <v>18.5</v>
+      </c>
+      <c r="AL6">
+        <v>24</v>
+      </c>
+      <c r="AM6">
+        <v>46</v>
+      </c>
+      <c r="AN6">
+        <v>8.4</v>
+      </c>
+      <c r="AO6">
+        <v>18.5</v>
+      </c>
+      <c r="AP6">
+        <v>29</v>
+      </c>
+      <c r="AQ6">
+        <v>21</v>
+      </c>
+      <c r="AR6">
         <v>30</v>
       </c>
-      <c r="AK6">
-        <v>19.5</v>
-      </c>
-      <c r="AL6">
-        <v>25</v>
-      </c>
-      <c r="AM6">
-        <v>55</v>
-      </c>
-      <c r="AN6">
-        <v>9</v>
-      </c>
-      <c r="AO6">
+      <c r="AS6">
+        <v>50</v>
+      </c>
+      <c r="AT6">
         <v>17</v>
       </c>
-      <c r="AP6">
-        <v>24</v>
-      </c>
-      <c r="AQ6">
-        <v>19.5</v>
-      </c>
-      <c r="AR6">
-        <v>27</v>
-      </c>
-      <c r="AS6">
-        <v>44</v>
-      </c>
-      <c r="AT6">
-        <v>16.5</v>
-      </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV6">
+        <v>13.5</v>
+      </c>
+      <c r="AW6">
+        <v>28</v>
+      </c>
+      <c r="AX6">
+        <v>17</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
         <v>13</v>
       </c>
-      <c r="AW6">
-        <v>25</v>
-      </c>
-      <c r="AX6">
-        <v>16</v>
-      </c>
-      <c r="AY6">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6">
-        <v>12.5</v>
-      </c>
       <c r="BA6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB6">
         <v>23</v>
       </c>
       <c r="BC6">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BG6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH6">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BI6">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ6">
         <v>8.4</v>
@@ -2121,7 +2121,7 @@
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN6">
         <v>5.9</v>
@@ -2130,13 +2130,13 @@
         <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
         <v>4.8</v>
       </c>
       <c r="BR6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS6">
         <v>5.6</v>
@@ -2145,25 +2145,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="s">
         <v>122</v>
@@ -2186,94 +2186,94 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="G7">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="H7">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="O7">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P7">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="R7">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="T7">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="U7">
         <v>2.66</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="X7">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Z7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB7">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC7">
+        <v>13</v>
+      </c>
+      <c r="AD7">
+        <v>23</v>
+      </c>
+      <c r="AE7">
+        <v>50</v>
+      </c>
+      <c r="AF7">
+        <v>16.5</v>
+      </c>
+      <c r="AG7">
         <v>12.5</v>
       </c>
-      <c r="AD7">
-        <v>21</v>
-      </c>
-      <c r="AE7">
-        <v>48</v>
-      </c>
-      <c r="AF7">
-        <v>16</v>
-      </c>
-      <c r="AG7">
-        <v>12</v>
-      </c>
       <c r="AH7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2288,34 +2288,34 @@
         <v>60</v>
       </c>
       <c r="AN7">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP7">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR7">
         <v>32</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>8.4</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2327,85 +2327,85 @@
         <v>14</v>
       </c>
       <c r="BA7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE7">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BF7">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BG7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH7">
+        <v>6.4</v>
+      </c>
+      <c r="BI7">
+        <v>4.4</v>
+      </c>
+      <c r="BJ7">
+        <v>9.4</v>
+      </c>
+      <c r="BK7">
+        <v>3.55</v>
+      </c>
+      <c r="BL7">
+        <v>65</v>
+      </c>
+      <c r="BM7">
+        <v>5.2</v>
+      </c>
+      <c r="BN7">
         <v>5.8</v>
-      </c>
-      <c r="BI7">
-        <v>4</v>
-      </c>
-      <c r="BJ7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK7">
-        <v>3.95</v>
-      </c>
-      <c r="BL7">
-        <v>75</v>
-      </c>
-      <c r="BM7">
-        <v>6.4</v>
-      </c>
-      <c r="BN7">
-        <v>5.4</v>
       </c>
       <c r="BO7">
         <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="BR7">
         <v>19.5</v>
       </c>
       <c r="BS7">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BT7">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BU7">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BV7">
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY7">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BZ7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CA7">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="CB7" t="s">
         <v>122</v>
@@ -2428,19 +2428,19 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G8">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I8">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K8">
         <v>5.4</v>
@@ -2452,58 +2452,58 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="O8">
         <v>1.07</v>
       </c>
       <c r="P8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q8">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R8">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="S8">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T8">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V8">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="W8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X8">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA8">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AB8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD8">
         <v>14</v>
       </c>
       <c r="AE8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AF8">
         <v>55</v>
@@ -2515,7 +2515,7 @@
         <v>15</v>
       </c>
       <c r="AI8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ8">
         <v>80</v>
@@ -2524,43 +2524,43 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM8">
         <v>29</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AP8">
         <v>48</v>
       </c>
       <c r="AQ8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AR8">
         <v>23</v>
       </c>
       <c r="AS8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AU8">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW8">
         <v>15.5</v>
       </c>
       <c r="AX8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY8">
         <v>18</v>
@@ -2569,13 +2569,13 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BC8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD8">
         <v>19</v>
@@ -2587,61 +2587,61 @@
         <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH8">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BI8">
         <v>5.1</v>
       </c>
       <c r="BJ8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
         <v>9.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS8">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BY8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
         <v>6.8</v>
@@ -2670,25 +2670,25 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G9">
         <v>2.26</v>
       </c>
       <c r="H9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
         <v>4.4</v>
       </c>
       <c r="J9">
+        <v>3.05</v>
+      </c>
+      <c r="K9">
         <v>3.1</v>
       </c>
-      <c r="K9">
-        <v>3.15</v>
-      </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M9">
         <v>1.15</v>
@@ -2697,10 +2697,10 @@
         <v>2.5</v>
       </c>
       <c r="O9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P9">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
         <v>2.98</v>
@@ -2712,7 +2712,7 @@
         <v>6.6</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
         <v>1.69</v>
@@ -2724,22 +2724,22 @@
         <v>1.79</v>
       </c>
       <c r="X9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA9">
         <v>120</v>
       </c>
       <c r="AB9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
         <v>19.5</v>
@@ -2751,7 +2751,7 @@
         <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>28</v>
@@ -2769,7 +2769,7 @@
         <v>75</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AN9">
         <v>36</v>
@@ -2778,31 +2778,31 @@
         <v>140</v>
       </c>
       <c r="AP9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR9">
         <v>25</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT9">
         <v>5.9</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AX9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
         <v>11</v>
@@ -2811,22 +2811,22 @@
         <v>25</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BB9">
         <v>26</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD9">
         <v>48</v>
       </c>
       <c r="BE9">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="BF9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG9">
         <v>42</v>
@@ -2835,19 +2835,19 @@
         <v>2.56</v>
       </c>
       <c r="BI9">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9">
         <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>230</v>
       </c>
       <c r="BN9">
         <v>4.9</v>
@@ -2859,22 +2859,22 @@
         <v>20</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR9">
         <v>48</v>
       </c>
       <c r="BS9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW9">
         <v>11</v>
@@ -2883,13 +2883,13 @@
         <v>75</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
         <v>55</v>
       </c>
       <c r="CA9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="s">
         <v>122</v>
@@ -2918,13 +2918,13 @@
         <v>2.54</v>
       </c>
       <c r="H10">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I10">
         <v>3.05</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
         <v>4.3</v>
@@ -2951,7 +2951,7 @@
         <v>1.61</v>
       </c>
       <c r="S10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T10">
         <v>1.54</v>
@@ -2960,7 +2960,7 @@
         <v>2.64</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
         <v>1.64</v>
@@ -2981,7 +2981,7 @@
         <v>16.5</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>14</v>
@@ -2999,7 +2999,7 @@
         <v>15.5</v>
       </c>
       <c r="AI10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ10">
         <v>36</v>
@@ -3029,19 +3029,19 @@
         <v>19.5</v>
       </c>
       <c r="AS10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT10">
         <v>13.5</v>
       </c>
       <c r="AU10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
         <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX10">
         <v>17</v>
@@ -3053,7 +3053,7 @@
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB10">
         <v>23</v>
@@ -3154,22 +3154,22 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J11">
         <v>3.25</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>1.5</v>
@@ -3178,16 +3178,16 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P11">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
         <v>1.24</v>
@@ -3202,19 +3202,19 @@
         <v>1.83</v>
       </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W11">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X11">
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA11">
         <v>500</v>
@@ -3226,10 +3226,10 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AF11">
         <v>11</v>
@@ -3238,40 +3238,40 @@
         <v>11</v>
       </c>
       <c r="AH11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI11">
         <v>240</v>
       </c>
       <c r="AJ11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>600</v>
       </c>
       <c r="AP11">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
         <v>12</v>
       </c>
       <c r="AR11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS11">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AT11">
         <v>6.4</v>
@@ -3283,7 +3283,7 @@
         <v>17.5</v>
       </c>
       <c r="AW11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX11">
         <v>9.4</v>
@@ -3292,28 +3292,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
         <v>50</v>
       </c>
       <c r="BB11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC11">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF11">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH11">
         <v>3.3</v>
@@ -3337,22 +3337,22 @@
         <v>5</v>
       </c>
       <c r="BO11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP11">
         <v>17</v>
       </c>
       <c r="BQ11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU11">
         <v>3.7</v>
@@ -3361,7 +3361,7 @@
         <v>55</v>
       </c>
       <c r="BW11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3373,7 +3373,7 @@
         <v>38</v>
       </c>
       <c r="CA11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="s">
         <v>122</v>
@@ -3396,10 +3396,10 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -3411,25 +3411,25 @@
         <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M12">
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O12">
         <v>1.46</v>
       </c>
       <c r="P12">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q12">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R12">
         <v>1.24</v>
@@ -3438,34 +3438,34 @@
         <v>4.7</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
         <v>1.74</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X12">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
         <v>970</v>
       </c>
       <c r="Z12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA12">
         <v>260</v>
       </c>
       <c r="AB12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>950</v>
@@ -3474,10 +3474,10 @@
         <v>150</v>
       </c>
       <c r="AF12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
         <v>950</v>
@@ -3486,79 +3486,79 @@
         <v>150</v>
       </c>
       <c r="AJ12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL12">
         <v>65</v>
       </c>
       <c r="AM12">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN12">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AO12">
         <v>250</v>
       </c>
       <c r="AP12">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR12">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS12">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT12">
         <v>5.8</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW12">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA12">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC12">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD12">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG12">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI12">
         <v>2.38</v>
@@ -3567,7 +3567,7 @@
         <v>14.5</v>
       </c>
       <c r="BK12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3576,7 +3576,7 @@
         <v>4.9</v>
       </c>
       <c r="BN12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO12">
         <v>3.15</v>
@@ -3585,10 +3585,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BR12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS12">
         <v>4.5</v>
@@ -3609,7 +3609,7 @@
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3638,31 +3638,31 @@
         <v>121</v>
       </c>
       <c r="F13">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H13">
         <v>7</v>
       </c>
       <c r="I13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
         <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M13">
         <v>1.08</v>
       </c>
       <c r="N13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O13">
         <v>1.38</v>
@@ -3671,25 +3671,25 @@
         <v>1.82</v>
       </c>
       <c r="Q13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T13">
         <v>2.16</v>
       </c>
       <c r="U13">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X13">
         <v>13</v>
@@ -3710,7 +3710,7 @@
         <v>9.4</v>
       </c>
       <c r="AD13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE13">
         <v>130</v>
@@ -3755,7 +3755,7 @@
         <v>50</v>
       </c>
       <c r="AS13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT13">
         <v>6.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>2026-08-05</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -304,9 +298,6 @@
     <t>23:15:00</t>
   </si>
   <si>
-    <t>ACS Dumbravita</t>
-  </si>
-  <si>
     <t>Keflavik</t>
   </si>
   <si>
@@ -331,9 +322,6 @@
     <t>Internacional de Bogotá</t>
   </si>
   <si>
-    <t>CSM Satu Mare</t>
-  </si>
-  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
@@ -358,7 +346,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-08-05 12:33:42</t>
+    <t>2026-08-05 14:41:37</t>
   </si>
 </sst>
 </file>
@@ -690,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,241 +928,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F2">
+        <v>1.91</v>
+      </c>
+      <c r="G2">
+        <v>1.92</v>
+      </c>
+      <c r="H2">
+        <v>3.85</v>
+      </c>
+      <c r="I2">
+        <v>3.9</v>
+      </c>
+      <c r="J2">
+        <v>4.4</v>
+      </c>
+      <c r="K2">
         <v>4.5</v>
       </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>1.92</v>
-      </c>
-      <c r="I2">
-        <v>1.99</v>
-      </c>
-      <c r="J2">
-        <v>3.5</v>
-      </c>
-      <c r="K2">
-        <v>3.75</v>
-      </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O2">
         <v>1.13</v>
       </c>
       <c r="P2">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="R2">
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>1.45</v>
+      </c>
+      <c r="U2">
         <v>3.1</v>
       </c>
-      <c r="T2">
-        <v>1.35</v>
-      </c>
-      <c r="U2">
-        <v>3.45</v>
-      </c>
       <c r="V2">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="X2">
+        <v>36</v>
+      </c>
+      <c r="Y2">
+        <v>30</v>
+      </c>
+      <c r="Z2">
+        <v>38</v>
+      </c>
+      <c r="AA2">
+        <v>75</v>
+      </c>
+      <c r="AB2">
+        <v>19</v>
+      </c>
+      <c r="AC2">
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <v>17</v>
+      </c>
+      <c r="AE2">
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <v>18</v>
+      </c>
+      <c r="AG2">
+        <v>11</v>
+      </c>
+      <c r="AH2">
+        <v>14</v>
+      </c>
+      <c r="AI2">
+        <v>32</v>
+      </c>
+      <c r="AJ2">
+        <v>25</v>
+      </c>
+      <c r="AK2">
+        <v>16.5</v>
+      </c>
+      <c r="AL2">
+        <v>19.5</v>
+      </c>
+      <c r="AM2">
+        <v>40</v>
+      </c>
+      <c r="AN2">
+        <v>6.6</v>
+      </c>
+      <c r="AO2">
+        <v>18.5</v>
+      </c>
+      <c r="AP2">
+        <v>30</v>
+      </c>
+      <c r="AQ2">
+        <v>26</v>
+      </c>
+      <c r="AR2">
+        <v>34</v>
+      </c>
+      <c r="AS2">
+        <v>60</v>
+      </c>
+      <c r="AT2">
+        <v>17.5</v>
+      </c>
+      <c r="AU2">
+        <v>11</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>17.5</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>13</v>
+      </c>
+      <c r="BA2">
+        <v>30</v>
+      </c>
+      <c r="BB2">
+        <v>24</v>
+      </c>
+      <c r="BC2">
+        <v>15</v>
+      </c>
+      <c r="BD2">
+        <v>19</v>
+      </c>
+      <c r="BE2">
+        <v>34</v>
+      </c>
+      <c r="BF2">
+        <v>6</v>
+      </c>
+      <c r="BG2">
+        <v>16.5</v>
+      </c>
+      <c r="BH2">
+        <v>6.4</v>
+      </c>
+      <c r="BI2">
+        <v>4.8</v>
+      </c>
+      <c r="BJ2">
+        <v>8.4</v>
+      </c>
+      <c r="BK2">
+        <v>6.8</v>
+      </c>
+      <c r="BL2">
         <v>1000</v>
       </c>
-      <c r="Y2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z2">
+      <c r="BM2">
+        <v>8.4</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>5</v>
+      </c>
+      <c r="BP2">
+        <v>12.5</v>
+      </c>
+      <c r="BQ2">
+        <v>9.6</v>
+      </c>
+      <c r="BR2">
+        <v>18</v>
+      </c>
+      <c r="BS2">
+        <v>6.6</v>
+      </c>
+      <c r="BT2">
+        <v>9.4</v>
+      </c>
+      <c r="BU2">
+        <v>7</v>
+      </c>
+      <c r="BV2">
+        <v>24</v>
+      </c>
+      <c r="BW2">
+        <v>7.2</v>
+      </c>
+      <c r="BX2">
+        <v>26</v>
+      </c>
+      <c r="BY2">
+        <v>7</v>
+      </c>
+      <c r="BZ2">
         <v>11.5</v>
       </c>
-      <c r="AA2">
-        <v>38</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>6.2</v>
-      </c>
-      <c r="AD2">
-        <v>8.4</v>
-      </c>
-      <c r="AE2">
-        <v>25</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2">
-        <v>12.5</v>
-      </c>
-      <c r="AI2">
-        <v>42</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>32</v>
-      </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
+      <c r="CA2">
+        <v>9.4</v>
+      </c>
+      <c r="CB2" t="s">
         <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>42</v>
-      </c>
-      <c r="AO2">
-        <v>34</v>
-      </c>
-      <c r="AP2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>7.8</v>
-      </c>
-      <c r="AR2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS2">
-        <v>22</v>
-      </c>
-      <c r="AT2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2">
-        <v>5.6</v>
-      </c>
-      <c r="AV2">
-        <v>7.2</v>
-      </c>
-      <c r="AW2">
-        <v>18</v>
-      </c>
-      <c r="AX2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>10.5</v>
-      </c>
-      <c r="BA2">
-        <v>28</v>
-      </c>
-      <c r="BB2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC2">
-        <v>22</v>
-      </c>
-      <c r="BD2">
-        <v>26</v>
-      </c>
-      <c r="BE2">
-        <v>60</v>
-      </c>
-      <c r="BF2">
-        <v>26</v>
-      </c>
-      <c r="BG2">
-        <v>23</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>15.5</v>
-      </c>
-      <c r="BJ2">
-        <v>5.9</v>
-      </c>
-      <c r="BK2">
-        <v>5.2</v>
-      </c>
-      <c r="BL2">
-        <v>950</v>
-      </c>
-      <c r="BM2">
-        <v>15</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>15.5</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>15.5</v>
-      </c>
-      <c r="BR2">
-        <v>65</v>
-      </c>
-      <c r="BS2">
-        <v>42</v>
-      </c>
-      <c r="BT2">
-        <v>1.59</v>
-      </c>
-      <c r="BU2">
-        <v>1.52</v>
-      </c>
-      <c r="BV2">
-        <v>10.5</v>
-      </c>
-      <c r="BW2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX2">
-        <v>46</v>
-      </c>
-      <c r="BY2">
-        <v>18.5</v>
-      </c>
-      <c r="BZ2">
-        <v>120</v>
-      </c>
-      <c r="CA2">
-        <v>32</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,1209 +1170,1209 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M3">
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
         <v>1.41</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="T3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AB3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD3">
+        <v>25</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
         <v>17.5</v>
-      </c>
-      <c r="AE3">
-        <v>34</v>
-      </c>
-      <c r="AF3">
-        <v>18.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
+        <v>19.5</v>
+      </c>
+      <c r="AI3">
+        <v>44</v>
+      </c>
+      <c r="AJ3">
+        <v>22</v>
+      </c>
+      <c r="AK3">
+        <v>15.5</v>
+      </c>
+      <c r="AL3">
+        <v>24</v>
+      </c>
+      <c r="AM3">
+        <v>60</v>
+      </c>
+      <c r="AN3">
+        <v>5.1</v>
+      </c>
+      <c r="AO3">
+        <v>32</v>
+      </c>
+      <c r="AP3">
+        <v>13</v>
+      </c>
+      <c r="AQ3">
+        <v>22</v>
+      </c>
+      <c r="AR3">
+        <v>18</v>
+      </c>
+      <c r="AS3">
+        <v>8</v>
+      </c>
+      <c r="AT3">
         <v>14.5</v>
       </c>
-      <c r="AI3">
-        <v>32</v>
-      </c>
-      <c r="AJ3">
-        <v>25</v>
-      </c>
-      <c r="AK3">
+      <c r="AU3">
+        <v>10.5</v>
+      </c>
+      <c r="AV3">
+        <v>18.5</v>
+      </c>
+      <c r="AW3">
+        <v>20</v>
+      </c>
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>14</v>
+      </c>
+      <c r="BA3">
+        <v>20</v>
+      </c>
+      <c r="BB3">
         <v>17</v>
       </c>
-      <c r="AL3">
-        <v>22</v>
-      </c>
-      <c r="AM3">
-        <v>44</v>
-      </c>
-      <c r="AN3">
-        <v>6.6</v>
-      </c>
-      <c r="AO3">
-        <v>19</v>
-      </c>
-      <c r="AP3">
-        <v>34</v>
-      </c>
-      <c r="AQ3">
-        <v>24</v>
-      </c>
-      <c r="AR3">
-        <v>30</v>
-      </c>
-      <c r="AS3">
-        <v>55</v>
-      </c>
-      <c r="AT3">
-        <v>17.5</v>
-      </c>
-      <c r="AU3">
-        <v>11</v>
-      </c>
-      <c r="AV3">
-        <v>15</v>
-      </c>
-      <c r="AW3">
-        <v>30</v>
-      </c>
-      <c r="AX3">
-        <v>17</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
+      <c r="BC3">
         <v>12.5</v>
       </c>
-      <c r="BA3">
-        <v>29</v>
-      </c>
-      <c r="BB3">
-        <v>22</v>
-      </c>
-      <c r="BC3">
-        <v>15.5</v>
-      </c>
       <c r="BD3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BH3">
         <v>6.2</v>
       </c>
       <c r="BI3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BJ3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3">
         <v>4.2</v>
       </c>
       <c r="BL3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BQ3">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BS3">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
         <v>32</v>
       </c>
       <c r="BY3">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA3">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>1.93</v>
       </c>
       <c r="I4">
+        <v>1.97</v>
+      </c>
+      <c r="J4">
+        <v>4.9</v>
+      </c>
+      <c r="K4">
+        <v>5.2</v>
+      </c>
+      <c r="L4">
+        <v>1.14</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>14</v>
+      </c>
+      <c r="O4">
+        <v>1.07</v>
+      </c>
+      <c r="P4">
+        <v>5.3</v>
+      </c>
+      <c r="Q4">
+        <v>1.21</v>
+      </c>
+      <c r="R4">
+        <v>2.82</v>
+      </c>
+      <c r="S4">
+        <v>1.52</v>
+      </c>
+      <c r="T4">
+        <v>1.28</v>
+      </c>
+      <c r="U4">
+        <v>4.2</v>
+      </c>
+      <c r="V4">
+        <v>2.02</v>
+      </c>
+      <c r="W4">
+        <v>1.39</v>
+      </c>
+      <c r="X4">
+        <v>130</v>
+      </c>
+      <c r="Y4">
+        <v>36</v>
+      </c>
+      <c r="Z4">
+        <v>29</v>
+      </c>
+      <c r="AA4">
+        <v>32</v>
+      </c>
+      <c r="AB4">
+        <v>60</v>
+      </c>
+      <c r="AC4">
+        <v>18.5</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <v>18.5</v>
+      </c>
+      <c r="AF4">
+        <v>110</v>
+      </c>
+      <c r="AG4">
+        <v>21</v>
+      </c>
+      <c r="AH4">
+        <v>14.5</v>
+      </c>
+      <c r="AI4">
+        <v>18</v>
+      </c>
+      <c r="AJ4">
+        <v>75</v>
+      </c>
+      <c r="AK4">
+        <v>34</v>
+      </c>
+      <c r="AL4">
+        <v>25</v>
+      </c>
+      <c r="AM4">
+        <v>28</v>
+      </c>
+      <c r="AN4">
+        <v>11</v>
+      </c>
+      <c r="AO4">
+        <v>4.6</v>
+      </c>
+      <c r="AP4">
+        <v>55</v>
+      </c>
+      <c r="AQ4">
+        <v>30</v>
+      </c>
+      <c r="AR4">
+        <v>25</v>
+      </c>
+      <c r="AS4">
+        <v>27</v>
+      </c>
+      <c r="AT4">
+        <v>42</v>
+      </c>
+      <c r="AU4">
+        <v>16</v>
+      </c>
+      <c r="AV4">
+        <v>13</v>
+      </c>
+      <c r="AW4">
+        <v>16</v>
+      </c>
+      <c r="AX4">
+        <v>42</v>
+      </c>
+      <c r="AY4">
+        <v>18</v>
+      </c>
+      <c r="AZ4">
+        <v>12.5</v>
+      </c>
+      <c r="BA4">
+        <v>16</v>
+      </c>
+      <c r="BB4">
+        <v>40</v>
+      </c>
+      <c r="BC4">
+        <v>28</v>
+      </c>
+      <c r="BD4">
+        <v>22</v>
+      </c>
+      <c r="BE4">
+        <v>24</v>
+      </c>
+      <c r="BF4">
+        <v>9.6</v>
+      </c>
+      <c r="BG4">
+        <v>4.2</v>
+      </c>
+      <c r="BH4">
+        <v>8</v>
+      </c>
+      <c r="BI4">
+        <v>6.6</v>
+      </c>
+      <c r="BJ4">
+        <v>8</v>
+      </c>
+      <c r="BK4">
+        <v>6.6</v>
+      </c>
+      <c r="BL4">
+        <v>34</v>
+      </c>
+      <c r="BM4">
+        <v>11</v>
+      </c>
+      <c r="BN4">
+        <v>9</v>
+      </c>
+      <c r="BO4">
+        <v>7.8</v>
+      </c>
+      <c r="BP4">
+        <v>21</v>
+      </c>
+      <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>18.5</v>
+      </c>
+      <c r="BS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT4">
+        <v>7</v>
+      </c>
+      <c r="BU4">
+        <v>6</v>
+      </c>
+      <c r="BV4">
+        <v>12</v>
+      </c>
+      <c r="BW4">
+        <v>9.6</v>
+      </c>
+      <c r="BX4">
+        <v>14</v>
+      </c>
+      <c r="BY4">
+        <v>7.6</v>
+      </c>
+      <c r="BZ4">
+        <v>6.6</v>
+      </c>
+      <c r="CA4">
         <v>5.4</v>
       </c>
-      <c r="J4">
-        <v>4.7</v>
-      </c>
-      <c r="K4">
-        <v>5.6</v>
-      </c>
-      <c r="L4">
-        <v>1.2</v>
-      </c>
-      <c r="M4">
-        <v>1.02</v>
-      </c>
-      <c r="N4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O4">
-        <v>1.11</v>
-      </c>
-      <c r="P4">
-        <v>3.4</v>
-      </c>
-      <c r="Q4">
-        <v>1.4</v>
-      </c>
-      <c r="R4">
-        <v>2.02</v>
-      </c>
-      <c r="S4">
-        <v>1.88</v>
-      </c>
-      <c r="T4">
-        <v>1.45</v>
-      </c>
-      <c r="U4">
-        <v>2.78</v>
-      </c>
-      <c r="V4">
-        <v>1.22</v>
-      </c>
-      <c r="W4">
-        <v>2.46</v>
-      </c>
-      <c r="X4">
-        <v>50</v>
-      </c>
-      <c r="Y4">
-        <v>38</v>
-      </c>
-      <c r="Z4">
-        <v>55</v>
-      </c>
-      <c r="AA4">
-        <v>150</v>
-      </c>
-      <c r="AB4">
-        <v>20</v>
-      </c>
-      <c r="AC4">
-        <v>14</v>
-      </c>
-      <c r="AD4">
-        <v>24</v>
-      </c>
-      <c r="AE4">
-        <v>55</v>
-      </c>
-      <c r="AF4">
-        <v>18</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>44</v>
-      </c>
-      <c r="AJ4">
-        <v>20</v>
-      </c>
-      <c r="AK4">
-        <v>16.5</v>
-      </c>
-      <c r="AL4">
-        <v>24</v>
-      </c>
-      <c r="AM4">
-        <v>55</v>
-      </c>
-      <c r="AN4">
-        <v>5.1</v>
-      </c>
-      <c r="AO4">
-        <v>28</v>
-      </c>
-      <c r="AP4">
-        <v>29</v>
-      </c>
-      <c r="AQ4">
-        <v>27</v>
-      </c>
-      <c r="AR4">
-        <v>40</v>
-      </c>
-      <c r="AS4">
-        <v>80</v>
-      </c>
-      <c r="AT4">
-        <v>16</v>
-      </c>
-      <c r="AU4">
-        <v>10.5</v>
-      </c>
-      <c r="AV4">
-        <v>18.5</v>
-      </c>
-      <c r="AW4">
-        <v>34</v>
-      </c>
-      <c r="AX4">
-        <v>13</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>14</v>
-      </c>
-      <c r="BA4">
-        <v>26</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>18</v>
-      </c>
-      <c r="BE4">
-        <v>38</v>
-      </c>
-      <c r="BF4">
-        <v>4.2</v>
-      </c>
-      <c r="BG4">
-        <v>21</v>
-      </c>
-      <c r="BH4">
-        <v>6.2</v>
-      </c>
-      <c r="BI4">
-        <v>4.7</v>
-      </c>
-      <c r="BJ4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK4">
-        <v>4.2</v>
-      </c>
-      <c r="BL4">
-        <v>60</v>
-      </c>
-      <c r="BM4">
-        <v>6.8</v>
-      </c>
-      <c r="BN4">
-        <v>5.7</v>
-      </c>
-      <c r="BO4">
-        <v>4.4</v>
-      </c>
-      <c r="BP4">
-        <v>11.5</v>
-      </c>
-      <c r="BQ4">
-        <v>4.6</v>
-      </c>
-      <c r="BR4">
-        <v>17.5</v>
-      </c>
-      <c r="BS4">
-        <v>5.3</v>
-      </c>
-      <c r="BT4">
-        <v>10</v>
-      </c>
-      <c r="BU4">
-        <v>4.3</v>
-      </c>
-      <c r="BV4">
-        <v>34</v>
-      </c>
-      <c r="BW4">
-        <v>6.2</v>
-      </c>
-      <c r="BX4">
-        <v>32</v>
-      </c>
-      <c r="BY4">
-        <v>6.2</v>
-      </c>
-      <c r="BZ4">
-        <v>9.6</v>
-      </c>
-      <c r="CA4">
-        <v>4.2</v>
-      </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="G5">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="H5">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="I5">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="P5">
-        <v>5.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
-        <v>1.21</v>
+        <v>2.96</v>
       </c>
       <c r="R5">
-        <v>2.82</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
-        <v>1.52</v>
+        <v>6.4</v>
       </c>
       <c r="T5">
+        <v>2.36</v>
+      </c>
+      <c r="U5">
+        <v>1.69</v>
+      </c>
+      <c r="V5">
         <v>1.29</v>
       </c>
-      <c r="U5">
-        <v>4.2</v>
-      </c>
-      <c r="V5">
-        <v>2.1</v>
-      </c>
       <c r="W5">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="X5">
-        <v>90</v>
+        <v>7.8</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>55</v>
+        <v>6.4</v>
       </c>
       <c r="AC5">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AK5">
         <v>34</v>
       </c>
       <c r="AL5">
+        <v>75</v>
+      </c>
+      <c r="AM5">
+        <v>250</v>
+      </c>
+      <c r="AN5">
+        <v>36</v>
+      </c>
+      <c r="AO5">
+        <v>140</v>
+      </c>
+      <c r="AP5">
+        <v>7</v>
+      </c>
+      <c r="AQ5">
+        <v>9.6</v>
+      </c>
+      <c r="AR5">
+        <v>25</v>
+      </c>
+      <c r="AS5">
+        <v>85</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>17.5</v>
+      </c>
+      <c r="AW5">
+        <v>70</v>
+      </c>
+      <c r="AX5">
+        <v>10.5</v>
+      </c>
+      <c r="AY5">
+        <v>11</v>
+      </c>
+      <c r="AZ5">
+        <v>25</v>
+      </c>
+      <c r="BA5">
+        <v>85</v>
+      </c>
+      <c r="BB5">
         <v>26</v>
       </c>
-      <c r="AM5">
-        <v>28</v>
-      </c>
-      <c r="AN5">
-        <v>11</v>
-      </c>
-      <c r="AO5">
-        <v>4.4</v>
-      </c>
-      <c r="AP5">
-        <v>55</v>
-      </c>
-      <c r="AQ5">
+      <c r="BC5">
         <v>27</v>
       </c>
-      <c r="AR5">
-        <v>24</v>
-      </c>
-      <c r="AS5">
-        <v>27</v>
-      </c>
-      <c r="AT5">
-        <v>44</v>
-      </c>
-      <c r="AU5">
-        <v>16.5</v>
-      </c>
-      <c r="AV5">
-        <v>13</v>
-      </c>
-      <c r="AW5">
-        <v>16</v>
-      </c>
-      <c r="AX5">
-        <v>32</v>
-      </c>
-      <c r="AY5">
-        <v>18.5</v>
-      </c>
-      <c r="AZ5">
+      <c r="BD5">
+        <v>48</v>
+      </c>
+      <c r="BE5">
+        <v>180</v>
+      </c>
+      <c r="BF5">
+        <v>30</v>
+      </c>
+      <c r="BG5">
+        <v>48</v>
+      </c>
+      <c r="BH5">
+        <v>2.56</v>
+      </c>
+      <c r="BI5">
+        <v>2.42</v>
+      </c>
+      <c r="BJ5">
         <v>12.5</v>
       </c>
-      <c r="BA5">
-        <v>15.5</v>
-      </c>
-      <c r="BB5">
-        <v>48</v>
-      </c>
-      <c r="BC5">
-        <v>25</v>
-      </c>
-      <c r="BD5">
-        <v>18.5</v>
-      </c>
-      <c r="BE5">
-        <v>23</v>
-      </c>
-      <c r="BF5">
-        <v>9.4</v>
-      </c>
-      <c r="BG5">
-        <v>4</v>
-      </c>
-      <c r="BH5">
-        <v>8</v>
-      </c>
-      <c r="BI5">
-        <v>5.2</v>
-      </c>
-      <c r="BJ5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BL5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="BN5">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ5">
         <v>8.800000000000001</v>
       </c>
       <c r="BR5">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="BS5">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
+        <v>46</v>
+      </c>
+      <c r="BW5">
         <v>12</v>
       </c>
-      <c r="BW5">
-        <v>6.6</v>
-      </c>
       <c r="BX5">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BZ5">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="CA5">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="I6">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
+        <v>1.19</v>
+      </c>
+      <c r="P6">
+        <v>2.52</v>
+      </c>
+      <c r="Q6">
+        <v>1.62</v>
+      </c>
+      <c r="R6">
+        <v>1.61</v>
+      </c>
+      <c r="S6">
+        <v>2.48</v>
+      </c>
+      <c r="T6">
+        <v>1.56</v>
+      </c>
+      <c r="U6">
+        <v>2.58</v>
+      </c>
+      <c r="V6">
+        <v>1.51</v>
+      </c>
+      <c r="W6">
         <v>1.64</v>
       </c>
-      <c r="P6">
-        <v>1.48</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
-      </c>
-      <c r="R6">
-        <v>1.17</v>
-      </c>
-      <c r="S6">
-        <v>6.6</v>
-      </c>
-      <c r="T6">
-        <v>2.36</v>
-      </c>
-      <c r="U6">
-        <v>1.69</v>
-      </c>
-      <c r="V6">
-        <v>1.29</v>
-      </c>
-      <c r="W6">
-        <v>1.81</v>
-      </c>
       <c r="X6">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="Z6">
+        <v>24</v>
+      </c>
+      <c r="AA6">
+        <v>46</v>
+      </c>
+      <c r="AB6">
+        <v>17</v>
+      </c>
+      <c r="AC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>14</v>
+      </c>
+      <c r="AE6">
+        <v>28</v>
+      </c>
+      <c r="AF6">
+        <v>21</v>
+      </c>
+      <c r="AG6">
+        <v>13</v>
+      </c>
+      <c r="AH6">
+        <v>15.5</v>
+      </c>
+      <c r="AI6">
+        <v>34</v>
+      </c>
+      <c r="AJ6">
+        <v>36</v>
+      </c>
+      <c r="AK6">
+        <v>24</v>
+      </c>
+      <c r="AL6">
         <v>30</v>
       </c>
-      <c r="AA6">
-        <v>120</v>
-      </c>
-      <c r="AB6">
-        <v>6.4</v>
-      </c>
-      <c r="AC6">
-        <v>7.2</v>
-      </c>
-      <c r="AD6">
+      <c r="AM6">
+        <v>70</v>
+      </c>
+      <c r="AN6">
+        <v>14</v>
+      </c>
+      <c r="AO6">
+        <v>16.5</v>
+      </c>
+      <c r="AP6">
+        <v>18</v>
+      </c>
+      <c r="AQ6">
+        <v>14.5</v>
+      </c>
+      <c r="AR6">
         <v>19.5</v>
       </c>
-      <c r="AE6">
-        <v>85</v>
-      </c>
-      <c r="AF6">
+      <c r="AS6">
+        <v>32</v>
+      </c>
+      <c r="AT6">
+        <v>13.5</v>
+      </c>
+      <c r="AU6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV6">
         <v>11.5</v>
       </c>
-      <c r="AG6">
+      <c r="AW6">
+        <v>21</v>
+      </c>
+      <c r="AX6">
+        <v>17</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
         <v>12.5</v>
       </c>
-      <c r="AH6">
-        <v>28</v>
-      </c>
-      <c r="AI6">
-        <v>120</v>
-      </c>
-      <c r="AJ6">
-        <v>30</v>
-      </c>
-      <c r="AK6">
-        <v>34</v>
-      </c>
-      <c r="AL6">
-        <v>75</v>
-      </c>
-      <c r="AM6">
-        <v>250</v>
-      </c>
-      <c r="AN6">
-        <v>36</v>
-      </c>
-      <c r="AO6">
-        <v>150</v>
-      </c>
-      <c r="AP6">
-        <v>7</v>
-      </c>
-      <c r="AQ6">
-        <v>9.6</v>
-      </c>
-      <c r="AR6">
+      <c r="BA6">
         <v>25</v>
-      </c>
-      <c r="AS6">
-        <v>65</v>
-      </c>
-      <c r="AT6">
-        <v>5.9</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>17.5</v>
-      </c>
-      <c r="AW6">
-        <v>40</v>
-      </c>
-      <c r="AX6">
-        <v>10.5</v>
-      </c>
-      <c r="AY6">
-        <v>11</v>
-      </c>
-      <c r="AZ6">
-        <v>25</v>
-      </c>
-      <c r="BA6">
-        <v>55</v>
       </c>
       <c r="BB6">
         <v>26</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="BE6">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="BF6">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BH6">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="BI6">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>230</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6">
+        <v>6.2</v>
+      </c>
+      <c r="BO6">
+        <v>4.5</v>
+      </c>
+      <c r="BP6">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6">
+        <v>6.6</v>
+      </c>
+      <c r="BR6">
+        <v>25</v>
+      </c>
+      <c r="BS6">
+        <v>7.4</v>
+      </c>
+      <c r="BT6">
+        <v>6.6</v>
+      </c>
+      <c r="BU6">
         <v>4.8</v>
       </c>
-      <c r="BO6">
-        <v>4.3</v>
-      </c>
-      <c r="BP6">
-        <v>20</v>
-      </c>
-      <c r="BQ6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR6">
-        <v>48</v>
-      </c>
-      <c r="BS6">
-        <v>12</v>
-      </c>
-      <c r="BT6">
-        <v>7.6</v>
-      </c>
-      <c r="BU6">
-        <v>5.1</v>
-      </c>
       <c r="BV6">
-        <v>48</v>
+        <v>19.5</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BX6">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="BY6">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="G7">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="H7">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="I7">
+        <v>5.2</v>
+      </c>
+      <c r="J7">
+        <v>3.3</v>
+      </c>
+      <c r="K7">
+        <v>3.55</v>
+      </c>
+      <c r="L7">
+        <v>1.5</v>
+      </c>
+      <c r="M7">
+        <v>1.1</v>
+      </c>
+      <c r="N7">
         <v>2.96</v>
       </c>
-      <c r="J7">
-        <v>3.8</v>
-      </c>
-      <c r="K7">
-        <v>4.2</v>
-      </c>
-      <c r="L7">
-        <v>1.29</v>
-      </c>
-      <c r="M7">
-        <v>1.04</v>
-      </c>
-      <c r="N7">
-        <v>5.5</v>
-      </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="P7">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="AA7">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB7">
+        <v>7.4</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>21</v>
+      </c>
+      <c r="AE7">
+        <v>210</v>
+      </c>
+      <c r="AF7">
+        <v>11.5</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>28</v>
+      </c>
+      <c r="AI7">
+        <v>240</v>
+      </c>
+      <c r="AJ7">
+        <v>28</v>
+      </c>
+      <c r="AK7">
+        <v>29</v>
+      </c>
+      <c r="AL7">
+        <v>120</v>
+      </c>
+      <c r="AM7">
+        <v>580</v>
+      </c>
+      <c r="AN7">
+        <v>21</v>
+      </c>
+      <c r="AO7">
+        <v>600</v>
+      </c>
+      <c r="AP7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ7">
+        <v>11.5</v>
+      </c>
+      <c r="AR7">
         <v>16.5</v>
       </c>
-      <c r="AC7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7">
-        <v>14</v>
-      </c>
-      <c r="AE7">
-        <v>28</v>
-      </c>
-      <c r="AF7">
+      <c r="AS7">
+        <v>10.5</v>
+      </c>
+      <c r="AT7">
+        <v>6.2</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>17</v>
+      </c>
+      <c r="AW7">
+        <v>34</v>
+      </c>
+      <c r="AX7">
+        <v>9.4</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>12</v>
+      </c>
+      <c r="BA7">
+        <v>40</v>
+      </c>
+      <c r="BB7">
+        <v>20</v>
+      </c>
+      <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
         <v>22</v>
       </c>
-      <c r="AG7">
-        <v>13</v>
-      </c>
-      <c r="AH7">
-        <v>15.5</v>
-      </c>
-      <c r="AI7">
-        <v>32</v>
-      </c>
-      <c r="AJ7">
-        <v>36</v>
-      </c>
-      <c r="AK7">
-        <v>24</v>
-      </c>
-      <c r="AL7">
-        <v>30</v>
-      </c>
-      <c r="AM7">
-        <v>70</v>
-      </c>
-      <c r="AN7">
-        <v>14</v>
-      </c>
-      <c r="AO7">
-        <v>16</v>
-      </c>
-      <c r="AP7">
-        <v>20</v>
-      </c>
-      <c r="AQ7">
-        <v>15</v>
-      </c>
-      <c r="AR7">
-        <v>19.5</v>
-      </c>
-      <c r="AS7">
-        <v>30</v>
-      </c>
-      <c r="AT7">
-        <v>14</v>
-      </c>
-      <c r="AU7">
-        <v>8.4</v>
-      </c>
-      <c r="AV7">
-        <v>11.5</v>
-      </c>
-      <c r="AW7">
-        <v>21</v>
-      </c>
-      <c r="AX7">
-        <v>17.5</v>
-      </c>
-      <c r="AY7">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7">
+      <c r="BE7">
+        <v>120</v>
+      </c>
+      <c r="BF7">
+        <v>7.2</v>
+      </c>
+      <c r="BG7">
+        <v>10</v>
+      </c>
+      <c r="BH7">
+        <v>3.3</v>
+      </c>
+      <c r="BI7">
+        <v>2.5</v>
+      </c>
+      <c r="BJ7">
         <v>12.5</v>
       </c>
-      <c r="BA7">
-        <v>25</v>
-      </c>
-      <c r="BB7">
-        <v>25</v>
-      </c>
-      <c r="BC7">
-        <v>20</v>
-      </c>
-      <c r="BD7">
-        <v>24</v>
-      </c>
-      <c r="BE7">
-        <v>44</v>
-      </c>
-      <c r="BF7">
-        <v>11.5</v>
-      </c>
-      <c r="BG7">
-        <v>13.5</v>
-      </c>
-      <c r="BH7">
-        <v>4.6</v>
-      </c>
-      <c r="BI7">
-        <v>3.45</v>
-      </c>
-      <c r="BJ7">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BK7">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.199999999999999</v>
+        <v>140</v>
       </c>
       <c r="BN7">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP7">
         <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BU7">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="BV7">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="BW7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2392,37 +2380,37 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="G8">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="I8">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M8">
         <v>1.1</v>
@@ -2431,202 +2419,202 @@
         <v>2.96</v>
       </c>
       <c r="O8">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P8">
         <v>1.65</v>
       </c>
       <c r="Q8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>1.24</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="X8">
         <v>11</v>
       </c>
       <c r="Y8">
+        <v>15.5</v>
+      </c>
+      <c r="Z8">
+        <v>70</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>6.4</v>
+      </c>
+      <c r="AC8">
+        <v>8.4</v>
+      </c>
+      <c r="AD8">
+        <v>32</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>32</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>18.5</v>
+      </c>
+      <c r="AK8">
+        <v>28</v>
+      </c>
+      <c r="AL8">
+        <v>75</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>16.5</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>9.6</v>
+      </c>
+      <c r="AQ8">
         <v>14</v>
       </c>
-      <c r="Z8">
+      <c r="AR8">
+        <v>27</v>
+      </c>
+      <c r="AS8">
         <v>44</v>
       </c>
-      <c r="AA8">
-        <v>350</v>
-      </c>
-      <c r="AB8">
-        <v>7.4</v>
-      </c>
-      <c r="AC8">
+      <c r="AT8">
+        <v>5.8</v>
+      </c>
+      <c r="AU8">
         <v>7.8</v>
       </c>
-      <c r="AD8">
+      <c r="AV8">
         <v>21</v>
       </c>
-      <c r="AE8">
-        <v>95</v>
-      </c>
-      <c r="AF8">
-        <v>11.5</v>
-      </c>
-      <c r="AG8">
-        <v>11</v>
-      </c>
-      <c r="AH8">
-        <v>30</v>
-      </c>
-      <c r="AI8">
-        <v>130</v>
-      </c>
-      <c r="AJ8">
-        <v>28</v>
-      </c>
-      <c r="AK8">
+      <c r="AW8">
+        <v>38</v>
+      </c>
+      <c r="AX8">
+        <v>8</v>
+      </c>
+      <c r="AY8">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8">
+        <v>19</v>
+      </c>
+      <c r="BA8">
+        <v>70</v>
+      </c>
+      <c r="BB8">
+        <v>16</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
         <v>29</v>
       </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>580</v>
-      </c>
-      <c r="AN8">
-        <v>21</v>
-      </c>
-      <c r="AO8">
-        <v>600</v>
-      </c>
-      <c r="AP8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ8">
-        <v>11.5</v>
-      </c>
-      <c r="AR8">
-        <v>24</v>
-      </c>
-      <c r="AS8">
-        <v>60</v>
-      </c>
-      <c r="AT8">
-        <v>6.2</v>
-      </c>
-      <c r="AU8">
-        <v>6.8</v>
-      </c>
-      <c r="AV8">
-        <v>17</v>
-      </c>
-      <c r="AW8">
-        <v>42</v>
-      </c>
-      <c r="AX8">
-        <v>9.6</v>
-      </c>
-      <c r="AY8">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8">
-        <v>19.5</v>
-      </c>
-      <c r="BA8">
-        <v>50</v>
-      </c>
-      <c r="BB8">
-        <v>20</v>
-      </c>
-      <c r="BC8">
-        <v>21</v>
-      </c>
-      <c r="BD8">
-        <v>30</v>
-      </c>
       <c r="BE8">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="BF8">
         <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI8">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK8">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>140</v>
+        <v>5.1</v>
       </c>
       <c r="BN8">
+        <v>4.6</v>
+      </c>
+      <c r="BO8">
+        <v>3.15</v>
+      </c>
+      <c r="BP8">
+        <v>15.5</v>
+      </c>
+      <c r="BQ8">
+        <v>3.9</v>
+      </c>
+      <c r="BR8">
+        <v>44</v>
+      </c>
+      <c r="BS8">
+        <v>4.7</v>
+      </c>
+      <c r="BT8">
+        <v>11.5</v>
+      </c>
+      <c r="BU8">
+        <v>3.6</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>4.9</v>
+      </c>
+      <c r="BX8">
+        <v>100</v>
+      </c>
+      <c r="BY8">
         <v>5</v>
       </c>
-      <c r="BO8">
-        <v>3.6</v>
-      </c>
-      <c r="BP8">
-        <v>17.5</v>
-      </c>
-      <c r="BQ8">
-        <v>4.5</v>
-      </c>
-      <c r="BR8">
-        <v>40</v>
-      </c>
-      <c r="BS8">
-        <v>5.3</v>
-      </c>
-      <c r="BT8">
-        <v>9</v>
-      </c>
-      <c r="BU8">
-        <v>3.65</v>
-      </c>
-      <c r="BV8">
-        <v>55</v>
-      </c>
-      <c r="BW8">
-        <v>5.5</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>5.6</v>
-      </c>
       <c r="BZ8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2634,483 +2622,241 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F9">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="G9">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="H9">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S9">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V9">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="X9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="Z9">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB9">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
         <v>29</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ9">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AK9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL9">
-        <v>580</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP9">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
+        <v>18</v>
+      </c>
+      <c r="AR9">
+        <v>50</v>
+      </c>
+      <c r="AS9">
         <v>14</v>
       </c>
-      <c r="AR9">
-        <v>27</v>
-      </c>
-      <c r="AS9">
-        <v>44</v>
-      </c>
       <c r="AT9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU9">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV9">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AX9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="BB9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE9">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="BF9">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BG9">
-        <v>70</v>
+        <v>13.5</v>
       </c>
       <c r="BH9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI9">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BO9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BP9">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BS9">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU9">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW9">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BY9">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10">
-        <v>1.59</v>
-      </c>
-      <c r="G10">
-        <v>1.61</v>
-      </c>
-      <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="I10">
-        <v>7.2</v>
-      </c>
-      <c r="J10">
-        <v>4.1</v>
-      </c>
-      <c r="K10">
-        <v>4.3</v>
-      </c>
-      <c r="L10">
-        <v>1.45</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.5</v>
-      </c>
-      <c r="O10">
-        <v>1.38</v>
-      </c>
-      <c r="P10">
-        <v>1.83</v>
-      </c>
-      <c r="Q10">
-        <v>2.14</v>
-      </c>
-      <c r="R10">
-        <v>1.31</v>
-      </c>
-      <c r="S10">
-        <v>4</v>
-      </c>
-      <c r="T10">
-        <v>2.18</v>
-      </c>
-      <c r="U10">
-        <v>1.76</v>
-      </c>
-      <c r="V10">
-        <v>1.16</v>
-      </c>
-      <c r="W10">
-        <v>2.62</v>
-      </c>
-      <c r="X10">
-        <v>13</v>
-      </c>
-      <c r="Y10">
-        <v>21</v>
-      </c>
-      <c r="Z10">
-        <v>60</v>
-      </c>
-      <c r="AA10">
-        <v>260</v>
-      </c>
-      <c r="AB10">
-        <v>7</v>
-      </c>
-      <c r="AC10">
-        <v>9.4</v>
-      </c>
-      <c r="AD10">
-        <v>29</v>
-      </c>
-      <c r="AE10">
-        <v>130</v>
-      </c>
-      <c r="AF10">
-        <v>8.6</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>27</v>
-      </c>
-      <c r="AI10">
-        <v>130</v>
-      </c>
-      <c r="AJ10">
-        <v>15</v>
-      </c>
-      <c r="AK10">
-        <v>19</v>
-      </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
-      <c r="AM10">
-        <v>190</v>
-      </c>
-      <c r="AN10">
-        <v>11</v>
-      </c>
-      <c r="AO10">
-        <v>230</v>
-      </c>
-      <c r="AP10">
-        <v>11</v>
-      </c>
-      <c r="AQ10">
-        <v>17</v>
-      </c>
-      <c r="AR10">
-        <v>50</v>
-      </c>
-      <c r="AS10">
-        <v>14</v>
-      </c>
-      <c r="AT10">
-        <v>6.4</v>
-      </c>
-      <c r="AU10">
-        <v>8.4</v>
-      </c>
-      <c r="AV10">
-        <v>25</v>
-      </c>
-      <c r="AW10">
-        <v>13.5</v>
-      </c>
-      <c r="AX10">
-        <v>7.6</v>
-      </c>
-      <c r="AY10">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10">
-        <v>24</v>
-      </c>
-      <c r="BA10">
-        <v>14.5</v>
-      </c>
-      <c r="BB10">
-        <v>13</v>
-      </c>
-      <c r="BC10">
-        <v>16.5</v>
-      </c>
-      <c r="BD10">
-        <v>40</v>
-      </c>
-      <c r="BE10">
-        <v>13.5</v>
-      </c>
-      <c r="BF10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG10">
-        <v>14</v>
-      </c>
-      <c r="BH10">
-        <v>3.35</v>
-      </c>
-      <c r="BI10">
-        <v>2.6</v>
-      </c>
-      <c r="BJ10">
-        <v>12.5</v>
-      </c>
-      <c r="BK10">
-        <v>5.9</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>10.5</v>
-      </c>
-      <c r="BN10">
-        <v>4</v>
-      </c>
-      <c r="BO10">
-        <v>3.05</v>
-      </c>
-      <c r="BP10">
-        <v>11</v>
-      </c>
-      <c r="BQ10">
-        <v>5.6</v>
-      </c>
-      <c r="BR10">
-        <v>32</v>
-      </c>
-      <c r="BS10">
-        <v>8.4</v>
-      </c>
-      <c r="BT10">
-        <v>11</v>
-      </c>
-      <c r="BU10">
-        <v>5.6</v>
-      </c>
-      <c r="BV10">
-        <v>80</v>
-      </c>
-      <c r="BW10">
-        <v>10</v>
-      </c>
-      <c r="BX10">
-        <v>85</v>
-      </c>
-      <c r="BY10">
-        <v>10</v>
-      </c>
-      <c r="BZ10">
-        <v>24</v>
-      </c>
-      <c r="CA10">
-        <v>7.6</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-05.xlsx
@@ -346,7 +346,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-08-05 14:41:37</t>
+    <t>2026-08-05 16:52:06</t>
   </si>
 </sst>
 </file>
@@ -940,226 +940,226 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>85</v>
       </c>
       <c r="K2">
+        <v>1000</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1.26</v>
+      </c>
+      <c r="S2">
+        <v>4.7</v>
+      </c>
+      <c r="T2">
+        <v>1.53</v>
+      </c>
+      <c r="U2">
+        <v>1.02</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>50</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1.37</v>
+      </c>
+      <c r="AK2">
+        <v>12.5</v>
+      </c>
+      <c r="AL2">
+        <v>320</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>42</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>220</v>
+      </c>
+      <c r="AQ2">
+        <v>220</v>
+      </c>
+      <c r="AR2">
+        <v>220</v>
+      </c>
+      <c r="AS2">
+        <v>220</v>
+      </c>
+      <c r="AT2">
+        <v>220</v>
+      </c>
+      <c r="AU2">
+        <v>220</v>
+      </c>
+      <c r="AV2">
+        <v>220</v>
+      </c>
+      <c r="AW2">
+        <v>220</v>
+      </c>
+      <c r="AX2">
+        <v>220</v>
+      </c>
+      <c r="AY2">
+        <v>220</v>
+      </c>
+      <c r="AZ2">
+        <v>220</v>
+      </c>
+      <c r="BA2">
+        <v>220</v>
+      </c>
+      <c r="BB2">
+        <v>1.12</v>
+      </c>
+      <c r="BC2">
         <v>4.5</v>
       </c>
-      <c r="L2">
-        <v>1.23</v>
-      </c>
-      <c r="M2">
-        <v>1.03</v>
-      </c>
-      <c r="N2">
-        <v>8</v>
-      </c>
-      <c r="O2">
-        <v>1.13</v>
-      </c>
-      <c r="P2">
-        <v>3.35</v>
-      </c>
-      <c r="Q2">
-        <v>1.4</v>
-      </c>
-      <c r="R2">
-        <v>1.96</v>
-      </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
-      <c r="T2">
-        <v>1.45</v>
-      </c>
-      <c r="U2">
-        <v>3.1</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
-      <c r="W2">
-        <v>2.08</v>
-      </c>
-      <c r="X2">
-        <v>36</v>
-      </c>
-      <c r="Y2">
+      <c r="BD2">
         <v>30</v>
       </c>
-      <c r="Z2">
-        <v>38</v>
-      </c>
-      <c r="AA2">
-        <v>75</v>
-      </c>
-      <c r="AB2">
-        <v>19</v>
-      </c>
-      <c r="AC2">
-        <v>12.5</v>
-      </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>36</v>
-      </c>
-      <c r="AF2">
-        <v>18</v>
-      </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>14</v>
-      </c>
-      <c r="AI2">
-        <v>32</v>
-      </c>
-      <c r="AJ2">
-        <v>25</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>19.5</v>
-      </c>
-      <c r="AM2">
-        <v>40</v>
-      </c>
-      <c r="AN2">
-        <v>6.6</v>
-      </c>
-      <c r="AO2">
-        <v>18.5</v>
-      </c>
-      <c r="AP2">
-        <v>30</v>
-      </c>
-      <c r="AQ2">
-        <v>26</v>
-      </c>
-      <c r="AR2">
-        <v>34</v>
-      </c>
-      <c r="AS2">
-        <v>60</v>
-      </c>
-      <c r="AT2">
-        <v>17.5</v>
-      </c>
-      <c r="AU2">
-        <v>11</v>
-      </c>
-      <c r="AV2">
-        <v>15.5</v>
-      </c>
-      <c r="AW2">
-        <v>32</v>
-      </c>
-      <c r="AX2">
-        <v>17.5</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2">
+      <c r="BE2">
+        <v>6.2</v>
+      </c>
+      <c r="BF2">
         <v>13</v>
       </c>
-      <c r="BA2">
-        <v>30</v>
-      </c>
-      <c r="BB2">
-        <v>24</v>
-      </c>
-      <c r="BC2">
-        <v>15</v>
-      </c>
-      <c r="BD2">
-        <v>19</v>
-      </c>
-      <c r="BE2">
-        <v>34</v>
-      </c>
-      <c r="BF2">
-        <v>6</v>
-      </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>110</v>
@@ -1182,226 +1182,226 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="J3">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.22</v>
+        <v>7.2</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
+        <v>2.26</v>
+      </c>
+      <c r="O3">
+        <v>1.72</v>
+      </c>
+      <c r="P3">
+        <v>1.39</v>
+      </c>
+      <c r="Q3">
+        <v>3.35</v>
+      </c>
+      <c r="R3">
+        <v>1.12</v>
+      </c>
+      <c r="S3">
+        <v>8.6</v>
+      </c>
+      <c r="T3">
+        <v>2.7</v>
+      </c>
+      <c r="U3">
+        <v>1.54</v>
+      </c>
+      <c r="V3">
+        <v>1.32</v>
+      </c>
+      <c r="W3">
+        <v>1.72</v>
+      </c>
+      <c r="X3">
+        <v>7.2</v>
+      </c>
+      <c r="Y3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z3">
+        <v>29</v>
+      </c>
+      <c r="AA3">
+        <v>120</v>
+      </c>
+      <c r="AB3">
+        <v>6.2</v>
+      </c>
+      <c r="AC3">
         <v>7.6</v>
       </c>
-      <c r="O3">
-        <v>1.12</v>
-      </c>
-      <c r="P3">
-        <v>3.25</v>
-      </c>
-      <c r="Q3">
-        <v>1.41</v>
-      </c>
-      <c r="R3">
-        <v>2</v>
-      </c>
-      <c r="S3">
-        <v>1.96</v>
-      </c>
-      <c r="T3">
-        <v>1.47</v>
-      </c>
-      <c r="U3">
-        <v>2.8</v>
-      </c>
-      <c r="V3">
-        <v>1.22</v>
-      </c>
-      <c r="W3">
-        <v>2.48</v>
-      </c>
-      <c r="X3">
-        <v>50</v>
-      </c>
-      <c r="Y3">
+      <c r="AD3">
+        <v>26</v>
+      </c>
+      <c r="AE3">
+        <v>100</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>15.5</v>
+      </c>
+      <c r="AH3">
+        <v>42</v>
+      </c>
+      <c r="AI3">
+        <v>190</v>
+      </c>
+      <c r="AJ3">
         <v>36</v>
       </c>
-      <c r="Z3">
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>120</v>
+      </c>
+      <c r="AM3">
+        <v>590</v>
+      </c>
+      <c r="AN3">
         <v>55</v>
       </c>
-      <c r="AA3">
-        <v>150</v>
-      </c>
-      <c r="AB3">
-        <v>18.5</v>
-      </c>
-      <c r="AC3">
-        <v>13</v>
-      </c>
-      <c r="AD3">
-        <v>25</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>17.5</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>19.5</v>
-      </c>
-      <c r="AI3">
-        <v>44</v>
-      </c>
-      <c r="AJ3">
-        <v>22</v>
-      </c>
-      <c r="AK3">
-        <v>15.5</v>
-      </c>
-      <c r="AL3">
-        <v>24</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>5.1</v>
-      </c>
       <c r="AO3">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="AP3">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BA3">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="BB3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BC3">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BD3">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="BE3">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="BH3">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="BI3">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BJ3">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="BL3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.8</v>
+        <v>1.25</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>800</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="BP3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="BR3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>5.3</v>
+        <v>1.25</v>
       </c>
       <c r="BT3">
-        <v>10</v>
+        <v>800</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>1.25</v>
       </c>
       <c r="BX3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>6.2</v>
+        <v>1.25</v>
       </c>
       <c r="BZ3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>1.25</v>
       </c>
       <c r="CB3" t="s">
         <v>110</v>
@@ -1424,226 +1424,226 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>3.45</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="H4">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="I4">
+        <v>1.29</v>
+      </c>
+      <c r="J4">
+        <v>6.6</v>
+      </c>
+      <c r="K4">
+        <v>7.2</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>11</v>
+      </c>
+      <c r="O4">
+        <v>1.03</v>
+      </c>
+      <c r="P4">
+        <v>2.3</v>
+      </c>
+      <c r="Q4">
+        <v>1.73</v>
+      </c>
+      <c r="R4">
+        <v>2.1</v>
+      </c>
+      <c r="S4">
+        <v>1.83</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>2.74</v>
+      </c>
+      <c r="V4">
+        <v>4.3</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>25</v>
+      </c>
+      <c r="Z4">
+        <v>290</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>980</v>
+      </c>
+      <c r="AD4">
+        <v>14</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>790</v>
+      </c>
+      <c r="AH4">
+        <v>990</v>
+      </c>
+      <c r="AI4">
+        <v>80</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>10</v>
+      </c>
+      <c r="AP4">
+        <v>1.55</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>8.6</v>
+      </c>
+      <c r="AS4">
+        <v>1.34</v>
+      </c>
+      <c r="AT4">
+        <v>1.32</v>
+      </c>
+      <c r="AU4">
+        <v>2.5</v>
+      </c>
+      <c r="AV4">
+        <v>1.2</v>
+      </c>
+      <c r="AW4">
+        <v>1.34</v>
+      </c>
+      <c r="AX4">
+        <v>1.32</v>
+      </c>
+      <c r="AY4">
+        <v>1.32</v>
+      </c>
+      <c r="AZ4">
+        <v>2.5</v>
+      </c>
+      <c r="BA4">
+        <v>2.9</v>
+      </c>
+      <c r="BB4">
+        <v>1.32</v>
+      </c>
+      <c r="BC4">
+        <v>1.32</v>
+      </c>
+      <c r="BD4">
+        <v>2.9</v>
+      </c>
+      <c r="BE4">
+        <v>1.55</v>
+      </c>
+      <c r="BF4">
+        <v>1.32</v>
+      </c>
+      <c r="BG4">
+        <v>3.35</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.98</v>
+      </c>
+      <c r="BJ4">
+        <v>970</v>
+      </c>
+      <c r="BK4">
+        <v>3.1</v>
+      </c>
+      <c r="BL4">
+        <v>950</v>
+      </c>
+      <c r="BM4">
         <v>1.97</v>
       </c>
-      <c r="J4">
-        <v>4.9</v>
-      </c>
-      <c r="K4">
-        <v>5.2</v>
-      </c>
-      <c r="L4">
-        <v>1.14</v>
-      </c>
-      <c r="M4">
-        <v>1.01</v>
-      </c>
-      <c r="N4">
-        <v>14</v>
-      </c>
-      <c r="O4">
-        <v>1.07</v>
-      </c>
-      <c r="P4">
-        <v>5.3</v>
-      </c>
-      <c r="Q4">
-        <v>1.21</v>
-      </c>
-      <c r="R4">
-        <v>2.82</v>
-      </c>
-      <c r="S4">
-        <v>1.52</v>
-      </c>
-      <c r="T4">
-        <v>1.28</v>
-      </c>
-      <c r="U4">
-        <v>4.2</v>
-      </c>
-      <c r="V4">
-        <v>2.02</v>
-      </c>
-      <c r="W4">
-        <v>1.39</v>
-      </c>
-      <c r="X4">
-        <v>130</v>
-      </c>
-      <c r="Y4">
-        <v>36</v>
-      </c>
-      <c r="Z4">
-        <v>29</v>
-      </c>
-      <c r="AA4">
-        <v>32</v>
-      </c>
-      <c r="AB4">
-        <v>60</v>
-      </c>
-      <c r="AC4">
-        <v>18.5</v>
-      </c>
-      <c r="AD4">
-        <v>15</v>
-      </c>
-      <c r="AE4">
-        <v>18.5</v>
-      </c>
-      <c r="AF4">
-        <v>110</v>
-      </c>
-      <c r="AG4">
-        <v>21</v>
-      </c>
-      <c r="AH4">
-        <v>14.5</v>
-      </c>
-      <c r="AI4">
-        <v>18</v>
-      </c>
-      <c r="AJ4">
-        <v>75</v>
-      </c>
-      <c r="AK4">
-        <v>34</v>
-      </c>
-      <c r="AL4">
-        <v>25</v>
-      </c>
-      <c r="AM4">
-        <v>28</v>
-      </c>
-      <c r="AN4">
-        <v>11</v>
-      </c>
-      <c r="AO4">
-        <v>4.6</v>
-      </c>
-      <c r="AP4">
-        <v>55</v>
-      </c>
-      <c r="AQ4">
-        <v>30</v>
-      </c>
-      <c r="AR4">
-        <v>25</v>
-      </c>
-      <c r="AS4">
-        <v>27</v>
-      </c>
-      <c r="AT4">
-        <v>42</v>
-      </c>
-      <c r="AU4">
-        <v>16</v>
-      </c>
-      <c r="AV4">
-        <v>13</v>
-      </c>
-      <c r="AW4">
-        <v>16</v>
-      </c>
-      <c r="AX4">
-        <v>42</v>
-      </c>
-      <c r="AY4">
-        <v>18</v>
-      </c>
-      <c r="AZ4">
-        <v>12.5</v>
-      </c>
-      <c r="BA4">
-        <v>16</v>
-      </c>
-      <c r="BB4">
-        <v>40</v>
-      </c>
-      <c r="BC4">
-        <v>28</v>
-      </c>
-      <c r="BD4">
-        <v>22</v>
-      </c>
-      <c r="BE4">
-        <v>24</v>
-      </c>
-      <c r="BF4">
-        <v>9.6</v>
-      </c>
-      <c r="BG4">
-        <v>4.2</v>
-      </c>
-      <c r="BH4">
-        <v>8</v>
-      </c>
-      <c r="BI4">
-        <v>6.6</v>
-      </c>
-      <c r="BJ4">
-        <v>8</v>
-      </c>
-      <c r="BK4">
-        <v>6.6</v>
-      </c>
-      <c r="BL4">
-        <v>34</v>
-      </c>
-      <c r="BM4">
-        <v>11</v>
-      </c>
       <c r="BN4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>7.8</v>
+        <v>1.98</v>
       </c>
       <c r="BP4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>1.98</v>
       </c>
       <c r="BR4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>1.98</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>1.22</v>
       </c>
       <c r="BV4">
-        <v>12</v>
+        <v>890</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>1.99</v>
       </c>
       <c r="BX4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
-        <v>6.6</v>
+        <v>830</v>
       </c>
       <c r="CA4">
-        <v>5.4</v>
+        <v>1.97</v>
       </c>
       <c r="CB4" t="s">
         <v>110</v>
@@ -1666,178 +1666,178 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q5">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="R5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="X5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB5">
         <v>6.4</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM5">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AO5">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC5">
         <v>27</v>
       </c>
       <c r="BD5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE5">
         <v>180</v>
       </c>
       <c r="BF5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="BH5">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BI5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1846,46 +1846,46 @@
         <v>230</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BR5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BX5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>110</v>
@@ -1908,85 +1908,85 @@
         <v>106</v>
       </c>
       <c r="F6">
+        <v>2.5</v>
+      </c>
+      <c r="G6">
+        <v>2.64</v>
+      </c>
+      <c r="H6">
+        <v>2.86</v>
+      </c>
+      <c r="I6">
+        <v>3.05</v>
+      </c>
+      <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
+        <v>3.75</v>
+      </c>
+      <c r="L6">
+        <v>1.31</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>1.22</v>
+      </c>
+      <c r="P6">
+        <v>2.38</v>
+      </c>
+      <c r="Q6">
+        <v>1.71</v>
+      </c>
+      <c r="R6">
+        <v>1.56</v>
+      </c>
+      <c r="S6">
+        <v>2.66</v>
+      </c>
+      <c r="T6">
+        <v>1.6</v>
+      </c>
+      <c r="U6">
         <v>2.44</v>
       </c>
-      <c r="G6">
-        <v>2.56</v>
-      </c>
-      <c r="H6">
-        <v>2.78</v>
-      </c>
-      <c r="I6">
-        <v>2.96</v>
-      </c>
-      <c r="J6">
-        <v>3.75</v>
-      </c>
-      <c r="K6">
-        <v>4.1</v>
-      </c>
-      <c r="L6">
-        <v>1.29</v>
-      </c>
-      <c r="M6">
-        <v>1.04</v>
-      </c>
-      <c r="N6">
-        <v>5.5</v>
-      </c>
-      <c r="O6">
-        <v>1.19</v>
-      </c>
-      <c r="P6">
-        <v>2.52</v>
-      </c>
-      <c r="Q6">
-        <v>1.62</v>
-      </c>
-      <c r="R6">
-        <v>1.61</v>
-      </c>
-      <c r="S6">
-        <v>2.48</v>
-      </c>
-      <c r="T6">
-        <v>1.56</v>
-      </c>
-      <c r="U6">
-        <v>2.58</v>
-      </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>14</v>
       </c>
       <c r="AE6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG6">
         <v>13</v>
@@ -1995,52 +1995,52 @@
         <v>15.5</v>
       </c>
       <c r="AI6">
+        <v>36</v>
+      </c>
+      <c r="AJ6">
+        <v>38</v>
+      </c>
+      <c r="AK6">
+        <v>26</v>
+      </c>
+      <c r="AL6">
         <v>34</v>
       </c>
-      <c r="AJ6">
+      <c r="AM6">
+        <v>65</v>
+      </c>
+      <c r="AN6">
+        <v>16.5</v>
+      </c>
+      <c r="AO6">
+        <v>19.5</v>
+      </c>
+      <c r="AP6">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6">
+        <v>13</v>
+      </c>
+      <c r="AR6">
+        <v>18.5</v>
+      </c>
+      <c r="AS6">
         <v>36</v>
       </c>
-      <c r="AK6">
-        <v>24</v>
-      </c>
-      <c r="AL6">
-        <v>30</v>
-      </c>
-      <c r="AM6">
-        <v>70</v>
-      </c>
-      <c r="AN6">
-        <v>14</v>
-      </c>
-      <c r="AO6">
-        <v>16.5</v>
-      </c>
-      <c r="AP6">
-        <v>18</v>
-      </c>
-      <c r="AQ6">
-        <v>14.5</v>
-      </c>
-      <c r="AR6">
-        <v>19.5</v>
-      </c>
-      <c r="AS6">
-        <v>32</v>
-      </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY6">
         <v>10</v>
@@ -2049,79 +2049,79 @@
         <v>12.5</v>
       </c>
       <c r="BA6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB6">
         <v>26</v>
       </c>
       <c r="BC6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD6">
         <v>24</v>
       </c>
       <c r="BE6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
+        <v>4.3</v>
+      </c>
+      <c r="BI6">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6">
+        <v>9</v>
+      </c>
+      <c r="BK6">
         <v>4.6</v>
       </c>
-      <c r="BI6">
-        <v>3.45</v>
-      </c>
-      <c r="BJ6">
+      <c r="BL6">
+        <v>85</v>
+      </c>
+      <c r="BM6">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BK6">
-        <v>4.8</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>9.199999999999999</v>
       </c>
       <c r="BN6">
         <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
         <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2156,25 +2156,25 @@
         <v>2.06</v>
       </c>
       <c r="H7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
         <v>1.46</v>
@@ -2183,7 +2183,7 @@
         <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
         <v>1.23</v>
@@ -2192,16 +2192,16 @@
         <v>4.7</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>10.5</v>
@@ -2210,13 +2210,13 @@
         <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="AB7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2228,25 +2228,25 @@
         <v>210</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="AJ7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK7">
         <v>29</v>
       </c>
       <c r="AL7">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2264,13 +2264,13 @@
         <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AS7">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="AT7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
@@ -2279,7 +2279,7 @@
         <v>17</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AX7">
         <v>9.4</v>
@@ -2288,10 +2288,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2300,16 +2300,16 @@
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BE7">
         <v>120</v>
       </c>
       <c r="BF7">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BH7">
         <v>3.3</v>
@@ -2318,10 +2318,10 @@
         <v>2.5</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2330,46 +2330,46 @@
         <v>140</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BO7">
         <v>3.6</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BR7">
         <v>40</v>
       </c>
       <c r="BS7">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BT7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW7">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7">
         <v>40</v>
       </c>
       <c r="CA7">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="s">
         <v>110</v>
@@ -2395,37 +2395,37 @@
         <v>1.72</v>
       </c>
       <c r="G8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>3.65</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.46</v>
       </c>
       <c r="P8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
         <v>1.24</v>
@@ -2437,22 +2437,22 @@
         <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V8">
         <v>1.18</v>
       </c>
       <c r="W8">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X8">
         <v>11</v>
       </c>
       <c r="Y8">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2461,7 +2461,7 @@
         <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>32</v>
@@ -2482,19 +2482,19 @@
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK8">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2503,16 +2503,16 @@
         <v>9.6</v>
       </c>
       <c r="AQ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AS8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU8">
         <v>7.8</v>
@@ -2530,82 +2530,82 @@
         <v>9.6</v>
       </c>
       <c r="AZ8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA8">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="BB8">
         <v>16</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BE8">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="BF8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG8">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ8">
         <v>14.5</v>
       </c>
       <c r="BK8">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BN8">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO8">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BP8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BR8">
         <v>44</v>
       </c>
       <c r="BS8">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BT8">
         <v>11.5</v>
       </c>
       <c r="BU8">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BX8">
         <v>100</v>
       </c>
       <c r="BY8">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2634,16 +2634,16 @@
         <v>109</v>
       </c>
       <c r="F9">
+        <v>1.56</v>
+      </c>
+      <c r="G9">
         <v>1.59</v>
       </c>
-      <c r="G9">
-        <v>1.61</v>
-      </c>
       <c r="H9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>4.1</v>
@@ -2652,7 +2652,7 @@
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
         <v>1.08</v>
@@ -2664,7 +2664,7 @@
         <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
         <v>2.14</v>
@@ -2673,19 +2673,19 @@
         <v>1.31</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U9">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="X9">
         <v>13</v>
@@ -2694,67 +2694,67 @@
         <v>21</v>
       </c>
       <c r="Z9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AA9">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD9">
         <v>29</v>
       </c>
       <c r="AE9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK9">
         <v>19</v>
       </c>
       <c r="AL9">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AM9">
+        <v>190</v>
+      </c>
+      <c r="AN9">
+        <v>24</v>
+      </c>
+      <c r="AO9">
         <v>200</v>
       </c>
-      <c r="AN9">
-        <v>11</v>
-      </c>
-      <c r="AO9">
-        <v>230</v>
-      </c>
       <c r="AP9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9">
         <v>50</v>
       </c>
       <c r="AS9">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AT9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU9">
         <v>8.4</v>
@@ -2763,10 +2763,10 @@
         <v>25</v>
       </c>
       <c r="AW9">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="AX9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY9">
         <v>9.4</v>
@@ -2775,85 +2775,85 @@
         <v>24</v>
       </c>
       <c r="BA9">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BD9">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="BE9">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF9">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI9">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9">
         <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO9">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP9">
         <v>11</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR9">
         <v>32</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9">
         <v>24</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="s">
         <v>110</v>
